--- a/elec_room_project/template_전기실_운영일지.xlsx
+++ b/elec_room_project/template_전기실_운영일지.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\pygame\pygame\elec_room_project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\elec_room_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A33918B2-EA72-435F-BCDF-D4855CED4282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F8C2CF6-317B-440C-99C8-FAC2AB451094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1980" yWindow="1785" windowWidth="21600" windowHeight="13590" xr2:uid="{943AB7D1-EB27-49C3-9C36-555299583416}"/>
+    <workbookView xWindow="1515" yWindow="1740" windowWidth="21600" windowHeight="13590" xr2:uid="{943AB7D1-EB27-49C3-9C36-555299583416}"/>
   </bookViews>
   <sheets>
     <sheet name="전력설비_운전현황" sheetId="4" r:id="rId1"/>
@@ -1029,7 +1029,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="43">
+  <borders count="44">
     <border>
       <left/>
       <right/>
@@ -1591,13 +1591,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="148">
+  <cellXfs count="150">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1628,10 +1641,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1783,260 +1792,817 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="57">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2354,7 +2920,7 @@
   <cols>
     <col min="1" max="1" width="9.125" customWidth="1"/>
     <col min="2" max="2" width="9.375" customWidth="1"/>
-    <col min="3" max="10" width="16.25" customWidth="1"/>
+    <col min="3" max="10" width="17.75" customWidth="1"/>
     <col min="11" max="11" width="22.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2369,30 +2935,30 @@
         <v>223</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="65.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="72" t="s">
+    <row r="2" spans="1:10" ht="86.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="109" t="s">
         <v>170</v>
       </c>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
+      <c r="B2" s="109"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="109"/>
+      <c r="F2" s="109"/>
+      <c r="G2" s="109"/>
       <c r="H2" s="7"/>
       <c r="I2" s="8"/>
       <c r="J2" s="9"/>
     </row>
-    <row r="3" spans="1:10" ht="25.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
+    <row r="3" spans="1:10" ht="25.9" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="10" t="s">
+      <c r="B3" s="149"/>
+      <c r="C3" s="149"/>
+      <c r="D3" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="H3" s="2" t="s">
         <v>173</v>
       </c>
     </row>
@@ -2402,417 +2968,417 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="73" t="s">
+      <c r="A5" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="74"/>
-      <c r="C5" s="73" t="s">
+      <c r="B5" s="110"/>
+      <c r="C5" s="88" t="s">
         <v>175</v>
       </c>
-      <c r="D5" s="73"/>
-      <c r="E5" s="73" t="s">
+      <c r="D5" s="88"/>
+      <c r="E5" s="88" t="s">
         <v>176</v>
       </c>
-      <c r="F5" s="73"/>
-      <c r="G5" s="73" t="s">
+      <c r="F5" s="88"/>
+      <c r="G5" s="88" t="s">
         <v>177</v>
       </c>
-      <c r="H5" s="73"/>
-      <c r="I5" s="73" t="s">
+      <c r="H5" s="88"/>
+      <c r="I5" s="88" t="s">
         <v>178</v>
       </c>
-      <c r="J5" s="73"/>
+      <c r="J5" s="88"/>
     </row>
     <row r="6" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="75"/>
-      <c r="B6" s="76"/>
-      <c r="C6" s="12" t="s">
+      <c r="A6" s="111"/>
+      <c r="B6" s="112"/>
+      <c r="C6" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="J6" s="12" t="s">
+      <c r="J6" s="10" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="73" t="s">
+      <c r="A7" s="88" t="s">
         <v>181</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="C7" s="121" t="s">
+      <c r="C7" s="61" t="s">
         <v>183</v>
       </c>
-      <c r="D7" s="121" t="s">
+      <c r="D7" s="61" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="121" t="s">
+      <c r="E7" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="121" t="s">
+      <c r="F7" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="121" t="s">
+      <c r="G7" s="61" t="s">
         <v>57</v>
       </c>
-      <c r="H7" s="121" t="s">
+      <c r="H7" s="61" t="s">
         <v>58</v>
       </c>
-      <c r="I7" s="121" t="s">
+      <c r="I7" s="61" t="s">
         <v>77</v>
       </c>
-      <c r="J7" s="121" t="s">
+      <c r="J7" s="61" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="73"/>
-      <c r="B8" s="12" t="s">
+      <c r="A8" s="88"/>
+      <c r="B8" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="C8" s="121" t="s">
+      <c r="C8" s="61" t="s">
         <v>185</v>
       </c>
-      <c r="D8" s="121" t="s">
+      <c r="D8" s="61" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="121" t="s">
+      <c r="E8" s="61" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="121" t="s">
+      <c r="F8" s="61" t="s">
         <v>40</v>
       </c>
-      <c r="G8" s="121" t="s">
+      <c r="G8" s="61" t="s">
         <v>59</v>
       </c>
-      <c r="H8" s="121" t="s">
+      <c r="H8" s="61" t="s">
         <v>60</v>
       </c>
-      <c r="I8" s="121" t="s">
+      <c r="I8" s="61" t="s">
         <v>79</v>
       </c>
-      <c r="J8" s="121" t="s">
+      <c r="J8" s="61" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="73"/>
-      <c r="B9" s="12" t="s">
+      <c r="A9" s="88"/>
+      <c r="B9" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="C9" s="121" t="s">
+      <c r="C9" s="61" t="s">
         <v>187</v>
       </c>
-      <c r="D9" s="121" t="s">
+      <c r="D9" s="61" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="121" t="s">
+      <c r="E9" s="61" t="s">
         <v>41</v>
       </c>
-      <c r="F9" s="121" t="s">
+      <c r="F9" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="121" t="s">
+      <c r="G9" s="61" t="s">
         <v>61</v>
       </c>
-      <c r="H9" s="121" t="s">
+      <c r="H9" s="61" t="s">
         <v>62</v>
       </c>
-      <c r="I9" s="121" t="s">
+      <c r="I9" s="61" t="s">
         <v>81</v>
       </c>
-      <c r="J9" s="121" t="s">
+      <c r="J9" s="61" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="73" t="s">
+      <c r="A10" s="88" t="s">
         <v>188</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="C10" s="121" t="s">
+      <c r="C10" s="61" t="s">
         <v>190</v>
       </c>
-      <c r="D10" s="121" t="s">
+      <c r="D10" s="61" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="121" t="s">
+      <c r="E10" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="F10" s="121" t="s">
+      <c r="F10" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="G10" s="121" t="s">
+      <c r="G10" s="61" t="s">
         <v>63</v>
       </c>
-      <c r="H10" s="121" t="s">
+      <c r="H10" s="61" t="s">
         <v>64</v>
       </c>
-      <c r="I10" s="121" t="s">
+      <c r="I10" s="61" t="s">
         <v>83</v>
       </c>
-      <c r="J10" s="121" t="s">
+      <c r="J10" s="61" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="73"/>
-      <c r="B11" s="12" t="s">
+      <c r="A11" s="88"/>
+      <c r="B11" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="C11" s="121" t="s">
+      <c r="C11" s="61" t="s">
         <v>192</v>
       </c>
-      <c r="D11" s="121" t="s">
+      <c r="D11" s="61" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="121" t="s">
+      <c r="E11" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="F11" s="121" t="s">
+      <c r="F11" s="61" t="s">
         <v>46</v>
       </c>
-      <c r="G11" s="121" t="s">
+      <c r="G11" s="61" t="s">
         <v>65</v>
       </c>
-      <c r="H11" s="121" t="s">
+      <c r="H11" s="61" t="s">
         <v>66</v>
       </c>
-      <c r="I11" s="121" t="s">
+      <c r="I11" s="61" t="s">
         <v>85</v>
       </c>
-      <c r="J11" s="121" t="s">
+      <c r="J11" s="61" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="73"/>
-      <c r="B12" s="12" t="s">
+      <c r="A12" s="88"/>
+      <c r="B12" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="C12" s="121" t="s">
+      <c r="C12" s="61" t="s">
         <v>194</v>
       </c>
-      <c r="D12" s="121" t="s">
+      <c r="D12" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="121" t="s">
+      <c r="E12" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="F12" s="121" t="s">
+      <c r="F12" s="61" t="s">
         <v>48</v>
       </c>
-      <c r="G12" s="121" t="s">
+      <c r="G12" s="61" t="s">
         <v>67</v>
       </c>
-      <c r="H12" s="121" t="s">
+      <c r="H12" s="61" t="s">
         <v>68</v>
       </c>
-      <c r="I12" s="121" t="s">
+      <c r="I12" s="61" t="s">
         <v>87</v>
       </c>
-      <c r="J12" s="121" t="s">
+      <c r="J12" s="61" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="73" t="s">
+      <c r="A13" s="88" t="s">
         <v>195</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="C13" s="121" t="s">
+      <c r="C13" s="61" t="s">
         <v>196</v>
       </c>
-      <c r="D13" s="121" t="s">
+      <c r="D13" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="121" t="s">
+      <c r="E13" s="61" t="s">
         <v>49</v>
       </c>
-      <c r="F13" s="121" t="s">
+      <c r="F13" s="61" t="s">
         <v>50</v>
       </c>
-      <c r="G13" s="121" t="s">
+      <c r="G13" s="61" t="s">
         <v>69</v>
       </c>
-      <c r="H13" s="121" t="s">
+      <c r="H13" s="61" t="s">
         <v>70</v>
       </c>
-      <c r="I13" s="121" t="s">
+      <c r="I13" s="61" t="s">
         <v>89</v>
       </c>
-      <c r="J13" s="121" t="s">
+      <c r="J13" s="61" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="73"/>
-      <c r="B14" s="12" t="s">
+      <c r="A14" s="88"/>
+      <c r="B14" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="C14" s="121" t="s">
+      <c r="C14" s="61" t="s">
         <v>197</v>
       </c>
-      <c r="D14" s="121" t="s">
+      <c r="D14" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="121" t="s">
+      <c r="E14" s="61" t="s">
         <v>51</v>
       </c>
-      <c r="F14" s="121" t="s">
+      <c r="F14" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="G14" s="121" t="s">
+      <c r="G14" s="61" t="s">
         <v>71</v>
       </c>
-      <c r="H14" s="121" t="s">
+      <c r="H14" s="61" t="s">
         <v>72</v>
       </c>
-      <c r="I14" s="121" t="s">
+      <c r="I14" s="61" t="s">
         <v>91</v>
       </c>
-      <c r="J14" s="121" t="s">
+      <c r="J14" s="61" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="73"/>
-      <c r="B15" s="12" t="s">
+      <c r="A15" s="88"/>
+      <c r="B15" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="C15" s="121" t="s">
+      <c r="C15" s="61" t="s">
         <v>198</v>
       </c>
-      <c r="D15" s="121" t="s">
+      <c r="D15" s="61" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="121" t="s">
+      <c r="E15" s="61" t="s">
         <v>53</v>
       </c>
-      <c r="F15" s="121" t="s">
+      <c r="F15" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="G15" s="121" t="s">
+      <c r="G15" s="61" t="s">
         <v>73</v>
       </c>
-      <c r="H15" s="121" t="s">
+      <c r="H15" s="61" t="s">
         <v>74</v>
       </c>
-      <c r="I15" s="121" t="s">
+      <c r="I15" s="61" t="s">
         <v>93</v>
       </c>
-      <c r="J15" s="121" t="s">
+      <c r="J15" s="61" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="C16" s="121" t="s">
+      <c r="C16" s="61" t="s">
         <v>200</v>
       </c>
-      <c r="D16" s="121" t="s">
+      <c r="D16" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="E16" s="121" t="s">
+      <c r="E16" s="61" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="121" t="s">
+      <c r="F16" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="G16" s="121" t="s">
+      <c r="G16" s="61" t="s">
         <v>75</v>
       </c>
-      <c r="H16" s="121" t="s">
+      <c r="H16" s="61" t="s">
         <v>76</v>
       </c>
-      <c r="I16" s="121" t="s">
+      <c r="I16" s="61" t="s">
         <v>95</v>
       </c>
-      <c r="J16" s="121" t="s">
+      <c r="J16" s="61" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="83" t="s">
+      <c r="A17" s="122" t="s">
         <v>201</v>
       </c>
-      <c r="B17" s="84"/>
-      <c r="C17" s="121"/>
-      <c r="D17" s="121"/>
-      <c r="E17" s="121" t="s">
+      <c r="B17" s="123"/>
+      <c r="C17" s="61"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="61" t="s">
         <v>202</v>
       </c>
-      <c r="F17" s="121" t="s">
+      <c r="F17" s="61" t="s">
         <v>203</v>
       </c>
-      <c r="G17" s="121" t="s">
+      <c r="G17" s="61" t="s">
         <v>204</v>
       </c>
-      <c r="H17" s="121" t="s">
+      <c r="H17" s="61" t="s">
         <v>205</v>
       </c>
-      <c r="I17" s="121" t="s">
+      <c r="I17" s="61" t="s">
         <v>206</v>
       </c>
-      <c r="J17" s="121" t="s">
+      <c r="J17" s="61" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="103" t="s">
+      <c r="A18" s="89" t="s">
         <v>225</v>
       </c>
-      <c r="B18" s="103"/>
-      <c r="C18" s="121"/>
-      <c r="D18" s="121"/>
-      <c r="E18" s="122" t="e">
+      <c r="B18" s="89"/>
+      <c r="C18" s="61"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="62" t="e">
         <f>+E16/1000</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F18" s="123" t="e">
+      <c r="F18" s="63" t="e">
         <f>+F16/1000</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G18" s="122" t="e">
+      <c r="G18" s="62" t="e">
         <f>+G16/1250</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H18" s="123" t="e">
+      <c r="H18" s="63" t="e">
         <f t="shared" ref="H18:J18" si="0">+H16/1250</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I18" s="122" t="e">
+      <c r="I18" s="62" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="J18" s="123" t="e">
+      <c r="J18" s="63" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -2823,60 +3389,60 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="80" t="s">
+      <c r="A20" s="118" t="s">
         <v>209</v>
       </c>
-      <c r="B20" s="78"/>
-      <c r="C20" s="78" t="s">
+      <c r="B20" s="116"/>
+      <c r="C20" s="116" t="s">
         <v>210</v>
       </c>
-      <c r="D20" s="78"/>
-      <c r="E20" s="78" t="s">
+      <c r="D20" s="116"/>
+      <c r="E20" s="147" t="s">
         <v>211</v>
       </c>
-      <c r="F20" s="78"/>
-      <c r="G20" s="78" t="s">
+      <c r="F20" s="148"/>
+      <c r="G20" s="116" t="s">
         <v>212</v>
       </c>
-      <c r="H20" s="79"/>
+      <c r="H20" s="117"/>
     </row>
     <row r="21" spans="1:10" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="81" t="s">
+      <c r="A21" s="119" t="s">
         <v>213</v>
       </c>
-      <c r="B21" s="73"/>
-      <c r="C21" s="124" t="s">
+      <c r="B21" s="88"/>
+      <c r="C21" s="82" t="s">
         <v>224</v>
       </c>
-      <c r="D21" s="124"/>
-      <c r="E21" s="124" t="s">
+      <c r="D21" s="82"/>
+      <c r="E21" s="145" t="s">
         <v>214</v>
       </c>
-      <c r="F21" s="124"/>
-      <c r="G21" s="124" t="e">
+      <c r="F21" s="146"/>
+      <c r="G21" s="82" t="e">
         <f>E21-C21</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H21" s="125"/>
+      <c r="H21" s="114"/>
     </row>
     <row r="22" spans="1:10" ht="35.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="82" t="s">
+      <c r="A22" s="120" t="s">
         <v>215</v>
       </c>
-      <c r="B22" s="77"/>
-      <c r="C22" s="126" t="s">
+      <c r="B22" s="121"/>
+      <c r="C22" s="113" t="s">
         <v>241</v>
       </c>
-      <c r="D22" s="126"/>
-      <c r="E22" s="126" t="s">
+      <c r="D22" s="113"/>
+      <c r="E22" s="113" t="s">
         <v>242</v>
       </c>
-      <c r="F22" s="126"/>
-      <c r="G22" s="127" t="e">
+      <c r="F22" s="113"/>
+      <c r="G22" s="84" t="e">
         <f>+E22-C22</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H22" s="128"/>
+      <c r="H22" s="115"/>
     </row>
     <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="24" spans="1:10" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -2885,343 +3451,343 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="136" t="s">
+      <c r="A25" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="B25" s="134"/>
-      <c r="C25" s="134" t="s">
+      <c r="B25" s="74"/>
+      <c r="C25" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="134"/>
-      <c r="E25" s="134" t="s">
+      <c r="D25" s="74"/>
+      <c r="E25" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="F25" s="134"/>
-      <c r="G25" s="134"/>
-      <c r="H25" s="134" t="s">
+      <c r="F25" s="74"/>
+      <c r="G25" s="74"/>
+      <c r="H25" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="I25" s="134"/>
-      <c r="J25" s="135"/>
+      <c r="I25" s="74"/>
+      <c r="J25" s="87"/>
     </row>
     <row r="26" spans="1:10" ht="35.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="132"/>
-      <c r="B26" s="133"/>
-      <c r="C26" s="138" t="s">
+      <c r="A26" s="90"/>
+      <c r="B26" s="91"/>
+      <c r="C26" s="66" t="s">
         <v>4</v>
       </c>
-      <c r="D26" s="138" t="s">
+      <c r="D26" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="E26" s="138" t="s">
+      <c r="E26" s="66" t="s">
         <v>6</v>
       </c>
-      <c r="F26" s="138" t="s">
+      <c r="F26" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="G26" s="138" t="s">
+      <c r="G26" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="H26" s="138" t="s">
+      <c r="H26" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="I26" s="138" t="s">
+      <c r="I26" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="J26" s="139" t="s">
+      <c r="J26" s="67" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="136" t="s">
+      <c r="A27" s="73" t="s">
         <v>243</v>
       </c>
-      <c r="B27" s="134"/>
-      <c r="C27" s="145" t="s">
+      <c r="B27" s="74"/>
+      <c r="C27" s="70" t="s">
         <v>244</v>
       </c>
-      <c r="D27" s="145" t="s">
+      <c r="D27" s="70" t="s">
         <v>245</v>
       </c>
-      <c r="E27" s="145" t="s">
+      <c r="E27" s="70" t="s">
         <v>246</v>
       </c>
-      <c r="F27" s="145" t="s">
+      <c r="F27" s="70" t="s">
         <v>247</v>
       </c>
-      <c r="G27" s="145" t="s">
+      <c r="G27" s="70" t="s">
         <v>248</v>
       </c>
-      <c r="H27" s="145" t="s">
+      <c r="H27" s="70" t="s">
         <v>249</v>
       </c>
-      <c r="I27" s="145" t="s">
+      <c r="I27" s="70" t="s">
         <v>250</v>
       </c>
-      <c r="J27" s="146" t="s">
+      <c r="J27" s="71" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="131" t="s">
+      <c r="A28" s="81" t="s">
         <v>12</v>
       </c>
-      <c r="B28" s="124"/>
-      <c r="C28" s="121" t="s">
+      <c r="B28" s="82"/>
+      <c r="C28" s="61" t="s">
         <v>260</v>
       </c>
-      <c r="D28" s="121" t="s">
+      <c r="D28" s="61" t="s">
         <v>261</v>
       </c>
-      <c r="E28" s="121" t="s">
+      <c r="E28" s="61" t="s">
         <v>262</v>
       </c>
-      <c r="F28" s="121" t="s">
+      <c r="F28" s="61" t="s">
         <v>263</v>
       </c>
-      <c r="G28" s="121" t="s">
+      <c r="G28" s="61" t="s">
         <v>264</v>
       </c>
-      <c r="H28" s="121" t="s">
+      <c r="H28" s="61" t="s">
         <v>265</v>
       </c>
-      <c r="I28" s="121" t="s">
+      <c r="I28" s="61" t="s">
         <v>266</v>
       </c>
-      <c r="J28" s="147" t="s">
+      <c r="J28" s="72" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="131" t="s">
+      <c r="A29" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="B29" s="124"/>
-      <c r="C29" s="121" t="s">
+      <c r="B29" s="82"/>
+      <c r="C29" s="61" t="s">
         <v>252</v>
       </c>
-      <c r="D29" s="121" t="s">
+      <c r="D29" s="61" t="s">
         <v>253</v>
       </c>
-      <c r="E29" s="121" t="s">
+      <c r="E29" s="61" t="s">
         <v>254</v>
       </c>
-      <c r="F29" s="121" t="s">
+      <c r="F29" s="61" t="s">
         <v>255</v>
       </c>
-      <c r="G29" s="121" t="s">
+      <c r="G29" s="61" t="s">
         <v>256</v>
       </c>
-      <c r="H29" s="121" t="s">
+      <c r="H29" s="61" t="s">
         <v>257</v>
       </c>
-      <c r="I29" s="121" t="s">
+      <c r="I29" s="61" t="s">
         <v>258</v>
       </c>
-      <c r="J29" s="147" t="s">
+      <c r="J29" s="72" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="131" t="s">
+      <c r="A30" s="81" t="s">
         <v>14</v>
       </c>
-      <c r="B30" s="124"/>
-      <c r="C30" s="129" t="e">
+      <c r="B30" s="82"/>
+      <c r="C30" s="64" t="e">
         <f>+C28-C29</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D30" s="129" t="e">
+      <c r="D30" s="64" t="e">
         <f t="shared" ref="D30:J30" si="1">+D28-D29</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E30" s="129" t="e">
+      <c r="E30" s="64" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F30" s="129" t="e">
+      <c r="F30" s="64" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="G30" s="129" t="e">
+      <c r="G30" s="64" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H30" s="129" t="e">
+      <c r="H30" s="64" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="I30" s="129" t="e">
+      <c r="I30" s="64" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="J30" s="130" t="e">
+      <c r="J30" s="65" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="131" t="s">
+      <c r="A31" s="81" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="124"/>
-      <c r="C31" s="129" t="e">
+      <c r="B31" s="82"/>
+      <c r="C31" s="64" t="e">
         <f>+C30*2400</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D31" s="129" t="e">
+      <c r="D31" s="64" t="e">
         <f>+D30*2400</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E31" s="129" t="e">
+      <c r="E31" s="64" t="e">
         <f>E30*80</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F31" s="129" t="e">
+      <c r="F31" s="64" t="e">
         <f t="shared" ref="F31:G31" si="2">F30*80</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G31" s="129" t="e">
+      <c r="G31" s="64" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H31" s="129" t="e">
+      <c r="H31" s="64" t="e">
         <f>+H30</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I31" s="129" t="e">
+      <c r="I31" s="64" t="e">
         <f t="shared" ref="I31:J31" si="3">+I30</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J31" s="130" t="e">
+      <c r="J31" s="65" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="131" t="s">
+      <c r="A32" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="B32" s="124"/>
-      <c r="C32" s="129" t="e">
+      <c r="B32" s="82"/>
+      <c r="C32" s="64" t="e">
         <f>(C28-C27)*2400</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D32" s="129" t="e">
+      <c r="D32" s="64" t="e">
         <f>(D28-D27)*2400</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E32" s="129" t="e">
-        <f t="shared" ref="D32:J32" si="4">+E57</f>
+      <c r="E32" s="64" t="e">
+        <f t="shared" ref="E32:J32" si="4">+E57</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F32" s="129" t="e">
+      <c r="F32" s="64" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="G32" s="129" t="e">
+      <c r="G32" s="64" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H32" s="129" t="e">
+      <c r="H32" s="64" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="I32" s="129" t="e">
+      <c r="I32" s="64" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="J32" s="130" t="e">
+      <c r="J32" s="65" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="33" spans="1:17" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="137" t="s">
+      <c r="A33" s="83" t="s">
         <v>17</v>
       </c>
-      <c r="B33" s="127"/>
-      <c r="C33" s="16" t="e">
+      <c r="B33" s="84"/>
+      <c r="C33" s="14" t="e">
         <f>C30/(SQRT(C30^2+D30^2*100))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D33" s="144"/>
-      <c r="E33" s="144"/>
-      <c r="F33" s="144"/>
-      <c r="G33" s="16" t="s">
+      <c r="D33" s="69"/>
+      <c r="E33" s="69"/>
+      <c r="F33" s="69"/>
+      <c r="G33" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="H33" s="32" t="s">
+      <c r="H33" s="30" t="s">
         <v>217</v>
       </c>
-      <c r="I33" s="32" t="s">
+      <c r="I33" s="30" t="s">
         <v>218</v>
       </c>
-      <c r="J33" s="33" t="s">
+      <c r="J33" s="31" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="34" spans="1:17" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="140" t="s">
+      <c r="A34" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="B34" s="141"/>
-      <c r="C34" s="142"/>
-      <c r="D34" s="142"/>
-      <c r="E34" s="142"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="143" t="s">
+      <c r="B34" s="86"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="H34" s="30" t="s">
+      <c r="H34" s="28" t="s">
         <v>268</v>
       </c>
-      <c r="I34" s="30" t="s">
+      <c r="I34" s="28" t="s">
         <v>268</v>
       </c>
-      <c r="J34" s="31" t="s">
+      <c r="J34" s="29" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="18"/>
-      <c r="B35" s="28"/>
-      <c r="C35" s="28"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="28"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="14" t="s">
+      <c r="A35" s="16"/>
+      <c r="B35" s="26"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="H35" s="12" t="s">
+      <c r="H35" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="I35" s="12" t="s">
+      <c r="I35" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="J35" s="15" t="s">
+      <c r="J35" s="13" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="36" spans="1:17" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="20"/>
-      <c r="B36" s="21"/>
-      <c r="C36" s="21"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="22"/>
-      <c r="G36" s="29" t="s">
+      <c r="A36" s="18"/>
+      <c r="B36" s="19"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="H36" s="16" t="e">
+      <c r="H36" s="14" t="e">
         <f>+H34-H35</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I36" s="16" t="e">
+      <c r="I36" s="14" t="e">
         <f t="shared" ref="I36:J36" si="5">+I34-I35</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J36" s="17" t="e">
+      <c r="J36" s="15" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
@@ -3230,302 +3796,302 @@
       <c r="A38" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="B38" s="23"/>
-      <c r="C38" s="23"/>
-      <c r="D38" s="23"/>
-      <c r="E38" s="23"/>
-      <c r="F38" s="23"/>
-      <c r="G38" s="23"/>
-      <c r="H38" s="23"/>
-      <c r="I38" s="23"/>
-      <c r="J38" s="23"/>
+      <c r="B38" s="21"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="21"/>
+      <c r="I38" s="21"/>
+      <c r="J38" s="21"/>
     </row>
     <row r="39" spans="1:17" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="86" t="s">
+      <c r="A39" s="95" t="s">
         <v>227</v>
       </c>
-      <c r="B39" s="87"/>
-      <c r="C39" s="87"/>
-      <c r="D39" s="87"/>
-      <c r="E39" s="27" t="s">
+      <c r="B39" s="96"/>
+      <c r="C39" s="96"/>
+      <c r="D39" s="96"/>
+      <c r="E39" s="25" t="s">
         <v>228</v>
       </c>
-      <c r="F39" s="87" t="s">
+      <c r="F39" s="96" t="s">
         <v>229</v>
       </c>
-      <c r="G39" s="87"/>
-      <c r="H39" s="88"/>
-      <c r="I39" s="89" t="s">
+      <c r="G39" s="96"/>
+      <c r="H39" s="97"/>
+      <c r="I39" s="98" t="s">
         <v>230</v>
       </c>
-      <c r="J39" s="90"/>
+      <c r="J39" s="99"/>
       <c r="Q39" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="91" t="s">
+      <c r="A40" s="100" t="s">
         <v>231</v>
       </c>
-      <c r="B40" s="92"/>
-      <c r="C40" s="92"/>
-      <c r="D40" s="92"/>
-      <c r="E40" s="26" t="s">
+      <c r="B40" s="101"/>
+      <c r="C40" s="101"/>
+      <c r="D40" s="101"/>
+      <c r="E40" s="24" t="s">
         <v>232</v>
       </c>
-      <c r="F40" s="92"/>
-      <c r="G40" s="92"/>
-      <c r="H40" s="93"/>
-      <c r="I40" s="94"/>
-      <c r="J40" s="95"/>
+      <c r="F40" s="101"/>
+      <c r="G40" s="101"/>
+      <c r="H40" s="102"/>
+      <c r="I40" s="103"/>
+      <c r="J40" s="104"/>
     </row>
     <row r="41" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="100" t="s">
+      <c r="A41" s="75" t="s">
         <v>233</v>
       </c>
-      <c r="B41" s="101"/>
-      <c r="C41" s="101"/>
-      <c r="D41" s="101"/>
-      <c r="E41" s="24" t="s">
+      <c r="B41" s="76"/>
+      <c r="C41" s="76"/>
+      <c r="D41" s="76"/>
+      <c r="E41" s="22" t="s">
         <v>232</v>
       </c>
-      <c r="F41" s="101"/>
-      <c r="G41" s="101"/>
-      <c r="H41" s="102"/>
-      <c r="I41" s="96"/>
-      <c r="J41" s="97"/>
+      <c r="F41" s="76"/>
+      <c r="G41" s="76"/>
+      <c r="H41" s="77"/>
+      <c r="I41" s="105"/>
+      <c r="J41" s="106"/>
     </row>
     <row r="42" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="100" t="s">
+      <c r="A42" s="75" t="s">
         <v>234</v>
       </c>
-      <c r="B42" s="101"/>
-      <c r="C42" s="101"/>
-      <c r="D42" s="101"/>
-      <c r="E42" s="24" t="s">
+      <c r="B42" s="76"/>
+      <c r="C42" s="76"/>
+      <c r="D42" s="76"/>
+      <c r="E42" s="22" t="s">
         <v>232</v>
       </c>
-      <c r="F42" s="101"/>
-      <c r="G42" s="101"/>
-      <c r="H42" s="102"/>
-      <c r="I42" s="96"/>
-      <c r="J42" s="97"/>
+      <c r="F42" s="76"/>
+      <c r="G42" s="76"/>
+      <c r="H42" s="77"/>
+      <c r="I42" s="105"/>
+      <c r="J42" s="106"/>
     </row>
     <row r="43" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="100" t="s">
+      <c r="A43" s="75" t="s">
         <v>235</v>
       </c>
-      <c r="B43" s="101"/>
-      <c r="C43" s="101"/>
-      <c r="D43" s="101"/>
-      <c r="E43" s="24" t="s">
+      <c r="B43" s="76"/>
+      <c r="C43" s="76"/>
+      <c r="D43" s="76"/>
+      <c r="E43" s="22" t="s">
         <v>232</v>
       </c>
-      <c r="F43" s="101"/>
-      <c r="G43" s="101"/>
-      <c r="H43" s="102"/>
-      <c r="I43" s="96"/>
-      <c r="J43" s="97"/>
+      <c r="F43" s="76"/>
+      <c r="G43" s="76"/>
+      <c r="H43" s="77"/>
+      <c r="I43" s="105"/>
+      <c r="J43" s="106"/>
     </row>
     <row r="44" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="100" t="s">
+      <c r="A44" s="75" t="s">
         <v>236</v>
       </c>
-      <c r="B44" s="101"/>
-      <c r="C44" s="101"/>
-      <c r="D44" s="101"/>
-      <c r="E44" s="24" t="s">
+      <c r="B44" s="76"/>
+      <c r="C44" s="76"/>
+      <c r="D44" s="76"/>
+      <c r="E44" s="22" t="s">
         <v>232</v>
       </c>
-      <c r="F44" s="101"/>
-      <c r="G44" s="101"/>
-      <c r="H44" s="102"/>
-      <c r="I44" s="96"/>
-      <c r="J44" s="97"/>
+      <c r="F44" s="76"/>
+      <c r="G44" s="76"/>
+      <c r="H44" s="77"/>
+      <c r="I44" s="105"/>
+      <c r="J44" s="106"/>
     </row>
     <row r="45" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="100" t="s">
+      <c r="A45" s="75" t="s">
         <v>237</v>
       </c>
-      <c r="B45" s="101"/>
-      <c r="C45" s="101"/>
-      <c r="D45" s="101"/>
-      <c r="E45" s="24" t="s">
+      <c r="B45" s="76"/>
+      <c r="C45" s="76"/>
+      <c r="D45" s="76"/>
+      <c r="E45" s="22" t="s">
         <v>232</v>
       </c>
-      <c r="F45" s="101"/>
-      <c r="G45" s="101"/>
-      <c r="H45" s="102"/>
-      <c r="I45" s="96"/>
-      <c r="J45" s="97"/>
+      <c r="F45" s="76"/>
+      <c r="G45" s="76"/>
+      <c r="H45" s="77"/>
+      <c r="I45" s="105"/>
+      <c r="J45" s="106"/>
     </row>
     <row r="46" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="100" t="s">
+      <c r="A46" s="75" t="s">
         <v>238</v>
       </c>
-      <c r="B46" s="101"/>
-      <c r="C46" s="101"/>
-      <c r="D46" s="101"/>
-      <c r="E46" s="24" t="s">
+      <c r="B46" s="76"/>
+      <c r="C46" s="76"/>
+      <c r="D46" s="76"/>
+      <c r="E46" s="22" t="s">
         <v>232</v>
       </c>
-      <c r="F46" s="101"/>
-      <c r="G46" s="101"/>
-      <c r="H46" s="102"/>
-      <c r="I46" s="96"/>
-      <c r="J46" s="97"/>
+      <c r="F46" s="76"/>
+      <c r="G46" s="76"/>
+      <c r="H46" s="77"/>
+      <c r="I46" s="105"/>
+      <c r="J46" s="106"/>
     </row>
     <row r="47" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="100" t="s">
+      <c r="A47" s="75" t="s">
         <v>239</v>
       </c>
-      <c r="B47" s="101"/>
-      <c r="C47" s="101"/>
-      <c r="D47" s="101"/>
-      <c r="E47" s="24" t="s">
+      <c r="B47" s="76"/>
+      <c r="C47" s="76"/>
+      <c r="D47" s="76"/>
+      <c r="E47" s="22" t="s">
         <v>232</v>
       </c>
-      <c r="F47" s="101"/>
-      <c r="G47" s="101"/>
-      <c r="H47" s="102"/>
-      <c r="I47" s="96"/>
-      <c r="J47" s="97"/>
+      <c r="F47" s="76"/>
+      <c r="G47" s="76"/>
+      <c r="H47" s="77"/>
+      <c r="I47" s="105"/>
+      <c r="J47" s="106"/>
     </row>
     <row r="48" spans="1:17" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="104" t="s">
+      <c r="A48" s="78" t="s">
         <v>240</v>
       </c>
-      <c r="B48" s="105"/>
-      <c r="C48" s="105"/>
-      <c r="D48" s="105"/>
-      <c r="E48" s="25" t="s">
+      <c r="B48" s="79"/>
+      <c r="C48" s="79"/>
+      <c r="D48" s="79"/>
+      <c r="E48" s="23" t="s">
         <v>232</v>
       </c>
-      <c r="F48" s="105"/>
-      <c r="G48" s="105"/>
-      <c r="H48" s="106"/>
-      <c r="I48" s="98"/>
-      <c r="J48" s="99"/>
+      <c r="F48" s="79"/>
+      <c r="G48" s="79"/>
+      <c r="H48" s="80"/>
+      <c r="I48" s="107"/>
+      <c r="J48" s="108"/>
     </row>
     <row r="52" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="53" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="63"/>
-      <c r="B53" s="64"/>
-      <c r="C53" s="63" t="s">
+      <c r="A53" s="92"/>
+      <c r="B53" s="93"/>
+      <c r="C53" s="92" t="s">
         <v>24</v>
       </c>
-      <c r="D53" s="64"/>
-      <c r="E53" s="63" t="s">
+      <c r="D53" s="93"/>
+      <c r="E53" s="92" t="s">
         <v>2</v>
       </c>
-      <c r="F53" s="85"/>
-      <c r="G53" s="64"/>
-      <c r="H53" s="63" t="s">
+      <c r="F53" s="94"/>
+      <c r="G53" s="93"/>
+      <c r="H53" s="92" t="s">
         <v>3</v>
       </c>
-      <c r="I53" s="85"/>
-      <c r="J53" s="64"/>
+      <c r="I53" s="94"/>
+      <c r="J53" s="93"/>
     </row>
     <row r="54" spans="1:10" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="65"/>
-      <c r="B54" s="66"/>
-      <c r="C54" s="57" t="s">
+      <c r="A54" s="124"/>
+      <c r="B54" s="125"/>
+      <c r="C54" s="55" t="s">
         <v>220</v>
       </c>
-      <c r="D54" s="56" t="s">
+      <c r="D54" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="E54" s="57" t="s">
+      <c r="E54" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="F54" s="55" t="s">
+      <c r="F54" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="G54" s="56" t="s">
+      <c r="G54" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="H54" s="57" t="s">
+      <c r="H54" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="I54" s="55" t="s">
+      <c r="I54" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="J54" s="56" t="s">
+      <c r="J54" s="54" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="67" t="s">
+      <c r="A55" s="126" t="s">
         <v>20</v>
       </c>
-      <c r="B55" s="68"/>
-      <c r="C55" s="58" t="str">
+      <c r="B55" s="127"/>
+      <c r="C55" s="56" t="str">
         <f>+C28</f>
         <v>금일("main_active")</v>
       </c>
-      <c r="D55" s="59">
+      <c r="D55" s="57">
         <v>0</v>
       </c>
-      <c r="E55" s="58" t="str">
+      <c r="E55" s="56" t="str">
         <f t="shared" ref="E55:J55" si="6">+E28</f>
         <v>금일("ind_mid")</v>
       </c>
-      <c r="F55" s="54" t="str">
+      <c r="F55" s="52" t="str">
         <f t="shared" si="6"/>
         <v>금일("ind_max")</v>
       </c>
-      <c r="G55" s="59" t="str">
+      <c r="G55" s="57" t="str">
         <f t="shared" si="6"/>
         <v>금일("ind_light")</v>
       </c>
-      <c r="H55" s="58" t="str">
+      <c r="H55" s="56" t="str">
         <f t="shared" si="6"/>
         <v>금일("street_mid")</v>
       </c>
-      <c r="I55" s="54" t="str">
+      <c r="I55" s="52" t="str">
         <f t="shared" si="6"/>
         <v>금일("street_max")</v>
       </c>
-      <c r="J55" s="59" t="str">
+      <c r="J55" s="57" t="str">
         <f t="shared" si="6"/>
         <v>금일("street_light")</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="69" t="s">
+      <c r="A56" s="128" t="s">
         <v>25</v>
       </c>
-      <c r="B56" s="70"/>
-      <c r="C56" s="60">
+      <c r="B56" s="129"/>
+      <c r="C56" s="58">
         <v>1309.8499999999999</v>
       </c>
-      <c r="D56" s="61">
+      <c r="D56" s="59">
         <v>0</v>
       </c>
-      <c r="E56" s="60">
+      <c r="E56" s="58">
         <v>7014.1</v>
       </c>
-      <c r="F56" s="62">
+      <c r="F56" s="60">
         <v>3563.95</v>
       </c>
-      <c r="G56" s="61">
+      <c r="G56" s="59">
         <v>9804.3799999999992</v>
       </c>
-      <c r="H56" s="60">
+      <c r="H56" s="58">
         <v>10305</v>
       </c>
-      <c r="I56" s="62">
+      <c r="I56" s="60">
         <v>1638</v>
       </c>
-      <c r="J56" s="61">
+      <c r="J56" s="59">
         <v>33594</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="65" t="s">
+      <c r="A57" s="124" t="s">
         <v>16</v>
       </c>
-      <c r="B57" s="66"/>
+      <c r="B57" s="125"/>
       <c r="C57" s="7" t="e">
         <f>(+C55-C56)*2400</f>
         <v>#VALUE!</v>
@@ -3559,60 +4125,20 @@
       </c>
     </row>
     <row r="58" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="71" t="s">
+      <c r="A58" s="130" t="s">
         <v>26</v>
       </c>
-      <c r="B58" s="71"/>
+      <c r="B58" s="130"/>
       <c r="C58">
         <v>100</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="A47:D47"/>
-    <mergeCell ref="F47:H47"/>
-    <mergeCell ref="A48:D48"/>
-    <mergeCell ref="F48:H48"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="F44:H44"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="F45:H45"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A25:B26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:G25"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="E53:G53"/>
-    <mergeCell ref="H53:J53"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="I40:J48"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A58:B58"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A5:B6"/>
     <mergeCell ref="C22:D22"/>
@@ -3629,16 +4155,93 @@
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A13:A15"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="E53:G53"/>
+    <mergeCell ref="H53:J53"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="I40:J48"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="A43:D43"/>
     <mergeCell ref="A53:B54"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A25:B26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="A48:D48"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="F44:H44"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="F45:H45"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A31:B31"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="E18 G18 I18">
+    <cfRule type="cellIs" dxfId="0" priority="7" operator="greaterThan">
+      <formula>0.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="10" operator="greaterThan">
+      <formula>0.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="11" operator="lessThanOrEqual">
+      <formula>0.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThanOrEqual">
+      <formula>0.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="lessThan">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E17 G17 I17">
+    <cfRule type="cellIs" dxfId="20" priority="5" operator="greaterThan">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="19" priority="6" operator="greaterThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="18" priority="8" operator="lessThan">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="17" priority="9" operator="greaterThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="4" operator="greaterThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="15" priority="3" operator="lessThan">
+      <formula>60</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="50" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="48" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3661,222 +4264,222 @@
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A4" s="113" t="s">
+      <c r="A4" s="137" t="s">
         <v>146</v>
       </c>
-      <c r="B4" s="117" t="s">
+      <c r="B4" s="141" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="119" t="s">
+      <c r="C4" s="143" t="s">
         <v>147</v>
       </c>
-      <c r="D4" s="115" t="s">
+      <c r="D4" s="139" t="s">
         <v>148</v>
       </c>
-      <c r="E4" s="116"/>
-      <c r="F4" s="107" t="s">
+      <c r="E4" s="140"/>
+      <c r="F4" s="131" t="s">
         <v>149</v>
       </c>
-      <c r="G4" s="108"/>
-      <c r="H4" s="108"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="108"/>
-      <c r="K4" s="108"/>
-      <c r="L4" s="108"/>
-      <c r="M4" s="108"/>
-      <c r="N4" s="108"/>
-      <c r="O4" s="108"/>
-      <c r="P4" s="108"/>
-      <c r="Q4" s="109"/>
-      <c r="R4" s="110" t="s">
+      <c r="G4" s="132"/>
+      <c r="H4" s="132"/>
+      <c r="I4" s="132"/>
+      <c r="J4" s="132"/>
+      <c r="K4" s="132"/>
+      <c r="L4" s="132"/>
+      <c r="M4" s="132"/>
+      <c r="N4" s="132"/>
+      <c r="O4" s="132"/>
+      <c r="P4" s="132"/>
+      <c r="Q4" s="133"/>
+      <c r="R4" s="134" t="s">
         <v>150</v>
       </c>
-      <c r="S4" s="108"/>
-      <c r="T4" s="108"/>
-      <c r="U4" s="108"/>
-      <c r="V4" s="108"/>
-      <c r="W4" s="108"/>
-      <c r="X4" s="108"/>
-      <c r="Y4" s="108"/>
-      <c r="Z4" s="108"/>
-      <c r="AA4" s="108"/>
-      <c r="AB4" s="109"/>
+      <c r="S4" s="132"/>
+      <c r="T4" s="132"/>
+      <c r="U4" s="132"/>
+      <c r="V4" s="132"/>
+      <c r="W4" s="132"/>
+      <c r="X4" s="132"/>
+      <c r="Y4" s="132"/>
+      <c r="Z4" s="132"/>
+      <c r="AA4" s="132"/>
+      <c r="AB4" s="133"/>
     </row>
     <row r="5" spans="1:28" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="114"/>
-      <c r="B5" s="118"/>
-      <c r="C5" s="120"/>
-      <c r="D5" s="50" t="s">
+      <c r="A5" s="138"/>
+      <c r="B5" s="142"/>
+      <c r="C5" s="144"/>
+      <c r="D5" s="48" t="s">
         <v>151</v>
       </c>
-      <c r="E5" s="51" t="s">
+      <c r="E5" s="49" t="s">
         <v>152</v>
       </c>
-      <c r="F5" s="50" t="s">
+      <c r="F5" s="48" t="s">
         <v>153</v>
       </c>
-      <c r="G5" s="53" t="s">
+      <c r="G5" s="51" t="s">
         <v>154</v>
       </c>
-      <c r="H5" s="53" t="s">
+      <c r="H5" s="51" t="s">
         <v>155</v>
       </c>
-      <c r="I5" s="53" t="s">
+      <c r="I5" s="51" t="s">
         <v>156</v>
       </c>
-      <c r="J5" s="53" t="s">
+      <c r="J5" s="51" t="s">
         <v>157</v>
       </c>
-      <c r="K5" s="53" t="s">
+      <c r="K5" s="51" t="s">
         <v>158</v>
       </c>
-      <c r="L5" s="53" t="s">
+      <c r="L5" s="51" t="s">
         <v>159</v>
       </c>
-      <c r="M5" s="53" t="s">
+      <c r="M5" s="51" t="s">
         <v>160</v>
       </c>
-      <c r="N5" s="53" t="s">
+      <c r="N5" s="51" t="s">
         <v>161</v>
       </c>
-      <c r="O5" s="53" t="s">
+      <c r="O5" s="51" t="s">
         <v>162</v>
       </c>
-      <c r="P5" s="53" t="s">
+      <c r="P5" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="Q5" s="51" t="s">
+      <c r="Q5" s="49" t="s">
         <v>164</v>
       </c>
-      <c r="R5" s="52" t="s">
+      <c r="R5" s="50" t="s">
         <v>153</v>
       </c>
-      <c r="S5" s="53" t="s">
+      <c r="S5" s="51" t="s">
         <v>154</v>
       </c>
-      <c r="T5" s="53" t="s">
+      <c r="T5" s="51" t="s">
         <v>155</v>
       </c>
-      <c r="U5" s="53" t="s">
+      <c r="U5" s="51" t="s">
         <v>156</v>
       </c>
-      <c r="V5" s="53" t="s">
+      <c r="V5" s="51" t="s">
         <v>157</v>
       </c>
-      <c r="W5" s="53" t="s">
+      <c r="W5" s="51" t="s">
         <v>158</v>
       </c>
-      <c r="X5" s="53" t="s">
+      <c r="X5" s="51" t="s">
         <v>159</v>
       </c>
-      <c r="Y5" s="53" t="s">
+      <c r="Y5" s="51" t="s">
         <v>160</v>
       </c>
-      <c r="Z5" s="53" t="s">
+      <c r="Z5" s="51" t="s">
         <v>161</v>
       </c>
-      <c r="AA5" s="53" t="s">
+      <c r="AA5" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="AB5" s="51" t="s">
+      <c r="AB5" s="49" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A6" s="45">
+      <c r="A6" s="43">
         <v>0</v>
       </c>
-      <c r="B6" s="46" t="s">
+      <c r="B6" s="44" t="s">
         <v>166</v>
       </c>
-      <c r="C6" s="47" t="s">
+      <c r="C6" s="45" t="s">
         <v>167</v>
       </c>
-      <c r="D6" s="46" t="s">
+      <c r="D6" s="44" t="s">
         <v>97</v>
       </c>
-      <c r="E6" s="47" t="s">
+      <c r="E6" s="45" t="s">
         <v>98</v>
       </c>
-      <c r="F6" s="46" t="s">
+      <c r="F6" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="G6" s="49" t="s">
+      <c r="G6" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="H6" s="49" t="s">
+      <c r="H6" s="47" t="s">
         <v>101</v>
       </c>
-      <c r="I6" s="49" t="s">
+      <c r="I6" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="J6" s="49" t="s">
+      <c r="J6" s="47" t="s">
         <v>103</v>
       </c>
-      <c r="K6" s="49" t="s">
+      <c r="K6" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="L6" s="49" t="s">
+      <c r="L6" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="M6" s="49" t="s">
+      <c r="M6" s="47" t="s">
         <v>106</v>
       </c>
-      <c r="N6" s="49" t="s">
+      <c r="N6" s="47" t="s">
         <v>107</v>
       </c>
-      <c r="O6" s="49" t="s">
+      <c r="O6" s="47" t="s">
         <v>108</v>
       </c>
-      <c r="P6" s="49" t="s">
+      <c r="P6" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="Q6" s="47" t="s">
+      <c r="Q6" s="45" t="s">
         <v>110</v>
       </c>
-      <c r="R6" s="48" t="s">
+      <c r="R6" s="46" t="s">
         <v>111</v>
       </c>
-      <c r="S6" s="49" t="s">
+      <c r="S6" s="47" t="s">
         <v>112</v>
       </c>
-      <c r="T6" s="49" t="s">
+      <c r="T6" s="47" t="s">
         <v>113</v>
       </c>
-      <c r="U6" s="49" t="s">
+      <c r="U6" s="47" t="s">
         <v>114</v>
       </c>
-      <c r="V6" s="49" t="s">
+      <c r="V6" s="47" t="s">
         <v>115</v>
       </c>
-      <c r="W6" s="49" t="s">
+      <c r="W6" s="47" t="s">
         <v>116</v>
       </c>
-      <c r="X6" s="49" t="s">
+      <c r="X6" s="47" t="s">
         <v>117</v>
       </c>
-      <c r="Y6" s="49" t="s">
+      <c r="Y6" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="Z6" s="49" t="s">
+      <c r="Z6" s="47" t="s">
         <v>119</v>
       </c>
-      <c r="AA6" s="49" t="s">
+      <c r="AA6" s="47" t="s">
         <v>120</v>
       </c>
-      <c r="AB6" s="49" t="s">
+      <c r="AB6" s="47" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A7" s="43">
+      <c r="A7" s="41">
         <v>1</v>
       </c>
-      <c r="B7" s="41"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="41"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="39"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -3887,8 +4490,8 @@
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
-      <c r="Q7" s="42"/>
-      <c r="R7" s="37"/>
+      <c r="Q7" s="40"/>
+      <c r="R7" s="35"/>
       <c r="S7" s="1"/>
       <c r="T7" s="1"/>
       <c r="U7" s="1"/>
@@ -3901,14 +4504,14 @@
       <c r="AB7" s="1"/>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A8" s="43">
+      <c r="A8" s="41">
         <v>2</v>
       </c>
-      <c r="B8" s="41"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="41"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="39"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -3919,8 +4522,8 @@
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
-      <c r="Q8" s="42"/>
-      <c r="R8" s="37"/>
+      <c r="Q8" s="40"/>
+      <c r="R8" s="35"/>
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
       <c r="U8" s="1"/>
@@ -3933,14 +4536,14 @@
       <c r="AB8" s="1"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A9" s="43">
+      <c r="A9" s="41">
         <v>3</v>
       </c>
-      <c r="B9" s="41"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="41"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="39"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -3951,8 +4554,8 @@
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
-      <c r="Q9" s="42"/>
-      <c r="R9" s="37"/>
+      <c r="Q9" s="40"/>
+      <c r="R9" s="35"/>
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
       <c r="U9" s="1"/>
@@ -3965,14 +4568,14 @@
       <c r="AB9" s="1"/>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A10" s="43">
+      <c r="A10" s="41">
         <v>4</v>
       </c>
-      <c r="B10" s="41"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="41"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="39"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -3983,8 +4586,8 @@
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
-      <c r="Q10" s="42"/>
-      <c r="R10" s="37"/>
+      <c r="Q10" s="40"/>
+      <c r="R10" s="35"/>
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
       <c r="U10" s="1"/>
@@ -3997,14 +4600,14 @@
       <c r="AB10" s="1"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A11" s="43">
+      <c r="A11" s="41">
         <v>5</v>
       </c>
-      <c r="B11" s="41"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="41"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="39"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -4015,8 +4618,8 @@
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
-      <c r="Q11" s="42"/>
-      <c r="R11" s="37"/>
+      <c r="Q11" s="40"/>
+      <c r="R11" s="35"/>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
       <c r="U11" s="1"/>
@@ -4029,14 +4632,14 @@
       <c r="AB11" s="1"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A12" s="43">
+      <c r="A12" s="41">
         <v>6</v>
       </c>
-      <c r="B12" s="41"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="41"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="39"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -4047,8 +4650,8 @@
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
-      <c r="Q12" s="42"/>
-      <c r="R12" s="37"/>
+      <c r="Q12" s="40"/>
+      <c r="R12" s="35"/>
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
       <c r="U12" s="1"/>
@@ -4061,14 +4664,14 @@
       <c r="AB12" s="1"/>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A13" s="43">
+      <c r="A13" s="41">
         <v>7</v>
       </c>
-      <c r="B13" s="41"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="41"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="39"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -4079,8 +4682,8 @@
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
-      <c r="Q13" s="42"/>
-      <c r="R13" s="37"/>
+      <c r="Q13" s="40"/>
+      <c r="R13" s="35"/>
       <c r="S13" s="1"/>
       <c r="T13" s="1"/>
       <c r="U13" s="1"/>
@@ -4093,14 +4696,14 @@
       <c r="AB13" s="1"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A14" s="43">
+      <c r="A14" s="41">
         <v>8</v>
       </c>
-      <c r="B14" s="41"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="41"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="39"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -4111,8 +4714,8 @@
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
-      <c r="Q14" s="42"/>
-      <c r="R14" s="37"/>
+      <c r="Q14" s="40"/>
+      <c r="R14" s="35"/>
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
       <c r="U14" s="1"/>
@@ -4125,14 +4728,14 @@
       <c r="AB14" s="1"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A15" s="43">
+      <c r="A15" s="41">
         <v>9</v>
       </c>
-      <c r="B15" s="41"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="41"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="39"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -4143,8 +4746,8 @@
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
-      <c r="Q15" s="42"/>
-      <c r="R15" s="37"/>
+      <c r="Q15" s="40"/>
+      <c r="R15" s="35"/>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
       <c r="U15" s="1"/>
@@ -4157,14 +4760,14 @@
       <c r="AB15" s="1"/>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A16" s="43">
+      <c r="A16" s="41">
         <v>10</v>
       </c>
-      <c r="B16" s="41"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="41"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="39"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -4175,8 +4778,8 @@
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
-      <c r="Q16" s="42"/>
-      <c r="R16" s="37"/>
+      <c r="Q16" s="40"/>
+      <c r="R16" s="35"/>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
       <c r="U16" s="1"/>
@@ -4189,14 +4792,14 @@
       <c r="AB16" s="1"/>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A17" s="43">
+      <c r="A17" s="41">
         <v>11</v>
       </c>
-      <c r="B17" s="41"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="41"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="41"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="39"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -4207,8 +4810,8 @@
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
-      <c r="Q17" s="42"/>
-      <c r="R17" s="37"/>
+      <c r="Q17" s="40"/>
+      <c r="R17" s="35"/>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
       <c r="U17" s="1"/>
@@ -4221,14 +4824,14 @@
       <c r="AB17" s="1"/>
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A18" s="43">
+      <c r="A18" s="41">
         <v>12</v>
       </c>
-      <c r="B18" s="41"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="41"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="39"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -4239,8 +4842,8 @@
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
-      <c r="Q18" s="42"/>
-      <c r="R18" s="37"/>
+      <c r="Q18" s="40"/>
+      <c r="R18" s="35"/>
       <c r="S18" s="1"/>
       <c r="T18" s="1"/>
       <c r="U18" s="1"/>
@@ -4253,14 +4856,14 @@
       <c r="AB18" s="1"/>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A19" s="43">
+      <c r="A19" s="41">
         <v>13</v>
       </c>
-      <c r="B19" s="41"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="41"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="39"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -4271,8 +4874,8 @@
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
-      <c r="Q19" s="42"/>
-      <c r="R19" s="37"/>
+      <c r="Q19" s="40"/>
+      <c r="R19" s="35"/>
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
       <c r="U19" s="1"/>
@@ -4285,14 +4888,14 @@
       <c r="AB19" s="1"/>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A20" s="43">
+      <c r="A20" s="41">
         <v>14</v>
       </c>
-      <c r="B20" s="41"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="41"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="41"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="39"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -4303,8 +4906,8 @@
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
-      <c r="Q20" s="42"/>
-      <c r="R20" s="37"/>
+      <c r="Q20" s="40"/>
+      <c r="R20" s="35"/>
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
       <c r="U20" s="1"/>
@@ -4317,14 +4920,14 @@
       <c r="AB20" s="1"/>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A21" s="43">
+      <c r="A21" s="41">
         <v>15</v>
       </c>
-      <c r="B21" s="41"/>
-      <c r="C21" s="42"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="42"/>
-      <c r="F21" s="41"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="39"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -4335,8 +4938,8 @@
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
-      <c r="Q21" s="42"/>
-      <c r="R21" s="37"/>
+      <c r="Q21" s="40"/>
+      <c r="R21" s="35"/>
       <c r="S21" s="1"/>
       <c r="T21" s="1"/>
       <c r="U21" s="1"/>
@@ -4349,14 +4952,14 @@
       <c r="AB21" s="1"/>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A22" s="43">
+      <c r="A22" s="41">
         <v>16</v>
       </c>
-      <c r="B22" s="41"/>
-      <c r="C22" s="42"/>
-      <c r="D22" s="41"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="41"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="40"/>
+      <c r="F22" s="39"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -4367,8 +4970,8 @@
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
-      <c r="Q22" s="42"/>
-      <c r="R22" s="37"/>
+      <c r="Q22" s="40"/>
+      <c r="R22" s="35"/>
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
       <c r="U22" s="1"/>
@@ -4381,14 +4984,14 @@
       <c r="AB22" s="1"/>
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A23" s="43">
+      <c r="A23" s="41">
         <v>17</v>
       </c>
-      <c r="B23" s="41"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="41"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="40"/>
+      <c r="F23" s="39"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -4399,8 +5002,8 @@
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
-      <c r="Q23" s="42"/>
-      <c r="R23" s="37"/>
+      <c r="Q23" s="40"/>
+      <c r="R23" s="35"/>
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
       <c r="U23" s="1"/>
@@ -4413,14 +5016,14 @@
       <c r="AB23" s="1"/>
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A24" s="43">
+      <c r="A24" s="41">
         <v>18</v>
       </c>
-      <c r="B24" s="41"/>
-      <c r="C24" s="42"/>
-      <c r="D24" s="41"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="41"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="39"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -4431,8 +5034,8 @@
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
-      <c r="Q24" s="42"/>
-      <c r="R24" s="37"/>
+      <c r="Q24" s="40"/>
+      <c r="R24" s="35"/>
       <c r="S24" s="1"/>
       <c r="T24" s="1"/>
       <c r="U24" s="1"/>
@@ -4445,14 +5048,14 @@
       <c r="AB24" s="1"/>
     </row>
     <row r="25" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A25" s="43">
+      <c r="A25" s="41">
         <v>19</v>
       </c>
-      <c r="B25" s="41"/>
-      <c r="C25" s="42"/>
-      <c r="D25" s="41"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="41"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="40"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="39"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
@@ -4463,8 +5066,8 @@
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
-      <c r="Q25" s="42"/>
-      <c r="R25" s="37"/>
+      <c r="Q25" s="40"/>
+      <c r="R25" s="35"/>
       <c r="S25" s="1"/>
       <c r="T25" s="1"/>
       <c r="U25" s="1"/>
@@ -4477,14 +5080,14 @@
       <c r="AB25" s="1"/>
     </row>
     <row r="26" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A26" s="43">
+      <c r="A26" s="41">
         <v>20</v>
       </c>
-      <c r="B26" s="41"/>
-      <c r="C26" s="42"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="42"/>
-      <c r="F26" s="41"/>
+      <c r="B26" s="39"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="39"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -4495,8 +5098,8 @@
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
-      <c r="Q26" s="42"/>
-      <c r="R26" s="37"/>
+      <c r="Q26" s="40"/>
+      <c r="R26" s="35"/>
       <c r="S26" s="1"/>
       <c r="T26" s="1"/>
       <c r="U26" s="1"/>
@@ -4509,14 +5112,14 @@
       <c r="AB26" s="1"/>
     </row>
     <row r="27" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A27" s="43">
+      <c r="A27" s="41">
         <v>21</v>
       </c>
-      <c r="B27" s="41"/>
-      <c r="C27" s="42"/>
-      <c r="D27" s="41"/>
-      <c r="E27" s="42"/>
-      <c r="F27" s="41"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="39"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -4527,8 +5130,8 @@
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
-      <c r="Q27" s="42"/>
-      <c r="R27" s="37"/>
+      <c r="Q27" s="40"/>
+      <c r="R27" s="35"/>
       <c r="S27" s="1"/>
       <c r="T27" s="1"/>
       <c r="U27" s="1"/>
@@ -4541,14 +5144,14 @@
       <c r="AB27" s="1"/>
     </row>
     <row r="28" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A28" s="43">
+      <c r="A28" s="41">
         <v>22</v>
       </c>
-      <c r="B28" s="41"/>
-      <c r="C28" s="42"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="42"/>
-      <c r="F28" s="41"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="40"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="40"/>
+      <c r="F28" s="39"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -4559,8 +5162,8 @@
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
-      <c r="Q28" s="42"/>
-      <c r="R28" s="37"/>
+      <c r="Q28" s="40"/>
+      <c r="R28" s="35"/>
       <c r="S28" s="1"/>
       <c r="T28" s="1"/>
       <c r="U28" s="1"/>
@@ -4573,7 +5176,7 @@
       <c r="AB28" s="1"/>
     </row>
     <row r="29" spans="1:28" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="44">
+      <c r="A29" s="42">
         <v>23</v>
       </c>
       <c r="B29" s="7"/>
@@ -4592,7 +5195,7 @@
       <c r="O29" s="8"/>
       <c r="P29" s="8"/>
       <c r="Q29" s="9"/>
-      <c r="R29" s="37"/>
+      <c r="R29" s="35"/>
       <c r="S29" s="1"/>
       <c r="T29" s="1"/>
       <c r="U29" s="1"/>
@@ -4606,173 +5209,173 @@
     </row>
     <row r="31" spans="1:28" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="32" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A32" s="111" t="s">
+      <c r="A32" s="135" t="s">
         <v>146</v>
       </c>
-      <c r="B32" s="63" t="s">
+      <c r="B32" s="92" t="s">
         <v>168</v>
       </c>
-      <c r="C32" s="85"/>
-      <c r="D32" s="85"/>
-      <c r="E32" s="85"/>
-      <c r="F32" s="85"/>
-      <c r="G32" s="85"/>
-      <c r="H32" s="85"/>
-      <c r="I32" s="85"/>
-      <c r="J32" s="85"/>
-      <c r="K32" s="85"/>
-      <c r="L32" s="64"/>
-      <c r="M32" s="63" t="s">
+      <c r="C32" s="94"/>
+      <c r="D32" s="94"/>
+      <c r="E32" s="94"/>
+      <c r="F32" s="94"/>
+      <c r="G32" s="94"/>
+      <c r="H32" s="94"/>
+      <c r="I32" s="94"/>
+      <c r="J32" s="94"/>
+      <c r="K32" s="94"/>
+      <c r="L32" s="93"/>
+      <c r="M32" s="92" t="s">
         <v>169</v>
       </c>
-      <c r="N32" s="85"/>
-      <c r="O32" s="85"/>
-      <c r="P32" s="85"/>
-      <c r="Q32" s="85"/>
-      <c r="R32" s="85"/>
-      <c r="S32" s="85"/>
-      <c r="T32" s="85"/>
-      <c r="U32" s="85"/>
-      <c r="V32" s="85"/>
-      <c r="W32" s="64"/>
+      <c r="N32" s="94"/>
+      <c r="O32" s="94"/>
+      <c r="P32" s="94"/>
+      <c r="Q32" s="94"/>
+      <c r="R32" s="94"/>
+      <c r="S32" s="94"/>
+      <c r="T32" s="94"/>
+      <c r="U32" s="94"/>
+      <c r="V32" s="94"/>
+      <c r="W32" s="93"/>
     </row>
     <row r="33" spans="1:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="112"/>
-      <c r="B33" s="38" t="s">
+      <c r="A33" s="136"/>
+      <c r="B33" s="36" t="s">
         <v>153</v>
       </c>
-      <c r="C33" s="35" t="s">
+      <c r="C33" s="33" t="s">
         <v>154</v>
       </c>
-      <c r="D33" s="35" t="s">
+      <c r="D33" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="E33" s="35" t="s">
+      <c r="E33" s="33" t="s">
         <v>156</v>
       </c>
-      <c r="F33" s="35" t="s">
+      <c r="F33" s="33" t="s">
         <v>157</v>
       </c>
-      <c r="G33" s="35" t="s">
+      <c r="G33" s="33" t="s">
         <v>158</v>
       </c>
-      <c r="H33" s="35" t="s">
+      <c r="H33" s="33" t="s">
         <v>159</v>
       </c>
-      <c r="I33" s="35" t="s">
+      <c r="I33" s="33" t="s">
         <v>160</v>
       </c>
-      <c r="J33" s="35" t="s">
+      <c r="J33" s="33" t="s">
         <v>161</v>
       </c>
-      <c r="K33" s="35" t="s">
+      <c r="K33" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="L33" s="36" t="s">
+      <c r="L33" s="34" t="s">
         <v>165</v>
       </c>
-      <c r="M33" s="38" t="s">
+      <c r="M33" s="36" t="s">
         <v>153</v>
       </c>
-      <c r="N33" s="35" t="s">
+      <c r="N33" s="33" t="s">
         <v>154</v>
       </c>
-      <c r="O33" s="35" t="s">
+      <c r="O33" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="P33" s="35" t="s">
+      <c r="P33" s="33" t="s">
         <v>156</v>
       </c>
-      <c r="Q33" s="35" t="s">
+      <c r="Q33" s="33" t="s">
         <v>157</v>
       </c>
-      <c r="R33" s="35" t="s">
+      <c r="R33" s="33" t="s">
         <v>158</v>
       </c>
-      <c r="S33" s="35" t="s">
+      <c r="S33" s="33" t="s">
         <v>159</v>
       </c>
-      <c r="T33" s="35" t="s">
+      <c r="T33" s="33" t="s">
         <v>160</v>
       </c>
-      <c r="U33" s="35" t="s">
+      <c r="U33" s="33" t="s">
         <v>161</v>
       </c>
-      <c r="V33" s="35" t="s">
+      <c r="V33" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="W33" s="36" t="s">
+      <c r="W33" s="34" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A34" s="13">
+      <c r="A34" s="11">
         <v>0</v>
       </c>
-      <c r="B34" s="39" t="s">
+      <c r="B34" s="37" t="s">
         <v>122</v>
       </c>
-      <c r="C34" s="34" t="s">
+      <c r="C34" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="D34" s="34" t="s">
+      <c r="D34" s="32" t="s">
         <v>124</v>
       </c>
-      <c r="E34" s="34" t="s">
+      <c r="E34" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="F34" s="34" t="s">
+      <c r="F34" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="G34" s="34" t="s">
+      <c r="G34" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="H34" s="34" t="s">
+      <c r="H34" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="I34" s="34" t="s">
+      <c r="I34" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="J34" s="34" t="s">
+      <c r="J34" s="32" t="s">
         <v>130</v>
       </c>
-      <c r="K34" s="34" t="s">
+      <c r="K34" s="32" t="s">
         <v>131</v>
       </c>
-      <c r="L34" s="40" t="s">
+      <c r="L34" s="38" t="s">
         <v>132</v>
       </c>
-      <c r="M34" s="39" t="s">
+      <c r="M34" s="37" t="s">
         <v>133</v>
       </c>
-      <c r="N34" s="34" t="s">
+      <c r="N34" s="32" t="s">
         <v>134</v>
       </c>
-      <c r="O34" s="34" t="s">
+      <c r="O34" s="32" t="s">
         <v>135</v>
       </c>
-      <c r="P34" s="34" t="s">
+      <c r="P34" s="32" t="s">
         <v>136</v>
       </c>
-      <c r="Q34" s="34" t="s">
+      <c r="Q34" s="32" t="s">
         <v>137</v>
       </c>
-      <c r="R34" s="34" t="s">
+      <c r="R34" s="32" t="s">
         <v>138</v>
       </c>
-      <c r="S34" s="34" t="s">
+      <c r="S34" s="32" t="s">
         <v>139</v>
       </c>
-      <c r="T34" s="34" t="s">
+      <c r="T34" s="32" t="s">
         <v>140</v>
       </c>
-      <c r="U34" s="34" t="s">
+      <c r="U34" s="32" t="s">
         <v>141</v>
       </c>
-      <c r="V34" s="34" t="s">
+      <c r="V34" s="32" t="s">
         <v>142</v>
       </c>
-      <c r="W34" s="40" t="s">
+      <c r="W34" s="38" t="s">
         <v>143</v>
       </c>
     </row>
@@ -4780,7 +5383,7 @@
       <c r="A35" s="3">
         <v>1</v>
       </c>
-      <c r="B35" s="41"/>
+      <c r="B35" s="39"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
@@ -4790,8 +5393,8 @@
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
-      <c r="L35" s="42"/>
-      <c r="M35" s="41"/>
+      <c r="L35" s="40"/>
+      <c r="M35" s="39"/>
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
       <c r="P35" s="1"/>
@@ -4801,13 +5404,13 @@
       <c r="T35" s="1"/>
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
-      <c r="W35" s="42"/>
+      <c r="W35" s="40"/>
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>2</v>
       </c>
-      <c r="B36" s="41"/>
+      <c r="B36" s="39"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
@@ -4817,8 +5420,8 @@
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
-      <c r="L36" s="42"/>
-      <c r="M36" s="41"/>
+      <c r="L36" s="40"/>
+      <c r="M36" s="39"/>
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
@@ -4828,13 +5431,13 @@
       <c r="T36" s="1"/>
       <c r="U36" s="1"/>
       <c r="V36" s="1"/>
-      <c r="W36" s="42"/>
+      <c r="W36" s="40"/>
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>3</v>
       </c>
-      <c r="B37" s="41"/>
+      <c r="B37" s="39"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
@@ -4844,8 +5447,8 @@
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
-      <c r="L37" s="42"/>
-      <c r="M37" s="41"/>
+      <c r="L37" s="40"/>
+      <c r="M37" s="39"/>
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
@@ -4855,13 +5458,13 @@
       <c r="T37" s="1"/>
       <c r="U37" s="1"/>
       <c r="V37" s="1"/>
-      <c r="W37" s="42"/>
+      <c r="W37" s="40"/>
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>4</v>
       </c>
-      <c r="B38" s="41"/>
+      <c r="B38" s="39"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
@@ -4871,8 +5474,8 @@
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
-      <c r="L38" s="42"/>
-      <c r="M38" s="41"/>
+      <c r="L38" s="40"/>
+      <c r="M38" s="39"/>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
@@ -4882,13 +5485,13 @@
       <c r="T38" s="1"/>
       <c r="U38" s="1"/>
       <c r="V38" s="1"/>
-      <c r="W38" s="42"/>
+      <c r="W38" s="40"/>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>5</v>
       </c>
-      <c r="B39" s="41"/>
+      <c r="B39" s="39"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
@@ -4898,8 +5501,8 @@
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
-      <c r="L39" s="42"/>
-      <c r="M39" s="41"/>
+      <c r="L39" s="40"/>
+      <c r="M39" s="39"/>
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
       <c r="P39" s="1"/>
@@ -4909,13 +5512,13 @@
       <c r="T39" s="1"/>
       <c r="U39" s="1"/>
       <c r="V39" s="1"/>
-      <c r="W39" s="42"/>
+      <c r="W39" s="40"/>
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>6</v>
       </c>
-      <c r="B40" s="41"/>
+      <c r="B40" s="39"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
@@ -4925,8 +5528,8 @@
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
-      <c r="L40" s="42"/>
-      <c r="M40" s="41"/>
+      <c r="L40" s="40"/>
+      <c r="M40" s="39"/>
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
@@ -4936,13 +5539,13 @@
       <c r="T40" s="1"/>
       <c r="U40" s="1"/>
       <c r="V40" s="1"/>
-      <c r="W40" s="42"/>
+      <c r="W40" s="40"/>
     </row>
     <row r="41" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>7</v>
       </c>
-      <c r="B41" s="41"/>
+      <c r="B41" s="39"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
@@ -4952,8 +5555,8 @@
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
-      <c r="L41" s="42"/>
-      <c r="M41" s="41"/>
+      <c r="L41" s="40"/>
+      <c r="M41" s="39"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
       <c r="P41" s="1"/>
@@ -4963,13 +5566,13 @@
       <c r="T41" s="1"/>
       <c r="U41" s="1"/>
       <c r="V41" s="1"/>
-      <c r="W41" s="42"/>
+      <c r="W41" s="40"/>
     </row>
     <row r="42" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>8</v>
       </c>
-      <c r="B42" s="41"/>
+      <c r="B42" s="39"/>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
@@ -4979,8 +5582,8 @@
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
-      <c r="L42" s="42"/>
-      <c r="M42" s="41"/>
+      <c r="L42" s="40"/>
+      <c r="M42" s="39"/>
       <c r="N42" s="1"/>
       <c r="O42" s="1"/>
       <c r="P42" s="1"/>
@@ -4990,13 +5593,13 @@
       <c r="T42" s="1"/>
       <c r="U42" s="1"/>
       <c r="V42" s="1"/>
-      <c r="W42" s="42"/>
+      <c r="W42" s="40"/>
     </row>
     <row r="43" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>9</v>
       </c>
-      <c r="B43" s="41"/>
+      <c r="B43" s="39"/>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
@@ -5006,8 +5609,8 @@
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
-      <c r="L43" s="42"/>
-      <c r="M43" s="41"/>
+      <c r="L43" s="40"/>
+      <c r="M43" s="39"/>
       <c r="N43" s="1"/>
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
@@ -5017,13 +5620,13 @@
       <c r="T43" s="1"/>
       <c r="U43" s="1"/>
       <c r="V43" s="1"/>
-      <c r="W43" s="42"/>
+      <c r="W43" s="40"/>
     </row>
     <row r="44" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>10</v>
       </c>
-      <c r="B44" s="41"/>
+      <c r="B44" s="39"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
@@ -5033,8 +5636,8 @@
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
-      <c r="L44" s="42"/>
-      <c r="M44" s="41"/>
+      <c r="L44" s="40"/>
+      <c r="M44" s="39"/>
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
@@ -5044,13 +5647,13 @@
       <c r="T44" s="1"/>
       <c r="U44" s="1"/>
       <c r="V44" s="1"/>
-      <c r="W44" s="42"/>
+      <c r="W44" s="40"/>
     </row>
     <row r="45" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>11</v>
       </c>
-      <c r="B45" s="41"/>
+      <c r="B45" s="39"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
@@ -5060,8 +5663,8 @@
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
-      <c r="L45" s="42"/>
-      <c r="M45" s="41"/>
+      <c r="L45" s="40"/>
+      <c r="M45" s="39"/>
       <c r="N45" s="1"/>
       <c r="O45" s="1"/>
       <c r="P45" s="1"/>
@@ -5071,13 +5674,13 @@
       <c r="T45" s="1"/>
       <c r="U45" s="1"/>
       <c r="V45" s="1"/>
-      <c r="W45" s="42"/>
+      <c r="W45" s="40"/>
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <v>12</v>
       </c>
-      <c r="B46" s="41"/>
+      <c r="B46" s="39"/>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
@@ -5087,8 +5690,8 @@
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
-      <c r="L46" s="42"/>
-      <c r="M46" s="41"/>
+      <c r="L46" s="40"/>
+      <c r="M46" s="39"/>
       <c r="N46" s="1"/>
       <c r="O46" s="1"/>
       <c r="P46" s="1"/>
@@ -5098,13 +5701,13 @@
       <c r="T46" s="1"/>
       <c r="U46" s="1"/>
       <c r="V46" s="1"/>
-      <c r="W46" s="42"/>
+      <c r="W46" s="40"/>
     </row>
     <row r="47" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>13</v>
       </c>
-      <c r="B47" s="41"/>
+      <c r="B47" s="39"/>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
@@ -5114,8 +5717,8 @@
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
-      <c r="L47" s="42"/>
-      <c r="M47" s="41"/>
+      <c r="L47" s="40"/>
+      <c r="M47" s="39"/>
       <c r="N47" s="1"/>
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
@@ -5125,13 +5728,13 @@
       <c r="T47" s="1"/>
       <c r="U47" s="1"/>
       <c r="V47" s="1"/>
-      <c r="W47" s="42"/>
+      <c r="W47" s="40"/>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>14</v>
       </c>
-      <c r="B48" s="41"/>
+      <c r="B48" s="39"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
@@ -5141,8 +5744,8 @@
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
-      <c r="L48" s="42"/>
-      <c r="M48" s="41"/>
+      <c r="L48" s="40"/>
+      <c r="M48" s="39"/>
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
       <c r="P48" s="1"/>
@@ -5152,13 +5755,13 @@
       <c r="T48" s="1"/>
       <c r="U48" s="1"/>
       <c r="V48" s="1"/>
-      <c r="W48" s="42"/>
+      <c r="W48" s="40"/>
     </row>
     <row r="49" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>15</v>
       </c>
-      <c r="B49" s="41"/>
+      <c r="B49" s="39"/>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
@@ -5168,8 +5771,8 @@
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
-      <c r="L49" s="42"/>
-      <c r="M49" s="41"/>
+      <c r="L49" s="40"/>
+      <c r="M49" s="39"/>
       <c r="N49" s="1"/>
       <c r="O49" s="1"/>
       <c r="P49" s="1"/>
@@ -5179,13 +5782,13 @@
       <c r="T49" s="1"/>
       <c r="U49" s="1"/>
       <c r="V49" s="1"/>
-      <c r="W49" s="42"/>
+      <c r="W49" s="40"/>
     </row>
     <row r="50" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <v>16</v>
       </c>
-      <c r="B50" s="41"/>
+      <c r="B50" s="39"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
@@ -5195,8 +5798,8 @@
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
-      <c r="L50" s="42"/>
-      <c r="M50" s="41"/>
+      <c r="L50" s="40"/>
+      <c r="M50" s="39"/>
       <c r="N50" s="1"/>
       <c r="O50" s="1"/>
       <c r="P50" s="1"/>
@@ -5206,13 +5809,13 @@
       <c r="T50" s="1"/>
       <c r="U50" s="1"/>
       <c r="V50" s="1"/>
-      <c r="W50" s="42"/>
+      <c r="W50" s="40"/>
     </row>
     <row r="51" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>17</v>
       </c>
-      <c r="B51" s="41"/>
+      <c r="B51" s="39"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -5222,8 +5825,8 @@
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
-      <c r="L51" s="42"/>
-      <c r="M51" s="41"/>
+      <c r="L51" s="40"/>
+      <c r="M51" s="39"/>
       <c r="N51" s="1"/>
       <c r="O51" s="1"/>
       <c r="P51" s="1"/>
@@ -5233,13 +5836,13 @@
       <c r="T51" s="1"/>
       <c r="U51" s="1"/>
       <c r="V51" s="1"/>
-      <c r="W51" s="42"/>
+      <c r="W51" s="40"/>
     </row>
     <row r="52" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <v>18</v>
       </c>
-      <c r="B52" s="41"/>
+      <c r="B52" s="39"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
@@ -5249,8 +5852,8 @@
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
-      <c r="L52" s="42"/>
-      <c r="M52" s="41"/>
+      <c r="L52" s="40"/>
+      <c r="M52" s="39"/>
       <c r="N52" s="1"/>
       <c r="O52" s="1"/>
       <c r="P52" s="1"/>
@@ -5260,13 +5863,13 @@
       <c r="T52" s="1"/>
       <c r="U52" s="1"/>
       <c r="V52" s="1"/>
-      <c r="W52" s="42"/>
+      <c r="W52" s="40"/>
     </row>
     <row r="53" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <v>19</v>
       </c>
-      <c r="B53" s="41"/>
+      <c r="B53" s="39"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -5276,8 +5879,8 @@
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
-      <c r="L53" s="42"/>
-      <c r="M53" s="41"/>
+      <c r="L53" s="40"/>
+      <c r="M53" s="39"/>
       <c r="N53" s="1"/>
       <c r="O53" s="1"/>
       <c r="P53" s="1"/>
@@ -5287,13 +5890,13 @@
       <c r="T53" s="1"/>
       <c r="U53" s="1"/>
       <c r="V53" s="1"/>
-      <c r="W53" s="42"/>
+      <c r="W53" s="40"/>
     </row>
     <row r="54" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
         <v>20</v>
       </c>
-      <c r="B54" s="41"/>
+      <c r="B54" s="39"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
@@ -5303,8 +5906,8 @@
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
-      <c r="L54" s="42"/>
-      <c r="M54" s="41"/>
+      <c r="L54" s="40"/>
+      <c r="M54" s="39"/>
       <c r="N54" s="1"/>
       <c r="O54" s="1"/>
       <c r="P54" s="1"/>
@@ -5314,13 +5917,13 @@
       <c r="T54" s="1"/>
       <c r="U54" s="1"/>
       <c r="V54" s="1"/>
-      <c r="W54" s="42"/>
+      <c r="W54" s="40"/>
     </row>
     <row r="55" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <v>21</v>
       </c>
-      <c r="B55" s="41"/>
+      <c r="B55" s="39"/>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
@@ -5330,8 +5933,8 @@
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
-      <c r="L55" s="42"/>
-      <c r="M55" s="41"/>
+      <c r="L55" s="40"/>
+      <c r="M55" s="39"/>
       <c r="N55" s="1"/>
       <c r="O55" s="1"/>
       <c r="P55" s="1"/>
@@ -5341,13 +5944,13 @@
       <c r="T55" s="1"/>
       <c r="U55" s="1"/>
       <c r="V55" s="1"/>
-      <c r="W55" s="42"/>
+      <c r="W55" s="40"/>
     </row>
     <row r="56" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
         <v>22</v>
       </c>
-      <c r="B56" s="41"/>
+      <c r="B56" s="39"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
@@ -5357,8 +5960,8 @@
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
-      <c r="L56" s="42"/>
-      <c r="M56" s="41"/>
+      <c r="L56" s="40"/>
+      <c r="M56" s="39"/>
       <c r="N56" s="1"/>
       <c r="O56" s="1"/>
       <c r="P56" s="1"/>
@@ -5368,13 +5971,13 @@
       <c r="T56" s="1"/>
       <c r="U56" s="1"/>
       <c r="V56" s="1"/>
-      <c r="W56" s="42"/>
+      <c r="W56" s="40"/>
     </row>
     <row r="57" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <v>22</v>
       </c>
-      <c r="B57" s="41"/>
+      <c r="B57" s="39"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
@@ -5384,8 +5987,8 @@
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
       <c r="K57" s="1"/>
-      <c r="L57" s="42"/>
-      <c r="M57" s="41"/>
+      <c r="L57" s="40"/>
+      <c r="M57" s="39"/>
       <c r="N57" s="1"/>
       <c r="O57" s="1"/>
       <c r="P57" s="1"/>
@@ -5395,7 +5998,7 @@
       <c r="T57" s="1"/>
       <c r="U57" s="1"/>
       <c r="V57" s="1"/>
-      <c r="W57" s="42"/>
+      <c r="W57" s="40"/>
     </row>
     <row r="58" spans="1:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="3">

--- a/elec_room_project/template_전기실_운영일지.xlsx
+++ b/elec_room_project/template_전기실_운영일지.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\elec_room_project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\pygame\pygame\elec_room_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F8C2CF6-317B-440C-99C8-FAC2AB451094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8723E4EA-BEF9-47B6-97D9-2351AB286FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1515" yWindow="1740" windowWidth="21600" windowHeight="13590" xr2:uid="{943AB7D1-EB27-49C3-9C36-555299583416}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{943AB7D1-EB27-49C3-9C36-555299583416}"/>
   </bookViews>
   <sheets>
     <sheet name="전력설비_운전현황" sheetId="4" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="267">
   <si>
     <t>실내온도</t>
   </si>
@@ -114,13 +114,6 @@
     <t>한 전 메 인 / 2400배</t>
   </si>
   <si>
-    <t>전월지침</t>
-  </si>
-  <si>
-    <t>월평균
-역률(%)</t>
-  </si>
-  <si>
     <t>min( "KEP_V_R")</t>
   </si>
   <si>
@@ -701,11 +694,6 @@
   <si>
     <t>지열 3
 (2단지통로끝)</t>
-  </si>
-  <si>
-    <t>유 효 전 력
-(kW) 4번</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>시설대리</t>
@@ -1009,7 +997,7 @@
       <scheme val="major"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1019,12 +1007,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1610,7 +1592,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="150">
+  <cellXfs count="134">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1765,33 +1747,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -1828,115 +1783,11 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -1945,15 +1796,27 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1975,25 +1838,109 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2038,28 +1985,15 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="57">
+  <dxfs count="10">
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2077,7 +2011,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
+          <bgColor theme="5" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2104,25 +2038,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -2130,13 +2045,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2179,426 +2087,6 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2915,7 +2403,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q58"/>
+  <dimension ref="A1:Q48"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.125" customWidth="1"/>
@@ -2926,827 +2414,827 @@
   <sheetData>
     <row r="1" spans="1:10" ht="23.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H1" s="4" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="86.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="109" t="s">
-        <v>170</v>
-      </c>
-      <c r="B2" s="109"/>
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
-      <c r="E2" s="109"/>
-      <c r="F2" s="109"/>
-      <c r="G2" s="109"/>
+      <c r="A2" s="65" t="s">
+        <v>168</v>
+      </c>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
       <c r="H2" s="7"/>
       <c r="I2" s="8"/>
       <c r="J2" s="9"/>
     </row>
     <row r="3" spans="1:10" ht="25.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B3" s="64"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="B3" s="149"/>
-      <c r="C3" s="149"/>
-      <c r="D3" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="66" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="67"/>
+      <c r="C5" s="66" t="s">
+        <v>173</v>
+      </c>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="88" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="110"/>
-      <c r="C5" s="88" t="s">
+      <c r="F5" s="66"/>
+      <c r="G5" s="66" t="s">
         <v>175</v>
       </c>
-      <c r="D5" s="88"/>
-      <c r="E5" s="88" t="s">
+      <c r="H5" s="66"/>
+      <c r="I5" s="66" t="s">
         <v>176</v>
       </c>
-      <c r="F5" s="88"/>
-      <c r="G5" s="88" t="s">
+      <c r="J5" s="66"/>
+    </row>
+    <row r="6" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="68"/>
+      <c r="B6" s="69"/>
+      <c r="C6" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="H5" s="88"/>
-      <c r="I5" s="88" t="s">
+      <c r="D6" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="J5" s="88"/>
-    </row>
-    <row r="6" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="111"/>
-      <c r="B6" s="112"/>
-      <c r="C6" s="10" t="s">
+      <c r="E6" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="66" t="s">
         <v>179</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="B7" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="E6" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="F6" s="10" t="s">
+      <c r="C7" s="52" t="s">
+        <v>181</v>
+      </c>
+      <c r="D7" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="52" t="s">
+        <v>55</v>
+      </c>
+      <c r="H7" s="52" t="s">
+        <v>56</v>
+      </c>
+      <c r="I7" s="52" t="s">
+        <v>75</v>
+      </c>
+      <c r="J7" s="52" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="66"/>
+      <c r="B8" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="C8" s="52" t="s">
+        <v>183</v>
+      </c>
+      <c r="D8" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="52" t="s">
+        <v>57</v>
+      </c>
+      <c r="H8" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="I8" s="52" t="s">
+        <v>77</v>
+      </c>
+      <c r="J8" s="52" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="66"/>
+      <c r="B9" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="C9" s="52" t="s">
+        <v>185</v>
+      </c>
+      <c r="D9" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="52" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="52" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="I9" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="J9" s="52" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="66" t="s">
+        <v>186</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C10" s="52" t="s">
+        <v>188</v>
+      </c>
+      <c r="D10" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="52" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" s="52" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="52" t="s">
+        <v>61</v>
+      </c>
+      <c r="H10" s="52" t="s">
+        <v>62</v>
+      </c>
+      <c r="I10" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="J10" s="52" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="66"/>
+      <c r="B11" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="C11" s="52" t="s">
+        <v>190</v>
+      </c>
+      <c r="D11" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="52" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" s="52" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" s="52" t="s">
+        <v>63</v>
+      </c>
+      <c r="H11" s="52" t="s">
+        <v>64</v>
+      </c>
+      <c r="I11" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="J11" s="52" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="66"/>
+      <c r="B12" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="C12" s="52" t="s">
+        <v>192</v>
+      </c>
+      <c r="D12" s="52" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="52" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" s="52" t="s">
+        <v>46</v>
+      </c>
+      <c r="G12" s="52" t="s">
+        <v>65</v>
+      </c>
+      <c r="H12" s="52" t="s">
+        <v>66</v>
+      </c>
+      <c r="I12" s="52" t="s">
+        <v>85</v>
+      </c>
+      <c r="J12" s="52" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="66" t="s">
+        <v>193</v>
+      </c>
+      <c r="B13" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="G6" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="J6" s="10" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="88" t="s">
-        <v>181</v>
-      </c>
-      <c r="B7" s="10" t="s">
+      <c r="C13" s="52" t="s">
+        <v>194</v>
+      </c>
+      <c r="D13" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="52" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13" s="52" t="s">
+        <v>48</v>
+      </c>
+      <c r="G13" s="52" t="s">
+        <v>67</v>
+      </c>
+      <c r="H13" s="52" t="s">
+        <v>68</v>
+      </c>
+      <c r="I13" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="J13" s="52" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="66"/>
+      <c r="B14" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="C7" s="61" t="s">
-        <v>183</v>
-      </c>
-      <c r="D7" s="61" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="61" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" s="61" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" s="61" t="s">
-        <v>57</v>
-      </c>
-      <c r="H7" s="61" t="s">
-        <v>58</v>
-      </c>
-      <c r="I7" s="61" t="s">
-        <v>77</v>
-      </c>
-      <c r="J7" s="61" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="88"/>
-      <c r="B8" s="10" t="s">
+      <c r="C14" s="52" t="s">
+        <v>195</v>
+      </c>
+      <c r="D14" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" s="52" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" s="52" t="s">
+        <v>50</v>
+      </c>
+      <c r="G14" s="52" t="s">
+        <v>69</v>
+      </c>
+      <c r="H14" s="52" t="s">
+        <v>70</v>
+      </c>
+      <c r="I14" s="52" t="s">
+        <v>89</v>
+      </c>
+      <c r="J14" s="52" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="66"/>
+      <c r="B15" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="C8" s="61" t="s">
-        <v>185</v>
-      </c>
-      <c r="D8" s="61" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="61" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="61" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8" s="61" t="s">
-        <v>59</v>
-      </c>
-      <c r="H8" s="61" t="s">
-        <v>60</v>
-      </c>
-      <c r="I8" s="61" t="s">
-        <v>79</v>
-      </c>
-      <c r="J8" s="61" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="88"/>
-      <c r="B9" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="C9" s="61" t="s">
-        <v>187</v>
-      </c>
-      <c r="D9" s="61" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="61" t="s">
-        <v>41</v>
-      </c>
-      <c r="F9" s="61" t="s">
-        <v>42</v>
-      </c>
-      <c r="G9" s="61" t="s">
-        <v>61</v>
-      </c>
-      <c r="H9" s="61" t="s">
-        <v>62</v>
-      </c>
-      <c r="I9" s="61" t="s">
-        <v>81</v>
-      </c>
-      <c r="J9" s="61" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="88" t="s">
-        <v>188</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="C10" s="61" t="s">
-        <v>190</v>
-      </c>
-      <c r="D10" s="61" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="61" t="s">
-        <v>43</v>
-      </c>
-      <c r="F10" s="61" t="s">
-        <v>44</v>
-      </c>
-      <c r="G10" s="61" t="s">
-        <v>63</v>
-      </c>
-      <c r="H10" s="61" t="s">
-        <v>64</v>
-      </c>
-      <c r="I10" s="61" t="s">
-        <v>83</v>
-      </c>
-      <c r="J10" s="61" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="88"/>
-      <c r="B11" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="C11" s="61" t="s">
-        <v>192</v>
-      </c>
-      <c r="D11" s="61" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" s="61" t="s">
-        <v>45</v>
-      </c>
-      <c r="F11" s="61" t="s">
-        <v>46</v>
-      </c>
-      <c r="G11" s="61" t="s">
-        <v>65</v>
-      </c>
-      <c r="H11" s="61" t="s">
-        <v>66</v>
-      </c>
-      <c r="I11" s="61" t="s">
-        <v>85</v>
-      </c>
-      <c r="J11" s="61" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="88"/>
-      <c r="B12" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="C12" s="61" t="s">
-        <v>194</v>
-      </c>
-      <c r="D12" s="61" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="61" t="s">
-        <v>47</v>
-      </c>
-      <c r="F12" s="61" t="s">
-        <v>48</v>
-      </c>
-      <c r="G12" s="61" t="s">
-        <v>67</v>
-      </c>
-      <c r="H12" s="61" t="s">
-        <v>68</v>
-      </c>
-      <c r="I12" s="61" t="s">
-        <v>87</v>
-      </c>
-      <c r="J12" s="61" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="88" t="s">
-        <v>195</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="C13" s="61" t="s">
+      <c r="C15" s="52" t="s">
         <v>196</v>
       </c>
-      <c r="D13" s="61" t="s">
+      <c r="D15" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="61" t="s">
-        <v>49</v>
-      </c>
-      <c r="F13" s="61" t="s">
-        <v>50</v>
-      </c>
-      <c r="G13" s="61" t="s">
-        <v>69</v>
-      </c>
-      <c r="H13" s="61" t="s">
-        <v>70</v>
-      </c>
-      <c r="I13" s="61" t="s">
-        <v>89</v>
-      </c>
-      <c r="J13" s="61" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="88"/>
-      <c r="B14" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="C14" s="61" t="s">
-        <v>197</v>
-      </c>
-      <c r="D14" s="61" t="s">
-        <v>34</v>
-      </c>
-      <c r="E14" s="61" t="s">
+      <c r="E15" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="F14" s="61" t="s">
+      <c r="F15" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G14" s="61" t="s">
+      <c r="G15" s="52" t="s">
         <v>71</v>
       </c>
-      <c r="H14" s="61" t="s">
+      <c r="H15" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="I14" s="61" t="s">
+      <c r="I15" s="52" t="s">
         <v>91</v>
       </c>
-      <c r="J14" s="61" t="s">
+      <c r="J15" s="52" t="s">
         <v>92</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="88"/>
-      <c r="B15" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="C15" s="61" t="s">
-        <v>198</v>
-      </c>
-      <c r="D15" s="61" t="s">
-        <v>35</v>
-      </c>
-      <c r="E15" s="61" t="s">
-        <v>53</v>
-      </c>
-      <c r="F15" s="61" t="s">
-        <v>54</v>
-      </c>
-      <c r="G15" s="61" t="s">
-        <v>73</v>
-      </c>
-      <c r="H15" s="61" t="s">
-        <v>74</v>
-      </c>
-      <c r="I15" s="61" t="s">
-        <v>93</v>
-      </c>
-      <c r="J15" s="61" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B16" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="C16" s="52" t="s">
+        <v>198</v>
+      </c>
+      <c r="D16" s="52" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16" s="52" t="s">
+        <v>54</v>
+      </c>
+      <c r="G16" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="H16" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="I16" s="52" t="s">
+        <v>93</v>
+      </c>
+      <c r="J16" s="52" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="83" t="s">
         <v>199</v>
       </c>
-      <c r="C16" s="61" t="s">
+      <c r="B17" s="84"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52" t="s">
         <v>200</v>
       </c>
-      <c r="D16" s="61" t="s">
-        <v>36</v>
-      </c>
-      <c r="E16" s="61" t="s">
-        <v>55</v>
-      </c>
-      <c r="F16" s="61" t="s">
-        <v>56</v>
-      </c>
-      <c r="G16" s="61" t="s">
-        <v>75</v>
-      </c>
-      <c r="H16" s="61" t="s">
-        <v>76</v>
-      </c>
-      <c r="I16" s="61" t="s">
-        <v>95</v>
-      </c>
-      <c r="J16" s="61" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="122" t="s">
+      <c r="F17" s="52" t="s">
         <v>201</v>
       </c>
-      <c r="B17" s="123"/>
-      <c r="C17" s="61"/>
-      <c r="D17" s="61"/>
-      <c r="E17" s="61" t="s">
+      <c r="G17" s="52" t="s">
         <v>202</v>
       </c>
-      <c r="F17" s="61" t="s">
+      <c r="H17" s="52" t="s">
         <v>203</v>
       </c>
-      <c r="G17" s="61" t="s">
+      <c r="I17" s="52" t="s">
         <v>204</v>
       </c>
-      <c r="H17" s="61" t="s">
+      <c r="J17" s="52" t="s">
         <v>205</v>
       </c>
-      <c r="I17" s="61" t="s">
-        <v>206</v>
-      </c>
-      <c r="J17" s="61" t="s">
-        <v>207</v>
-      </c>
     </row>
     <row r="18" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="89" t="s">
-        <v>225</v>
-      </c>
-      <c r="B18" s="89"/>
-      <c r="C18" s="61"/>
-      <c r="D18" s="61"/>
-      <c r="E18" s="62" t="e">
+      <c r="A18" s="105" t="s">
+        <v>222</v>
+      </c>
+      <c r="B18" s="105"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="53" t="e">
         <f>+E16/1000</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F18" s="63" t="e">
+      <c r="F18" s="54" t="e">
         <f>+F16/1000</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G18" s="62" t="e">
+      <c r="G18" s="53" t="e">
         <f>+G16/1250</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H18" s="63" t="e">
+      <c r="H18" s="54" t="e">
         <f t="shared" ref="H18:J18" si="0">+H16/1250</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I18" s="62" t="e">
+      <c r="I18" s="53" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="J18" s="63" t="e">
+      <c r="J18" s="54" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="79" t="s">
+        <v>207</v>
+      </c>
+      <c r="B20" s="75"/>
+      <c r="C20" s="75" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="118" t="s">
+      <c r="D20" s="75"/>
+      <c r="E20" s="76" t="s">
         <v>209</v>
       </c>
-      <c r="B20" s="116"/>
-      <c r="C20" s="116" t="s">
+      <c r="F20" s="77"/>
+      <c r="G20" s="75" t="s">
         <v>210</v>
       </c>
-      <c r="D20" s="116"/>
-      <c r="E20" s="147" t="s">
+      <c r="H20" s="78"/>
+    </row>
+    <row r="21" spans="1:10" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="80" t="s">
         <v>211</v>
       </c>
-      <c r="F20" s="148"/>
-      <c r="G20" s="116" t="s">
+      <c r="B21" s="66"/>
+      <c r="C21" s="71" t="s">
+        <v>221</v>
+      </c>
+      <c r="D21" s="71"/>
+      <c r="E21" s="112" t="s">
         <v>212</v>
       </c>
-      <c r="H20" s="117"/>
-    </row>
-    <row r="21" spans="1:10" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="119" t="s">
-        <v>213</v>
-      </c>
-      <c r="B21" s="88"/>
-      <c r="C21" s="82" t="s">
-        <v>224</v>
-      </c>
-      <c r="D21" s="82"/>
-      <c r="E21" s="145" t="s">
-        <v>214</v>
-      </c>
-      <c r="F21" s="146"/>
-      <c r="G21" s="82" t="e">
+      <c r="F21" s="113"/>
+      <c r="G21" s="71" t="e">
         <f>E21-C21</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H21" s="114"/>
+      <c r="H21" s="72"/>
     </row>
     <row r="22" spans="1:10" ht="35.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="120" t="s">
-        <v>215</v>
-      </c>
-      <c r="B22" s="121"/>
-      <c r="C22" s="113" t="s">
-        <v>241</v>
-      </c>
-      <c r="D22" s="113"/>
-      <c r="E22" s="113" t="s">
-        <v>242</v>
-      </c>
-      <c r="F22" s="113"/>
-      <c r="G22" s="84" t="e">
+      <c r="A22" s="81" t="s">
+        <v>213</v>
+      </c>
+      <c r="B22" s="82"/>
+      <c r="C22" s="70" t="s">
+        <v>238</v>
+      </c>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70" t="s">
+        <v>239</v>
+      </c>
+      <c r="F22" s="70"/>
+      <c r="G22" s="73" t="e">
         <f>+E22-C22</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H22" s="115"/>
+      <c r="H22" s="74"/>
     </row>
     <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="24" spans="1:10" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="73" t="s">
+      <c r="A25" s="106" t="s">
         <v>1</v>
       </c>
-      <c r="B25" s="74"/>
-      <c r="C25" s="74" t="s">
+      <c r="B25" s="107"/>
+      <c r="C25" s="107" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="74"/>
-      <c r="E25" s="74" t="s">
+      <c r="D25" s="107"/>
+      <c r="E25" s="107" t="s">
         <v>2</v>
       </c>
-      <c r="F25" s="74"/>
-      <c r="G25" s="74"/>
-      <c r="H25" s="74" t="s">
+      <c r="F25" s="107"/>
+      <c r="G25" s="107"/>
+      <c r="H25" s="107" t="s">
         <v>3</v>
       </c>
-      <c r="I25" s="74"/>
-      <c r="J25" s="87"/>
+      <c r="I25" s="107"/>
+      <c r="J25" s="111"/>
     </row>
     <row r="26" spans="1:10" ht="35.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="90"/>
-      <c r="B26" s="91"/>
-      <c r="C26" s="66" t="s">
+      <c r="A26" s="108"/>
+      <c r="B26" s="109"/>
+      <c r="C26" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="D26" s="66" t="s">
+      <c r="D26" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="E26" s="66" t="s">
+      <c r="E26" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="F26" s="66" t="s">
+      <c r="F26" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="G26" s="66" t="s">
+      <c r="G26" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="H26" s="66" t="s">
+      <c r="H26" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="I26" s="66" t="s">
+      <c r="I26" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="J26" s="67" t="s">
+      <c r="J26" s="58" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="73" t="s">
+      <c r="A27" s="106" t="s">
+        <v>240</v>
+      </c>
+      <c r="B27" s="107"/>
+      <c r="C27" s="61" t="s">
+        <v>241</v>
+      </c>
+      <c r="D27" s="61" t="s">
+        <v>242</v>
+      </c>
+      <c r="E27" s="61" t="s">
         <v>243</v>
       </c>
-      <c r="B27" s="74"/>
-      <c r="C27" s="70" t="s">
+      <c r="F27" s="61" t="s">
         <v>244</v>
       </c>
-      <c r="D27" s="70" t="s">
+      <c r="G27" s="61" t="s">
         <v>245</v>
       </c>
-      <c r="E27" s="70" t="s">
+      <c r="H27" s="61" t="s">
         <v>246</v>
       </c>
-      <c r="F27" s="70" t="s">
+      <c r="I27" s="61" t="s">
         <v>247</v>
       </c>
-      <c r="G27" s="70" t="s">
+      <c r="J27" s="62" t="s">
         <v>248</v>
       </c>
-      <c r="H27" s="70" t="s">
+    </row>
+    <row r="28" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="110" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" s="71"/>
+      <c r="C28" s="52" t="s">
+        <v>257</v>
+      </c>
+      <c r="D28" s="52" t="s">
+        <v>258</v>
+      </c>
+      <c r="E28" s="52" t="s">
+        <v>259</v>
+      </c>
+      <c r="F28" s="52" t="s">
+        <v>260</v>
+      </c>
+      <c r="G28" s="52" t="s">
+        <v>261</v>
+      </c>
+      <c r="H28" s="52" t="s">
+        <v>262</v>
+      </c>
+      <c r="I28" s="52" t="s">
+        <v>263</v>
+      </c>
+      <c r="J28" s="63" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="110" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" s="71"/>
+      <c r="C29" s="52" t="s">
         <v>249</v>
       </c>
-      <c r="I27" s="70" t="s">
+      <c r="D29" s="52" t="s">
         <v>250</v>
       </c>
-      <c r="J27" s="71" t="s">
+      <c r="E29" s="52" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="81" t="s">
-        <v>12</v>
-      </c>
-      <c r="B28" s="82"/>
-      <c r="C28" s="61" t="s">
-        <v>260</v>
-      </c>
-      <c r="D28" s="61" t="s">
-        <v>261</v>
-      </c>
-      <c r="E28" s="61" t="s">
-        <v>262</v>
-      </c>
-      <c r="F28" s="61" t="s">
-        <v>263</v>
-      </c>
-      <c r="G28" s="61" t="s">
-        <v>264</v>
-      </c>
-      <c r="H28" s="61" t="s">
-        <v>265</v>
-      </c>
-      <c r="I28" s="61" t="s">
-        <v>266</v>
-      </c>
-      <c r="J28" s="72" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="81" t="s">
-        <v>13</v>
-      </c>
-      <c r="B29" s="82"/>
-      <c r="C29" s="61" t="s">
+      <c r="F29" s="52" t="s">
         <v>252</v>
       </c>
-      <c r="D29" s="61" t="s">
+      <c r="G29" s="52" t="s">
         <v>253</v>
       </c>
-      <c r="E29" s="61" t="s">
+      <c r="H29" s="52" t="s">
         <v>254</v>
       </c>
-      <c r="F29" s="61" t="s">
+      <c r="I29" s="52" t="s">
         <v>255</v>
       </c>
-      <c r="G29" s="61" t="s">
+      <c r="J29" s="63" t="s">
         <v>256</v>
       </c>
-      <c r="H29" s="61" t="s">
-        <v>257</v>
-      </c>
-      <c r="I29" s="61" t="s">
-        <v>258</v>
-      </c>
-      <c r="J29" s="72" t="s">
-        <v>259</v>
-      </c>
     </row>
     <row r="30" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="81" t="s">
+      <c r="A30" s="110" t="s">
         <v>14</v>
       </c>
-      <c r="B30" s="82"/>
-      <c r="C30" s="64" t="e">
+      <c r="B30" s="71"/>
+      <c r="C30" s="55" t="e">
         <f>+C28-C29</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D30" s="64" t="e">
+      <c r="D30" s="55" t="e">
         <f t="shared" ref="D30:J30" si="1">+D28-D29</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E30" s="64" t="e">
+      <c r="E30" s="55" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F30" s="64" t="e">
+      <c r="F30" s="55" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="G30" s="64" t="e">
+      <c r="G30" s="55" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H30" s="64" t="e">
+      <c r="H30" s="55" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="I30" s="64" t="e">
+      <c r="I30" s="55" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="J30" s="65" t="e">
+      <c r="J30" s="56" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="81" t="s">
+      <c r="A31" s="110" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="82"/>
-      <c r="C31" s="64" t="e">
+      <c r="B31" s="71"/>
+      <c r="C31" s="55" t="e">
         <f>+C30*2400</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D31" s="64" t="e">
+      <c r="D31" s="55" t="e">
         <f>+D30*2400</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E31" s="64" t="e">
+      <c r="E31" s="55" t="e">
         <f>E30*80</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F31" s="64" t="e">
+      <c r="F31" s="55" t="e">
         <f t="shared" ref="F31:G31" si="2">F30*80</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G31" s="64" t="e">
+      <c r="G31" s="55" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H31" s="64" t="e">
+      <c r="H31" s="55" t="e">
         <f>+H30</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I31" s="64" t="e">
+      <c r="I31" s="55" t="e">
         <f t="shared" ref="I31:J31" si="3">+I30</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J31" s="65" t="e">
+      <c r="J31" s="56" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="81" t="s">
+      <c r="A32" s="110" t="s">
         <v>16</v>
       </c>
-      <c r="B32" s="82"/>
-      <c r="C32" s="64" t="e">
+      <c r="B32" s="71"/>
+      <c r="C32" s="55" t="e">
         <f>(C28-C27)*2400</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D32" s="64" t="e">
+      <c r="D32" s="55" t="e">
         <f>(D28-D27)*2400</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E32" s="64" t="e">
-        <f t="shared" ref="E32:J32" si="4">+E57</f>
+      <c r="E32" s="55" t="e">
+        <f>(E28-E27)*80</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F32" s="64" t="e">
+      <c r="F32" s="55" t="e">
+        <f t="shared" ref="F32:G32" si="4">(F28-F27)*80</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G32" s="55" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="G32" s="64" t="e">
-        <f t="shared" si="4"/>
+      <c r="H32" s="55" t="e">
+        <f>H28-H27</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H32" s="64" t="e">
-        <f t="shared" si="4"/>
+      <c r="I32" s="55" t="e">
+        <f t="shared" ref="I32:J32" si="5">I28-I27</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I32" s="64" t="e">
-        <f t="shared" si="4"/>
+      <c r="J32" s="56" t="e">
+        <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
-      <c r="J32" s="65" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
     </row>
     <row r="33" spans="1:17" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="83" t="s">
+      <c r="A33" s="117" t="s">
         <v>17</v>
       </c>
-      <c r="B33" s="84"/>
+      <c r="B33" s="73"/>
       <c r="C33" s="14" t="e">
         <f>C30/(SQRT(C30^2+D30^2*100))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D33" s="69"/>
-      <c r="E33" s="69"/>
-      <c r="F33" s="69"/>
+      <c r="D33" s="60"/>
+      <c r="E33" s="60"/>
+      <c r="F33" s="60"/>
       <c r="G33" s="14" t="s">
         <v>18</v>
       </c>
       <c r="H33" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="I33" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="J33" s="31" t="s">
         <v>217</v>
       </c>
-      <c r="I33" s="30" t="s">
-        <v>218</v>
-      </c>
-      <c r="J33" s="31" t="s">
-        <v>219</v>
-      </c>
     </row>
     <row r="34" spans="1:17" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="85" t="s">
+      <c r="A34" s="118" t="s">
         <v>19</v>
       </c>
-      <c r="B34" s="86"/>
+      <c r="B34" s="119"/>
       <c r="C34" s="26"/>
       <c r="D34" s="26"/>
       <c r="E34" s="26"/>
       <c r="F34" s="17"/>
-      <c r="G34" s="68" t="s">
+      <c r="G34" s="59" t="s">
         <v>20</v>
       </c>
       <c r="H34" s="28" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="I34" s="28" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="J34" s="29" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3760,13 +3248,13 @@
         <v>21</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="J35" s="13" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="36" spans="1:17" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -3784,17 +3272,17 @@
         <v>#VALUE!</v>
       </c>
       <c r="I36" s="14" t="e">
-        <f t="shared" ref="I36:J36" si="5">+I34-I35</f>
+        <f t="shared" ref="I36:J36" si="6">+I34-I35</f>
         <v>#VALUE!</v>
       </c>
       <c r="J36" s="15" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="38" spans="1:17" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B38" s="21"/>
       <c r="C38" s="21"/>
@@ -3807,338 +3295,219 @@
       <c r="J38" s="21"/>
     </row>
     <row r="39" spans="1:17" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="95" t="s">
+      <c r="A39" s="88" t="s">
+        <v>224</v>
+      </c>
+      <c r="B39" s="89"/>
+      <c r="C39" s="89"/>
+      <c r="D39" s="89"/>
+      <c r="E39" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="F39" s="89" t="s">
+        <v>226</v>
+      </c>
+      <c r="G39" s="89"/>
+      <c r="H39" s="90"/>
+      <c r="I39" s="91" t="s">
         <v>227</v>
       </c>
-      <c r="B39" s="96"/>
-      <c r="C39" s="96"/>
-      <c r="D39" s="96"/>
-      <c r="E39" s="25" t="s">
-        <v>228</v>
-      </c>
-      <c r="F39" s="96" t="s">
-        <v>229</v>
-      </c>
-      <c r="G39" s="96"/>
-      <c r="H39" s="97"/>
-      <c r="I39" s="98" t="s">
-        <v>230</v>
-      </c>
-      <c r="J39" s="99"/>
+      <c r="J39" s="92"/>
       <c r="Q39" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="100" t="s">
+      <c r="A40" s="93" t="s">
+        <v>228</v>
+      </c>
+      <c r="B40" s="94"/>
+      <c r="C40" s="94"/>
+      <c r="D40" s="94"/>
+      <c r="E40" s="24" t="s">
+        <v>229</v>
+      </c>
+      <c r="F40" s="94"/>
+      <c r="G40" s="94"/>
+      <c r="H40" s="95"/>
+      <c r="I40" s="96"/>
+      <c r="J40" s="97"/>
+    </row>
+    <row r="41" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="102" t="s">
+        <v>230</v>
+      </c>
+      <c r="B41" s="103"/>
+      <c r="C41" s="103"/>
+      <c r="D41" s="103"/>
+      <c r="E41" s="22" t="s">
+        <v>229</v>
+      </c>
+      <c r="F41" s="103"/>
+      <c r="G41" s="103"/>
+      <c r="H41" s="104"/>
+      <c r="I41" s="98"/>
+      <c r="J41" s="99"/>
+    </row>
+    <row r="42" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="102" t="s">
         <v>231</v>
       </c>
-      <c r="B40" s="101"/>
-      <c r="C40" s="101"/>
-      <c r="D40" s="101"/>
-      <c r="E40" s="24" t="s">
+      <c r="B42" s="103"/>
+      <c r="C42" s="103"/>
+      <c r="D42" s="103"/>
+      <c r="E42" s="22" t="s">
+        <v>229</v>
+      </c>
+      <c r="F42" s="103"/>
+      <c r="G42" s="103"/>
+      <c r="H42" s="104"/>
+      <c r="I42" s="98"/>
+      <c r="J42" s="99"/>
+    </row>
+    <row r="43" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="102" t="s">
         <v>232</v>
       </c>
-      <c r="F40" s="101"/>
-      <c r="G40" s="101"/>
-      <c r="H40" s="102"/>
-      <c r="I40" s="103"/>
-      <c r="J40" s="104"/>
-    </row>
-    <row r="41" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="75" t="s">
+      <c r="B43" s="103"/>
+      <c r="C43" s="103"/>
+      <c r="D43" s="103"/>
+      <c r="E43" s="22" t="s">
+        <v>229</v>
+      </c>
+      <c r="F43" s="103"/>
+      <c r="G43" s="103"/>
+      <c r="H43" s="104"/>
+      <c r="I43" s="98"/>
+      <c r="J43" s="99"/>
+    </row>
+    <row r="44" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="102" t="s">
         <v>233</v>
       </c>
-      <c r="B41" s="76"/>
-      <c r="C41" s="76"/>
-      <c r="D41" s="76"/>
-      <c r="E41" s="22" t="s">
-        <v>232</v>
-      </c>
-      <c r="F41" s="76"/>
-      <c r="G41" s="76"/>
-      <c r="H41" s="77"/>
-      <c r="I41" s="105"/>
-      <c r="J41" s="106"/>
-    </row>
-    <row r="42" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="75" t="s">
+      <c r="B44" s="103"/>
+      <c r="C44" s="103"/>
+      <c r="D44" s="103"/>
+      <c r="E44" s="22" t="s">
+        <v>229</v>
+      </c>
+      <c r="F44" s="103"/>
+      <c r="G44" s="103"/>
+      <c r="H44" s="104"/>
+      <c r="I44" s="98"/>
+      <c r="J44" s="99"/>
+    </row>
+    <row r="45" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="102" t="s">
         <v>234</v>
       </c>
-      <c r="B42" s="76"/>
-      <c r="C42" s="76"/>
-      <c r="D42" s="76"/>
-      <c r="E42" s="22" t="s">
-        <v>232</v>
-      </c>
-      <c r="F42" s="76"/>
-      <c r="G42" s="76"/>
-      <c r="H42" s="77"/>
-      <c r="I42" s="105"/>
-      <c r="J42" s="106"/>
-    </row>
-    <row r="43" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="75" t="s">
+      <c r="B45" s="103"/>
+      <c r="C45" s="103"/>
+      <c r="D45" s="103"/>
+      <c r="E45" s="22" t="s">
+        <v>229</v>
+      </c>
+      <c r="F45" s="103"/>
+      <c r="G45" s="103"/>
+      <c r="H45" s="104"/>
+      <c r="I45" s="98"/>
+      <c r="J45" s="99"/>
+    </row>
+    <row r="46" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="102" t="s">
         <v>235</v>
       </c>
-      <c r="B43" s="76"/>
-      <c r="C43" s="76"/>
-      <c r="D43" s="76"/>
-      <c r="E43" s="22" t="s">
-        <v>232</v>
-      </c>
-      <c r="F43" s="76"/>
-      <c r="G43" s="76"/>
-      <c r="H43" s="77"/>
-      <c r="I43" s="105"/>
-      <c r="J43" s="106"/>
-    </row>
-    <row r="44" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="75" t="s">
+      <c r="B46" s="103"/>
+      <c r="C46" s="103"/>
+      <c r="D46" s="103"/>
+      <c r="E46" s="22" t="s">
+        <v>229</v>
+      </c>
+      <c r="F46" s="103"/>
+      <c r="G46" s="103"/>
+      <c r="H46" s="104"/>
+      <c r="I46" s="98"/>
+      <c r="J46" s="99"/>
+    </row>
+    <row r="47" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="102" t="s">
         <v>236</v>
       </c>
-      <c r="B44" s="76"/>
-      <c r="C44" s="76"/>
-      <c r="D44" s="76"/>
-      <c r="E44" s="22" t="s">
-        <v>232</v>
-      </c>
-      <c r="F44" s="76"/>
-      <c r="G44" s="76"/>
-      <c r="H44" s="77"/>
-      <c r="I44" s="105"/>
-      <c r="J44" s="106"/>
-    </row>
-    <row r="45" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="75" t="s">
+      <c r="B47" s="103"/>
+      <c r="C47" s="103"/>
+      <c r="D47" s="103"/>
+      <c r="E47" s="22" t="s">
+        <v>229</v>
+      </c>
+      <c r="F47" s="103"/>
+      <c r="G47" s="103"/>
+      <c r="H47" s="104"/>
+      <c r="I47" s="98"/>
+      <c r="J47" s="99"/>
+    </row>
+    <row r="48" spans="1:17" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="114" t="s">
         <v>237</v>
       </c>
-      <c r="B45" s="76"/>
-      <c r="C45" s="76"/>
-      <c r="D45" s="76"/>
-      <c r="E45" s="22" t="s">
-        <v>232</v>
-      </c>
-      <c r="F45" s="76"/>
-      <c r="G45" s="76"/>
-      <c r="H45" s="77"/>
-      <c r="I45" s="105"/>
-      <c r="J45" s="106"/>
-    </row>
-    <row r="46" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="75" t="s">
-        <v>238</v>
-      </c>
-      <c r="B46" s="76"/>
-      <c r="C46" s="76"/>
-      <c r="D46" s="76"/>
-      <c r="E46" s="22" t="s">
-        <v>232</v>
-      </c>
-      <c r="F46" s="76"/>
-      <c r="G46" s="76"/>
-      <c r="H46" s="77"/>
-      <c r="I46" s="105"/>
-      <c r="J46" s="106"/>
-    </row>
-    <row r="47" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="75" t="s">
-        <v>239</v>
-      </c>
-      <c r="B47" s="76"/>
-      <c r="C47" s="76"/>
-      <c r="D47" s="76"/>
-      <c r="E47" s="22" t="s">
-        <v>232</v>
-      </c>
-      <c r="F47" s="76"/>
-      <c r="G47" s="76"/>
-      <c r="H47" s="77"/>
-      <c r="I47" s="105"/>
-      <c r="J47" s="106"/>
-    </row>
-    <row r="48" spans="1:17" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="78" t="s">
-        <v>240</v>
-      </c>
-      <c r="B48" s="79"/>
-      <c r="C48" s="79"/>
-      <c r="D48" s="79"/>
+      <c r="B48" s="115"/>
+      <c r="C48" s="115"/>
+      <c r="D48" s="115"/>
       <c r="E48" s="23" t="s">
-        <v>232</v>
-      </c>
-      <c r="F48" s="79"/>
-      <c r="G48" s="79"/>
-      <c r="H48" s="80"/>
-      <c r="I48" s="107"/>
-      <c r="J48" s="108"/>
-    </row>
-    <row r="52" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="53" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="92"/>
-      <c r="B53" s="93"/>
-      <c r="C53" s="92" t="s">
-        <v>24</v>
-      </c>
-      <c r="D53" s="93"/>
-      <c r="E53" s="92" t="s">
-        <v>2</v>
-      </c>
-      <c r="F53" s="94"/>
-      <c r="G53" s="93"/>
-      <c r="H53" s="92" t="s">
-        <v>3</v>
-      </c>
-      <c r="I53" s="94"/>
-      <c r="J53" s="93"/>
-    </row>
-    <row r="54" spans="1:10" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="124"/>
-      <c r="B54" s="125"/>
-      <c r="C54" s="55" t="s">
-        <v>220</v>
-      </c>
-      <c r="D54" s="54" t="s">
-        <v>5</v>
-      </c>
-      <c r="E54" s="55" t="s">
-        <v>6</v>
-      </c>
-      <c r="F54" s="53" t="s">
-        <v>7</v>
-      </c>
-      <c r="G54" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="H54" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="I54" s="53" t="s">
-        <v>10</v>
-      </c>
-      <c r="J54" s="54" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="126" t="s">
-        <v>20</v>
-      </c>
-      <c r="B55" s="127"/>
-      <c r="C55" s="56" t="str">
-        <f>+C28</f>
-        <v>금일("main_active")</v>
-      </c>
-      <c r="D55" s="57">
-        <v>0</v>
-      </c>
-      <c r="E55" s="56" t="str">
-        <f t="shared" ref="E55:J55" si="6">+E28</f>
-        <v>금일("ind_mid")</v>
-      </c>
-      <c r="F55" s="52" t="str">
-        <f t="shared" si="6"/>
-        <v>금일("ind_max")</v>
-      </c>
-      <c r="G55" s="57" t="str">
-        <f t="shared" si="6"/>
-        <v>금일("ind_light")</v>
-      </c>
-      <c r="H55" s="56" t="str">
-        <f t="shared" si="6"/>
-        <v>금일("street_mid")</v>
-      </c>
-      <c r="I55" s="52" t="str">
-        <f t="shared" si="6"/>
-        <v>금일("street_max")</v>
-      </c>
-      <c r="J55" s="57" t="str">
-        <f t="shared" si="6"/>
-        <v>금일("street_light")</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="128" t="s">
-        <v>25</v>
-      </c>
-      <c r="B56" s="129"/>
-      <c r="C56" s="58">
-        <v>1309.8499999999999</v>
-      </c>
-      <c r="D56" s="59">
-        <v>0</v>
-      </c>
-      <c r="E56" s="58">
-        <v>7014.1</v>
-      </c>
-      <c r="F56" s="60">
-        <v>3563.95</v>
-      </c>
-      <c r="G56" s="59">
-        <v>9804.3799999999992</v>
-      </c>
-      <c r="H56" s="58">
-        <v>10305</v>
-      </c>
-      <c r="I56" s="60">
-        <v>1638</v>
-      </c>
-      <c r="J56" s="59">
-        <v>33594</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="124" t="s">
-        <v>16</v>
-      </c>
-      <c r="B57" s="125"/>
-      <c r="C57" s="7" t="e">
-        <f>(+C55-C56)*2400</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D57" s="9">
-        <v>0</v>
-      </c>
-      <c r="E57" s="7" t="e">
-        <f>(+E55-E56)*80</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F57" s="8" t="e">
-        <f t="shared" ref="F57:G57" si="7">(+F55-F56)*80</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G57" s="9" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H57" s="7" t="e">
-        <f>+H55-H56</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I57" s="8" t="e">
-        <f t="shared" ref="I57:J57" si="8">+I55-I56</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J57" s="9" t="e">
-        <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="130" t="s">
-        <v>26</v>
-      </c>
-      <c r="B58" s="130"/>
-      <c r="C58">
-        <v>100</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="F48" s="115"/>
+      <c r="G48" s="115"/>
+      <c r="H48" s="116"/>
+      <c r="I48" s="100"/>
+      <c r="J48" s="101"/>
     </row>
   </sheetData>
-  <mergeCells count="65">
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A58:B58"/>
+  <mergeCells count="57">
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="F44:H44"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="F45:H45"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="I40:J48"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="A48:D48"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A25:B26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="A31:B31"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A5:B6"/>
     <mergeCell ref="C22:D22"/>
@@ -4151,92 +3520,40 @@
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="E53:G53"/>
-    <mergeCell ref="H53:J53"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="I40:J48"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="A43:D43"/>
-    <mergeCell ref="A53:B54"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A25:B26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:G25"/>
-    <mergeCell ref="A48:D48"/>
-    <mergeCell ref="F48:H48"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="F44:H44"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="F45:H45"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="A47:D47"/>
-    <mergeCell ref="F47:H47"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A31:B31"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="E17 G17 I17">
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="lessThan">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="4" operator="greaterThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="greaterThan">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="greaterThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="9" operator="greaterThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E18 G18 I18">
-    <cfRule type="cellIs" dxfId="0" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="lessThan">
+      <formula>0.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThanOrEqual">
+      <formula>0.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="7" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="1" priority="10" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="11" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="0" priority="11" operator="lessThanOrEqual">
       <formula>0.5</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThanOrEqual">
-      <formula>0.5</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="lessThan">
-      <formula>0.5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E17 G17 I17">
-    <cfRule type="cellIs" dxfId="20" priority="5" operator="greaterThan">
-      <formula>60</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="6" operator="greaterThanOrEqual">
-      <formula>60</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="8" operator="lessThan">
-      <formula>60</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="9" operator="greaterThanOrEqual">
-      <formula>60</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="4" operator="greaterThanOrEqual">
-      <formula>60</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="3" operator="lessThan">
-      <formula>60</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
@@ -4255,134 +3572,134 @@
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:28" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A4" s="126" t="s">
+        <v>144</v>
+      </c>
+      <c r="B4" s="130" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="132" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A4" s="137" t="s">
+      <c r="D4" s="128" t="s">
         <v>146</v>
       </c>
-      <c r="B4" s="141" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="143" t="s">
+      <c r="E4" s="129"/>
+      <c r="F4" s="120" t="s">
         <v>147</v>
       </c>
-      <c r="D4" s="139" t="s">
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="121"/>
+      <c r="L4" s="121"/>
+      <c r="M4" s="121"/>
+      <c r="N4" s="121"/>
+      <c r="O4" s="121"/>
+      <c r="P4" s="121"/>
+      <c r="Q4" s="122"/>
+      <c r="R4" s="123" t="s">
         <v>148</v>
       </c>
-      <c r="E4" s="140"/>
-      <c r="F4" s="131" t="s">
+      <c r="S4" s="121"/>
+      <c r="T4" s="121"/>
+      <c r="U4" s="121"/>
+      <c r="V4" s="121"/>
+      <c r="W4" s="121"/>
+      <c r="X4" s="121"/>
+      <c r="Y4" s="121"/>
+      <c r="Z4" s="121"/>
+      <c r="AA4" s="121"/>
+      <c r="AB4" s="122"/>
+    </row>
+    <row r="5" spans="1:28" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="127"/>
+      <c r="B5" s="131"/>
+      <c r="C5" s="133"/>
+      <c r="D5" s="48" t="s">
         <v>149</v>
       </c>
-      <c r="G4" s="132"/>
-      <c r="H4" s="132"/>
-      <c r="I4" s="132"/>
-      <c r="J4" s="132"/>
-      <c r="K4" s="132"/>
-      <c r="L4" s="132"/>
-      <c r="M4" s="132"/>
-      <c r="N4" s="132"/>
-      <c r="O4" s="132"/>
-      <c r="P4" s="132"/>
-      <c r="Q4" s="133"/>
-      <c r="R4" s="134" t="s">
+      <c r="E5" s="49" t="s">
         <v>150</v>
       </c>
-      <c r="S4" s="132"/>
-      <c r="T4" s="132"/>
-      <c r="U4" s="132"/>
-      <c r="V4" s="132"/>
-      <c r="W4" s="132"/>
-      <c r="X4" s="132"/>
-      <c r="Y4" s="132"/>
-      <c r="Z4" s="132"/>
-      <c r="AA4" s="132"/>
-      <c r="AB4" s="133"/>
-    </row>
-    <row r="5" spans="1:28" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="138"/>
-      <c r="B5" s="142"/>
-      <c r="C5" s="144"/>
-      <c r="D5" s="48" t="s">
+      <c r="F5" s="48" t="s">
         <v>151</v>
       </c>
-      <c r="E5" s="49" t="s">
+      <c r="G5" s="51" t="s">
         <v>152</v>
       </c>
-      <c r="F5" s="48" t="s">
+      <c r="H5" s="51" t="s">
         <v>153</v>
       </c>
-      <c r="G5" s="51" t="s">
+      <c r="I5" s="51" t="s">
         <v>154</v>
       </c>
-      <c r="H5" s="51" t="s">
+      <c r="J5" s="51" t="s">
         <v>155</v>
       </c>
-      <c r="I5" s="51" t="s">
+      <c r="K5" s="51" t="s">
         <v>156</v>
       </c>
-      <c r="J5" s="51" t="s">
+      <c r="L5" s="51" t="s">
         <v>157</v>
       </c>
-      <c r="K5" s="51" t="s">
+      <c r="M5" s="51" t="s">
         <v>158</v>
       </c>
-      <c r="L5" s="51" t="s">
+      <c r="N5" s="51" t="s">
         <v>159</v>
       </c>
-      <c r="M5" s="51" t="s">
+      <c r="O5" s="51" t="s">
         <v>160</v>
       </c>
-      <c r="N5" s="51" t="s">
+      <c r="P5" s="51" t="s">
         <v>161</v>
       </c>
-      <c r="O5" s="51" t="s">
+      <c r="Q5" s="49" t="s">
         <v>162</v>
       </c>
-      <c r="P5" s="51" t="s">
+      <c r="R5" s="50" t="s">
+        <v>151</v>
+      </c>
+      <c r="S5" s="51" t="s">
+        <v>152</v>
+      </c>
+      <c r="T5" s="51" t="s">
+        <v>153</v>
+      </c>
+      <c r="U5" s="51" t="s">
+        <v>154</v>
+      </c>
+      <c r="V5" s="51" t="s">
+        <v>155</v>
+      </c>
+      <c r="W5" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="X5" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y5" s="51" t="s">
+        <v>158</v>
+      </c>
+      <c r="Z5" s="51" t="s">
+        <v>159</v>
+      </c>
+      <c r="AA5" s="51" t="s">
+        <v>161</v>
+      </c>
+      <c r="AB5" s="49" t="s">
         <v>163</v>
-      </c>
-      <c r="Q5" s="49" t="s">
-        <v>164</v>
-      </c>
-      <c r="R5" s="50" t="s">
-        <v>153</v>
-      </c>
-      <c r="S5" s="51" t="s">
-        <v>154</v>
-      </c>
-      <c r="T5" s="51" t="s">
-        <v>155</v>
-      </c>
-      <c r="U5" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="V5" s="51" t="s">
-        <v>157</v>
-      </c>
-      <c r="W5" s="51" t="s">
-        <v>158</v>
-      </c>
-      <c r="X5" s="51" t="s">
-        <v>159</v>
-      </c>
-      <c r="Y5" s="51" t="s">
-        <v>160</v>
-      </c>
-      <c r="Z5" s="51" t="s">
-        <v>161</v>
-      </c>
-      <c r="AA5" s="51" t="s">
-        <v>163</v>
-      </c>
-      <c r="AB5" s="49" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.3">
@@ -4390,85 +3707,85 @@
         <v>0</v>
       </c>
       <c r="B6" s="44" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D6" s="44" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" s="45" t="s">
+        <v>96</v>
+      </c>
+      <c r="F6" s="44" t="s">
         <v>97</v>
       </c>
-      <c r="E6" s="45" t="s">
+      <c r="G6" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="F6" s="44" t="s">
+      <c r="H6" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="G6" s="47" t="s">
+      <c r="I6" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="H6" s="47" t="s">
+      <c r="J6" s="47" t="s">
         <v>101</v>
       </c>
-      <c r="I6" s="47" t="s">
+      <c r="K6" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="J6" s="47" t="s">
+      <c r="L6" s="47" t="s">
         <v>103</v>
       </c>
-      <c r="K6" s="47" t="s">
+      <c r="M6" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="L6" s="47" t="s">
+      <c r="N6" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="M6" s="47" t="s">
+      <c r="O6" s="47" t="s">
         <v>106</v>
       </c>
-      <c r="N6" s="47" t="s">
+      <c r="P6" s="47" t="s">
         <v>107</v>
       </c>
-      <c r="O6" s="47" t="s">
+      <c r="Q6" s="45" t="s">
         <v>108</v>
       </c>
-      <c r="P6" s="47" t="s">
+      <c r="R6" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="Q6" s="45" t="s">
+      <c r="S6" s="47" t="s">
         <v>110</v>
       </c>
-      <c r="R6" s="46" t="s">
+      <c r="T6" s="47" t="s">
         <v>111</v>
       </c>
-      <c r="S6" s="47" t="s">
+      <c r="U6" s="47" t="s">
         <v>112</v>
       </c>
-      <c r="T6" s="47" t="s">
+      <c r="V6" s="47" t="s">
         <v>113</v>
       </c>
-      <c r="U6" s="47" t="s">
+      <c r="W6" s="47" t="s">
         <v>114</v>
       </c>
-      <c r="V6" s="47" t="s">
+      <c r="X6" s="47" t="s">
         <v>115</v>
       </c>
-      <c r="W6" s="47" t="s">
+      <c r="Y6" s="47" t="s">
         <v>116</v>
       </c>
-      <c r="X6" s="47" t="s">
+      <c r="Z6" s="47" t="s">
         <v>117</v>
       </c>
-      <c r="Y6" s="47" t="s">
+      <c r="AA6" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="Z6" s="47" t="s">
+      <c r="AB6" s="47" t="s">
         <v>119</v>
-      </c>
-      <c r="AA6" s="47" t="s">
-        <v>120</v>
-      </c>
-      <c r="AB6" s="47" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.3">
@@ -5209,103 +4526,103 @@
     </row>
     <row r="31" spans="1:28" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="32" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A32" s="135" t="s">
-        <v>146</v>
-      </c>
-      <c r="B32" s="92" t="s">
-        <v>168</v>
-      </c>
-      <c r="C32" s="94"/>
-      <c r="D32" s="94"/>
-      <c r="E32" s="94"/>
-      <c r="F32" s="94"/>
-      <c r="G32" s="94"/>
-      <c r="H32" s="94"/>
-      <c r="I32" s="94"/>
-      <c r="J32" s="94"/>
-      <c r="K32" s="94"/>
-      <c r="L32" s="93"/>
-      <c r="M32" s="92" t="s">
-        <v>169</v>
-      </c>
-      <c r="N32" s="94"/>
-      <c r="O32" s="94"/>
-      <c r="P32" s="94"/>
-      <c r="Q32" s="94"/>
-      <c r="R32" s="94"/>
-      <c r="S32" s="94"/>
-      <c r="T32" s="94"/>
-      <c r="U32" s="94"/>
-      <c r="V32" s="94"/>
-      <c r="W32" s="93"/>
+      <c r="A32" s="124" t="s">
+        <v>144</v>
+      </c>
+      <c r="B32" s="85" t="s">
+        <v>166</v>
+      </c>
+      <c r="C32" s="87"/>
+      <c r="D32" s="87"/>
+      <c r="E32" s="87"/>
+      <c r="F32" s="87"/>
+      <c r="G32" s="87"/>
+      <c r="H32" s="87"/>
+      <c r="I32" s="87"/>
+      <c r="J32" s="87"/>
+      <c r="K32" s="87"/>
+      <c r="L32" s="86"/>
+      <c r="M32" s="85" t="s">
+        <v>167</v>
+      </c>
+      <c r="N32" s="87"/>
+      <c r="O32" s="87"/>
+      <c r="P32" s="87"/>
+      <c r="Q32" s="87"/>
+      <c r="R32" s="87"/>
+      <c r="S32" s="87"/>
+      <c r="T32" s="87"/>
+      <c r="U32" s="87"/>
+      <c r="V32" s="87"/>
+      <c r="W32" s="86"/>
     </row>
     <row r="33" spans="1:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="136"/>
+      <c r="A33" s="125"/>
       <c r="B33" s="36" t="s">
+        <v>151</v>
+      </c>
+      <c r="C33" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="D33" s="33" t="s">
         <v>153</v>
       </c>
-      <c r="C33" s="33" t="s">
+      <c r="E33" s="33" t="s">
         <v>154</v>
       </c>
-      <c r="D33" s="33" t="s">
+      <c r="F33" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="E33" s="33" t="s">
+      <c r="G33" s="33" t="s">
         <v>156</v>
       </c>
-      <c r="F33" s="33" t="s">
+      <c r="H33" s="33" t="s">
         <v>157</v>
       </c>
-      <c r="G33" s="33" t="s">
+      <c r="I33" s="33" t="s">
         <v>158</v>
       </c>
-      <c r="H33" s="33" t="s">
+      <c r="J33" s="33" t="s">
         <v>159</v>
       </c>
-      <c r="I33" s="33" t="s">
-        <v>160</v>
-      </c>
-      <c r="J33" s="33" t="s">
+      <c r="K33" s="33" t="s">
         <v>161</v>
       </c>
-      <c r="K33" s="33" t="s">
+      <c r="L33" s="34" t="s">
         <v>163</v>
       </c>
-      <c r="L33" s="34" t="s">
-        <v>165</v>
-      </c>
       <c r="M33" s="36" t="s">
+        <v>151</v>
+      </c>
+      <c r="N33" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="O33" s="33" t="s">
         <v>153</v>
       </c>
-      <c r="N33" s="33" t="s">
+      <c r="P33" s="33" t="s">
         <v>154</v>
       </c>
-      <c r="O33" s="33" t="s">
+      <c r="Q33" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="P33" s="33" t="s">
+      <c r="R33" s="33" t="s">
         <v>156</v>
       </c>
-      <c r="Q33" s="33" t="s">
+      <c r="S33" s="33" t="s">
         <v>157</v>
       </c>
-      <c r="R33" s="33" t="s">
+      <c r="T33" s="33" t="s">
         <v>158</v>
       </c>
-      <c r="S33" s="33" t="s">
+      <c r="U33" s="33" t="s">
         <v>159</v>
       </c>
-      <c r="T33" s="33" t="s">
-        <v>160</v>
-      </c>
-      <c r="U33" s="33" t="s">
+      <c r="V33" s="33" t="s">
         <v>161</v>
       </c>
-      <c r="V33" s="33" t="s">
+      <c r="W33" s="34" t="s">
         <v>163</v>
-      </c>
-      <c r="W33" s="34" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.3">
@@ -5313,70 +4630,70 @@
         <v>0</v>
       </c>
       <c r="B34" s="37" t="s">
+        <v>120</v>
+      </c>
+      <c r="C34" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="D34" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="C34" s="32" t="s">
+      <c r="E34" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="D34" s="32" t="s">
+      <c r="F34" s="32" t="s">
         <v>124</v>
       </c>
-      <c r="E34" s="32" t="s">
+      <c r="G34" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="F34" s="32" t="s">
+      <c r="H34" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="G34" s="32" t="s">
+      <c r="I34" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="H34" s="32" t="s">
+      <c r="J34" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="I34" s="32" t="s">
+      <c r="K34" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="J34" s="32" t="s">
+      <c r="L34" s="38" t="s">
         <v>130</v>
       </c>
-      <c r="K34" s="32" t="s">
+      <c r="M34" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="L34" s="38" t="s">
+      <c r="N34" s="32" t="s">
         <v>132</v>
       </c>
-      <c r="M34" s="37" t="s">
+      <c r="O34" s="32" t="s">
         <v>133</v>
       </c>
-      <c r="N34" s="32" t="s">
+      <c r="P34" s="32" t="s">
         <v>134</v>
       </c>
-      <c r="O34" s="32" t="s">
+      <c r="Q34" s="32" t="s">
         <v>135</v>
       </c>
-      <c r="P34" s="32" t="s">
+      <c r="R34" s="32" t="s">
         <v>136</v>
       </c>
-      <c r="Q34" s="32" t="s">
+      <c r="S34" s="32" t="s">
         <v>137</v>
       </c>
-      <c r="R34" s="32" t="s">
+      <c r="T34" s="32" t="s">
         <v>138</v>
       </c>
-      <c r="S34" s="32" t="s">
+      <c r="U34" s="32" t="s">
         <v>139</v>
       </c>
-      <c r="T34" s="32" t="s">
+      <c r="V34" s="32" t="s">
         <v>140</v>
       </c>
-      <c r="U34" s="32" t="s">
+      <c r="W34" s="38" t="s">
         <v>141</v>
-      </c>
-      <c r="V34" s="32" t="s">
-        <v>142</v>
-      </c>
-      <c r="W34" s="38" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="35" spans="1:23" x14ac:dyDescent="0.3">

--- a/elec_room_project/template_전기실_운영일지.xlsx
+++ b/elec_room_project/template_전기실_운영일지.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\pygame\pygame\elec_room_project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\elec_room_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8723E4EA-BEF9-47B6-97D9-2351AB286FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA5D9837-3051-456D-8789-5F5BD9F3FBCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{943AB7D1-EB27-49C3-9C36-555299583416}"/>
+    <workbookView xWindow="210" yWindow="315" windowWidth="18345" windowHeight="14295" xr2:uid="{943AB7D1-EB27-49C3-9C36-555299583416}"/>
   </bookViews>
   <sheets>
     <sheet name="전력설비_운전현황" sheetId="4" r:id="rId1"/>
@@ -24,12 +24,21 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="271">
   <si>
     <t>실내온도</t>
   </si>
@@ -723,17 +732,10 @@
     <t>점 검 사 항</t>
   </si>
   <si>
-    <t>결 과</t>
-  </si>
-  <si>
     <t>비     고</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">기타 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1. VCB, ACB, MCCB 등 차단기 이상 유무</t>
   </si>
   <si>
@@ -864,6 +866,30 @@
   </si>
   <si>
     <t>전일("geo_1")</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1차 점검</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2차 점검</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3차 점검</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>점검 결과</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1차("점검자)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1("점검시간")</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -874,7 +900,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -996,6 +1022,13 @@
       <charset val="129"/>
       <scheme val="major"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1011,7 +1044,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="44">
+  <borders count="43">
     <border>
       <left/>
       <right/>
@@ -1289,19 +1322,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -1323,64 +1343,6 @@
       </right>
       <top/>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1586,13 +1548,61 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="134">
+  <cellXfs count="140">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1657,28 +1667,16 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1702,33 +1700,33 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1741,7 +1739,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1765,7 +1763,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1784,10 +1782,58 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -1796,25 +1842,19 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1832,158 +1872,146 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2424,15 +2452,15 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="86.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="65" t="s">
+      <c r="A2" s="78" t="s">
         <v>168</v>
       </c>
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
       <c r="H2" s="7"/>
       <c r="I2" s="8"/>
       <c r="J2" s="9"/>
@@ -2441,8 +2469,8 @@
       <c r="A3" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B3" s="64"/>
-      <c r="C3" s="64"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="60"/>
       <c r="D3" s="2" t="s">
         <v>170</v>
       </c>
@@ -2456,30 +2484,30 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="66" t="s">
+      <c r="A5" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="67"/>
-      <c r="C5" s="66" t="s">
+      <c r="B5" s="79"/>
+      <c r="C5" s="69" t="s">
         <v>173</v>
       </c>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66" t="s">
+      <c r="D5" s="69"/>
+      <c r="E5" s="69" t="s">
         <v>174</v>
       </c>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66" t="s">
+      <c r="F5" s="69"/>
+      <c r="G5" s="69" t="s">
         <v>175</v>
       </c>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66" t="s">
+      <c r="H5" s="69"/>
+      <c r="I5" s="69" t="s">
         <v>176</v>
       </c>
-      <c r="J5" s="66"/>
+      <c r="J5" s="69"/>
     </row>
     <row r="6" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="68"/>
-      <c r="B6" s="69"/>
+      <c r="A6" s="80"/>
+      <c r="B6" s="81"/>
       <c r="C6" s="10" t="s">
         <v>177</v>
       </c>
@@ -2506,278 +2534,278 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="66" t="s">
+      <c r="A7" s="69" t="s">
         <v>179</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="C7" s="52" t="s">
+      <c r="C7" s="48" t="s">
         <v>181</v>
       </c>
-      <c r="D7" s="52" t="s">
+      <c r="D7" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="52" t="s">
+      <c r="E7" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="52" t="s">
+      <c r="F7" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="G7" s="52" t="s">
+      <c r="G7" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="52" t="s">
+      <c r="H7" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="I7" s="52" t="s">
+      <c r="I7" s="48" t="s">
         <v>75</v>
       </c>
-      <c r="J7" s="52" t="s">
+      <c r="J7" s="48" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="66"/>
+      <c r="A8" s="69"/>
       <c r="B8" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="C8" s="52" t="s">
+      <c r="C8" s="48" t="s">
         <v>183</v>
       </c>
-      <c r="D8" s="52" t="s">
+      <c r="D8" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="52" t="s">
+      <c r="E8" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="F8" s="52" t="s">
+      <c r="F8" s="48" t="s">
         <v>38</v>
       </c>
-      <c r="G8" s="52" t="s">
+      <c r="G8" s="48" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="52" t="s">
+      <c r="H8" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="I8" s="52" t="s">
+      <c r="I8" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="J8" s="52" t="s">
+      <c r="J8" s="48" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="66"/>
+      <c r="A9" s="69"/>
       <c r="B9" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="C9" s="52" t="s">
+      <c r="C9" s="48" t="s">
         <v>185</v>
       </c>
-      <c r="D9" s="52" t="s">
+      <c r="D9" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="52" t="s">
+      <c r="E9" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="52" t="s">
+      <c r="F9" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="G9" s="52" t="s">
+      <c r="G9" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="H9" s="52" t="s">
+      <c r="H9" s="48" t="s">
         <v>60</v>
       </c>
-      <c r="I9" s="52" t="s">
+      <c r="I9" s="48" t="s">
         <v>79</v>
       </c>
-      <c r="J9" s="52" t="s">
+      <c r="J9" s="48" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="66" t="s">
+      <c r="A10" s="69" t="s">
         <v>186</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="C10" s="52" t="s">
+      <c r="C10" s="48" t="s">
         <v>188</v>
       </c>
-      <c r="D10" s="52" t="s">
+      <c r="D10" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="52" t="s">
+      <c r="E10" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="F10" s="52" t="s">
+      <c r="F10" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="G10" s="52" t="s">
+      <c r="G10" s="48" t="s">
         <v>61</v>
       </c>
-      <c r="H10" s="52" t="s">
+      <c r="H10" s="48" t="s">
         <v>62</v>
       </c>
-      <c r="I10" s="52" t="s">
+      <c r="I10" s="48" t="s">
         <v>81</v>
       </c>
-      <c r="J10" s="52" t="s">
+      <c r="J10" s="48" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="66"/>
+      <c r="A11" s="69"/>
       <c r="B11" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="C11" s="52" t="s">
+      <c r="C11" s="48" t="s">
         <v>190</v>
       </c>
-      <c r="D11" s="52" t="s">
+      <c r="D11" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="52" t="s">
+      <c r="E11" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="F11" s="52" t="s">
+      <c r="F11" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="G11" s="52" t="s">
+      <c r="G11" s="48" t="s">
         <v>63</v>
       </c>
-      <c r="H11" s="52" t="s">
+      <c r="H11" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="I11" s="52" t="s">
+      <c r="I11" s="48" t="s">
         <v>83</v>
       </c>
-      <c r="J11" s="52" t="s">
+      <c r="J11" s="48" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="66"/>
+      <c r="A12" s="69"/>
       <c r="B12" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="C12" s="52" t="s">
+      <c r="C12" s="48" t="s">
         <v>192</v>
       </c>
-      <c r="D12" s="52" t="s">
+      <c r="D12" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="52" t="s">
+      <c r="E12" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="F12" s="52" t="s">
+      <c r="F12" s="48" t="s">
         <v>46</v>
       </c>
-      <c r="G12" s="52" t="s">
+      <c r="G12" s="48" t="s">
         <v>65</v>
       </c>
-      <c r="H12" s="52" t="s">
+      <c r="H12" s="48" t="s">
         <v>66</v>
       </c>
-      <c r="I12" s="52" t="s">
+      <c r="I12" s="48" t="s">
         <v>85</v>
       </c>
-      <c r="J12" s="52" t="s">
+      <c r="J12" s="48" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="66" t="s">
+      <c r="A13" s="69" t="s">
         <v>193</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="C13" s="52" t="s">
+      <c r="C13" s="48" t="s">
         <v>194</v>
       </c>
-      <c r="D13" s="52" t="s">
+      <c r="D13" s="48" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="52" t="s">
+      <c r="E13" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="52" t="s">
+      <c r="F13" s="48" t="s">
         <v>48</v>
       </c>
-      <c r="G13" s="52" t="s">
+      <c r="G13" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="H13" s="52" t="s">
+      <c r="H13" s="48" t="s">
         <v>68</v>
       </c>
-      <c r="I13" s="52" t="s">
+      <c r="I13" s="48" t="s">
         <v>87</v>
       </c>
-      <c r="J13" s="52" t="s">
+      <c r="J13" s="48" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="66"/>
+      <c r="A14" s="69"/>
       <c r="B14" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="C14" s="52" t="s">
+      <c r="C14" s="48" t="s">
         <v>195</v>
       </c>
-      <c r="D14" s="52" t="s">
+      <c r="D14" s="48" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="52" t="s">
+      <c r="E14" s="48" t="s">
         <v>49</v>
       </c>
-      <c r="F14" s="52" t="s">
+      <c r="F14" s="48" t="s">
         <v>50</v>
       </c>
-      <c r="G14" s="52" t="s">
+      <c r="G14" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="H14" s="52" t="s">
+      <c r="H14" s="48" t="s">
         <v>70</v>
       </c>
-      <c r="I14" s="52" t="s">
+      <c r="I14" s="48" t="s">
         <v>89</v>
       </c>
-      <c r="J14" s="52" t="s">
+      <c r="J14" s="48" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="66"/>
+      <c r="A15" s="69"/>
       <c r="B15" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="C15" s="52" t="s">
+      <c r="C15" s="48" t="s">
         <v>196</v>
       </c>
-      <c r="D15" s="52" t="s">
+      <c r="D15" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="E15" s="52" t="s">
+      <c r="E15" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="F15" s="52" t="s">
+      <c r="F15" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="G15" s="52" t="s">
+      <c r="G15" s="48" t="s">
         <v>71</v>
       </c>
-      <c r="H15" s="52" t="s">
+      <c r="H15" s="48" t="s">
         <v>72</v>
       </c>
-      <c r="I15" s="52" t="s">
+      <c r="I15" s="48" t="s">
         <v>91</v>
       </c>
-      <c r="J15" s="52" t="s">
+      <c r="J15" s="48" t="s">
         <v>92</v>
       </c>
     </row>
@@ -2788,85 +2816,85 @@
       <c r="B16" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="C16" s="52" t="s">
+      <c r="C16" s="48" t="s">
         <v>198</v>
       </c>
-      <c r="D16" s="52" t="s">
+      <c r="D16" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="E16" s="52" t="s">
+      <c r="E16" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="52" t="s">
+      <c r="F16" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="G16" s="52" t="s">
+      <c r="G16" s="48" t="s">
         <v>73</v>
       </c>
-      <c r="H16" s="52" t="s">
+      <c r="H16" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="I16" s="52" t="s">
+      <c r="I16" s="48" t="s">
         <v>93</v>
       </c>
-      <c r="J16" s="52" t="s">
+      <c r="J16" s="48" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="83" t="s">
+      <c r="A17" s="72" t="s">
         <v>199</v>
       </c>
-      <c r="B17" s="84"/>
-      <c r="C17" s="52"/>
-      <c r="D17" s="52"/>
-      <c r="E17" s="52" t="s">
+      <c r="B17" s="73"/>
+      <c r="C17" s="48"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="48" t="s">
         <v>200</v>
       </c>
-      <c r="F17" s="52" t="s">
+      <c r="F17" s="48" t="s">
         <v>201</v>
       </c>
-      <c r="G17" s="52" t="s">
+      <c r="G17" s="48" t="s">
         <v>202</v>
       </c>
-      <c r="H17" s="52" t="s">
+      <c r="H17" s="48" t="s">
         <v>203</v>
       </c>
-      <c r="I17" s="52" t="s">
+      <c r="I17" s="48" t="s">
         <v>204</v>
       </c>
-      <c r="J17" s="52" t="s">
+      <c r="J17" s="48" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="105" t="s">
+      <c r="A18" s="74" t="s">
         <v>222</v>
       </c>
-      <c r="B18" s="105"/>
-      <c r="C18" s="52"/>
-      <c r="D18" s="52"/>
-      <c r="E18" s="53" t="e">
+      <c r="B18" s="74"/>
+      <c r="C18" s="48"/>
+      <c r="D18" s="48"/>
+      <c r="E18" s="49" t="e">
         <f>+E16/1000</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F18" s="54" t="e">
+      <c r="F18" s="50" t="e">
         <f>+F16/1000</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G18" s="53" t="e">
+      <c r="G18" s="49" t="e">
         <f>+G16/1250</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H18" s="54" t="e">
+      <c r="H18" s="50" t="e">
         <f t="shared" ref="H18:J18" si="0">+H16/1250</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I18" s="53" t="e">
+      <c r="I18" s="49" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="J18" s="54" t="e">
+      <c r="J18" s="50" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -2877,60 +2905,60 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="79" t="s">
+      <c r="A20" s="89" t="s">
         <v>207</v>
       </c>
-      <c r="B20" s="75"/>
-      <c r="C20" s="75" t="s">
+      <c r="B20" s="85"/>
+      <c r="C20" s="85" t="s">
         <v>208</v>
       </c>
-      <c r="D20" s="75"/>
-      <c r="E20" s="76" t="s">
+      <c r="D20" s="85"/>
+      <c r="E20" s="86" t="s">
         <v>209</v>
       </c>
-      <c r="F20" s="77"/>
-      <c r="G20" s="75" t="s">
+      <c r="F20" s="87"/>
+      <c r="G20" s="85" t="s">
         <v>210</v>
       </c>
-      <c r="H20" s="78"/>
+      <c r="H20" s="88"/>
     </row>
     <row r="21" spans="1:10" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="80" t="s">
+      <c r="A21" s="90" t="s">
         <v>211</v>
       </c>
-      <c r="B21" s="66"/>
-      <c r="C21" s="71" t="s">
+      <c r="B21" s="69"/>
+      <c r="C21" s="62" t="s">
         <v>221</v>
       </c>
-      <c r="D21" s="71"/>
-      <c r="E21" s="112" t="s">
+      <c r="D21" s="62"/>
+      <c r="E21" s="70" t="s">
         <v>212</v>
       </c>
-      <c r="F21" s="113"/>
-      <c r="G21" s="71" t="e">
+      <c r="F21" s="71"/>
+      <c r="G21" s="62" t="e">
         <f>E21-C21</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H21" s="72"/>
+      <c r="H21" s="83"/>
     </row>
     <row r="22" spans="1:10" ht="35.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="81" t="s">
+      <c r="A22" s="91" t="s">
         <v>213</v>
       </c>
-      <c r="B22" s="82"/>
-      <c r="C22" s="70" t="s">
-        <v>238</v>
-      </c>
-      <c r="D22" s="70"/>
-      <c r="E22" s="70" t="s">
-        <v>239</v>
-      </c>
-      <c r="F22" s="70"/>
-      <c r="G22" s="73" t="e">
+      <c r="B22" s="92"/>
+      <c r="C22" s="82" t="s">
+        <v>236</v>
+      </c>
+      <c r="D22" s="82"/>
+      <c r="E22" s="82" t="s">
+        <v>237</v>
+      </c>
+      <c r="F22" s="82"/>
+      <c r="G22" s="64" t="e">
         <f>+E22-C22</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H22" s="74"/>
+      <c r="H22" s="84"/>
     </row>
     <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="24" spans="1:10" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -2939,322 +2967,322 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="106" t="s">
+      <c r="A25" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="B25" s="107"/>
-      <c r="C25" s="107" t="s">
+      <c r="B25" s="67"/>
+      <c r="C25" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="107"/>
-      <c r="E25" s="107" t="s">
+      <c r="D25" s="67"/>
+      <c r="E25" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="F25" s="107"/>
-      <c r="G25" s="107"/>
-      <c r="H25" s="107" t="s">
+      <c r="F25" s="67"/>
+      <c r="G25" s="67"/>
+      <c r="H25" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="I25" s="107"/>
-      <c r="J25" s="111"/>
+      <c r="I25" s="67"/>
+      <c r="J25" s="68"/>
     </row>
     <row r="26" spans="1:10" ht="35.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="108"/>
-      <c r="B26" s="109"/>
-      <c r="C26" s="57" t="s">
+      <c r="A26" s="76"/>
+      <c r="B26" s="77"/>
+      <c r="C26" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="D26" s="57" t="s">
+      <c r="D26" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="E26" s="57" t="s">
+      <c r="E26" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="F26" s="57" t="s">
+      <c r="F26" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="G26" s="57" t="s">
+      <c r="G26" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="H26" s="57" t="s">
+      <c r="H26" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="I26" s="57" t="s">
+      <c r="I26" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="J26" s="58" t="s">
+      <c r="J26" s="54" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="106" t="s">
+      <c r="A27" s="75" t="s">
+        <v>238</v>
+      </c>
+      <c r="B27" s="67"/>
+      <c r="C27" s="57" t="s">
+        <v>239</v>
+      </c>
+      <c r="D27" s="57" t="s">
         <v>240</v>
       </c>
-      <c r="B27" s="107"/>
-      <c r="C27" s="61" t="s">
+      <c r="E27" s="57" t="s">
         <v>241</v>
       </c>
-      <c r="D27" s="61" t="s">
+      <c r="F27" s="57" t="s">
         <v>242</v>
       </c>
-      <c r="E27" s="61" t="s">
+      <c r="G27" s="57" t="s">
         <v>243</v>
       </c>
-      <c r="F27" s="61" t="s">
+      <c r="H27" s="57" t="s">
         <v>244</v>
       </c>
-      <c r="G27" s="61" t="s">
+      <c r="I27" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="H27" s="61" t="s">
+      <c r="J27" s="58" t="s">
         <v>246</v>
       </c>
-      <c r="I27" s="61" t="s">
+    </row>
+    <row r="28" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="61" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" s="62"/>
+      <c r="C28" s="48" t="s">
+        <v>255</v>
+      </c>
+      <c r="D28" s="48" t="s">
+        <v>256</v>
+      </c>
+      <c r="E28" s="48" t="s">
+        <v>257</v>
+      </c>
+      <c r="F28" s="48" t="s">
+        <v>258</v>
+      </c>
+      <c r="G28" s="48" t="s">
+        <v>259</v>
+      </c>
+      <c r="H28" s="48" t="s">
+        <v>260</v>
+      </c>
+      <c r="I28" s="48" t="s">
+        <v>261</v>
+      </c>
+      <c r="J28" s="59" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="61" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" s="62"/>
+      <c r="C29" s="48" t="s">
         <v>247</v>
       </c>
-      <c r="J27" s="62" t="s">
+      <c r="D29" s="48" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="110" t="s">
-        <v>12</v>
-      </c>
-      <c r="B28" s="71"/>
-      <c r="C28" s="52" t="s">
-        <v>257</v>
-      </c>
-      <c r="D28" s="52" t="s">
-        <v>258</v>
-      </c>
-      <c r="E28" s="52" t="s">
-        <v>259</v>
-      </c>
-      <c r="F28" s="52" t="s">
-        <v>260</v>
-      </c>
-      <c r="G28" s="52" t="s">
-        <v>261</v>
-      </c>
-      <c r="H28" s="52" t="s">
-        <v>262</v>
-      </c>
-      <c r="I28" s="52" t="s">
-        <v>263</v>
-      </c>
-      <c r="J28" s="63" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="110" t="s">
-        <v>13</v>
-      </c>
-      <c r="B29" s="71"/>
-      <c r="C29" s="52" t="s">
+      <c r="E29" s="48" t="s">
         <v>249</v>
       </c>
-      <c r="D29" s="52" t="s">
+      <c r="F29" s="48" t="s">
         <v>250</v>
       </c>
-      <c r="E29" s="52" t="s">
+      <c r="G29" s="48" t="s">
         <v>251</v>
       </c>
-      <c r="F29" s="52" t="s">
+      <c r="H29" s="48" t="s">
         <v>252</v>
       </c>
-      <c r="G29" s="52" t="s">
+      <c r="I29" s="48" t="s">
         <v>253</v>
       </c>
-      <c r="H29" s="52" t="s">
+      <c r="J29" s="59" t="s">
         <v>254</v>
       </c>
-      <c r="I29" s="52" t="s">
-        <v>255</v>
-      </c>
-      <c r="J29" s="63" t="s">
-        <v>256</v>
-      </c>
     </row>
     <row r="30" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="110" t="s">
+      <c r="A30" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="B30" s="71"/>
-      <c r="C30" s="55" t="e">
+      <c r="B30" s="62"/>
+      <c r="C30" s="51" t="e">
         <f>+C28-C29</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D30" s="55" t="e">
+      <c r="D30" s="51" t="e">
         <f t="shared" ref="D30:J30" si="1">+D28-D29</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E30" s="55" t="e">
+      <c r="E30" s="51" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F30" s="55" t="e">
+      <c r="F30" s="51" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="G30" s="55" t="e">
+      <c r="G30" s="51" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H30" s="55" t="e">
+      <c r="H30" s="51" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="I30" s="55" t="e">
+      <c r="I30" s="51" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="J30" s="56" t="e">
+      <c r="J30" s="52" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="110" t="s">
+      <c r="A31" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="71"/>
-      <c r="C31" s="55" t="e">
+      <c r="B31" s="62"/>
+      <c r="C31" s="51" t="e">
         <f>+C30*2400</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D31" s="55" t="e">
+      <c r="D31" s="51" t="e">
         <f>+D30*2400</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E31" s="55" t="e">
+      <c r="E31" s="51" t="e">
         <f>E30*80</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F31" s="55" t="e">
+      <c r="F31" s="51" t="e">
         <f t="shared" ref="F31:G31" si="2">F30*80</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G31" s="55" t="e">
+      <c r="G31" s="51" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H31" s="55" t="e">
+      <c r="H31" s="51" t="e">
         <f>+H30</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I31" s="55" t="e">
+      <c r="I31" s="51" t="e">
         <f t="shared" ref="I31:J31" si="3">+I30</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J31" s="56" t="e">
+      <c r="J31" s="52" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="110" t="s">
+      <c r="A32" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="B32" s="71"/>
-      <c r="C32" s="55" t="e">
+      <c r="B32" s="62"/>
+      <c r="C32" s="51" t="e">
         <f>(C28-C27)*2400</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D32" s="55" t="e">
+      <c r="D32" s="51" t="e">
         <f>(D28-D27)*2400</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E32" s="55" t="e">
+      <c r="E32" s="51" t="e">
         <f>(E28-E27)*80</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F32" s="55" t="e">
+      <c r="F32" s="51" t="e">
         <f t="shared" ref="F32:G32" si="4">(F28-F27)*80</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G32" s="55" t="e">
+      <c r="G32" s="51" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H32" s="55" t="e">
+      <c r="H32" s="51" t="e">
         <f>H28-H27</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I32" s="55" t="e">
+      <c r="I32" s="51" t="e">
         <f t="shared" ref="I32:J32" si="5">I28-I27</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J32" s="56" t="e">
+      <c r="J32" s="52" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="33" spans="1:17" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="117" t="s">
+      <c r="A33" s="63" t="s">
         <v>17</v>
       </c>
-      <c r="B33" s="73"/>
+      <c r="B33" s="64"/>
       <c r="C33" s="14" t="e">
         <f>C30/(SQRT(C30^2+D30^2*100))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D33" s="60"/>
-      <c r="E33" s="60"/>
-      <c r="F33" s="60"/>
+      <c r="D33" s="56"/>
+      <c r="E33" s="56"/>
+      <c r="F33" s="56"/>
       <c r="G33" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="H33" s="30" t="s">
+      <c r="H33" s="26" t="s">
         <v>215</v>
       </c>
-      <c r="I33" s="30" t="s">
+      <c r="I33" s="26" t="s">
         <v>216</v>
       </c>
-      <c r="J33" s="31" t="s">
+      <c r="J33" s="27" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="34" spans="1:17" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="118" t="s">
+      <c r="A34" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="B34" s="119"/>
-      <c r="C34" s="26"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
+      <c r="B34" s="66"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
       <c r="F34" s="17"/>
-      <c r="G34" s="59" t="s">
+      <c r="G34" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="H34" s="28" t="s">
-        <v>265</v>
-      </c>
-      <c r="I34" s="28" t="s">
-        <v>265</v>
-      </c>
-      <c r="J34" s="29" t="s">
-        <v>265</v>
+      <c r="H34" s="24" t="s">
+        <v>263</v>
+      </c>
+      <c r="I34" s="24" t="s">
+        <v>263</v>
+      </c>
+      <c r="J34" s="25" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="16"/>
-      <c r="B35" s="26"/>
-      <c r="C35" s="26"/>
-      <c r="D35" s="26"/>
-      <c r="E35" s="26"/>
+      <c r="B35" s="22"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="22"/>
       <c r="F35" s="17"/>
       <c r="G35" s="12" t="s">
         <v>21</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="J35" s="13" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="36" spans="1:17" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -3264,7 +3292,7 @@
       <c r="D36" s="19"/>
       <c r="E36" s="19"/>
       <c r="F36" s="20"/>
-      <c r="G36" s="27" t="s">
+      <c r="G36" s="23" t="s">
         <v>22</v>
       </c>
       <c r="H36" s="14" t="e">
@@ -3295,218 +3323,198 @@
       <c r="J38" s="21"/>
     </row>
     <row r="39" spans="1:17" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="88" t="s">
+      <c r="A39" s="122" t="s">
         <v>224</v>
       </c>
-      <c r="B39" s="89"/>
-      <c r="C39" s="89"/>
-      <c r="D39" s="89"/>
-      <c r="E39" s="25" t="s">
+      <c r="B39" s="123"/>
+      <c r="C39" s="123"/>
+      <c r="D39" s="124"/>
+      <c r="E39" s="125" t="s">
+        <v>265</v>
+      </c>
+      <c r="F39" s="126" t="s">
+        <v>266</v>
+      </c>
+      <c r="G39" s="127" t="s">
+        <v>267</v>
+      </c>
+      <c r="H39" s="128" t="s">
+        <v>268</v>
+      </c>
+      <c r="I39" s="129" t="s">
         <v>225</v>
       </c>
-      <c r="F39" s="89" t="s">
-        <v>226</v>
-      </c>
-      <c r="G39" s="89"/>
-      <c r="H39" s="90"/>
-      <c r="I39" s="91" t="s">
-        <v>227</v>
-      </c>
-      <c r="J39" s="92"/>
+      <c r="J39" s="130"/>
       <c r="Q39" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="93" t="s">
+      <c r="A40" s="131" t="s">
+        <v>226</v>
+      </c>
+      <c r="B40" s="132"/>
+      <c r="C40" s="132"/>
+      <c r="D40" s="133"/>
+      <c r="E40" s="137" t="s">
+        <v>269</v>
+      </c>
+      <c r="F40" s="137" t="s">
+        <v>269</v>
+      </c>
+      <c r="G40" s="137" t="s">
+        <v>269</v>
+      </c>
+      <c r="H40" s="134" t="s">
+        <v>227</v>
+      </c>
+      <c r="I40" s="135"/>
+      <c r="J40" s="136"/>
+    </row>
+    <row r="41" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="110" t="s">
         <v>228</v>
       </c>
-      <c r="B40" s="94"/>
-      <c r="C40" s="94"/>
-      <c r="D40" s="94"/>
-      <c r="E40" s="24" t="s">
+      <c r="B41" s="111"/>
+      <c r="C41" s="111"/>
+      <c r="D41" s="116"/>
+      <c r="E41" s="138"/>
+      <c r="F41" s="138"/>
+      <c r="G41" s="138"/>
+      <c r="H41" s="120" t="s">
+        <v>227</v>
+      </c>
+      <c r="I41" s="118"/>
+      <c r="J41" s="114"/>
+    </row>
+    <row r="42" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="110" t="s">
         <v>229</v>
       </c>
-      <c r="F40" s="94"/>
-      <c r="G40" s="94"/>
-      <c r="H40" s="95"/>
-      <c r="I40" s="96"/>
-      <c r="J40" s="97"/>
-    </row>
-    <row r="41" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="102" t="s">
+      <c r="B42" s="111"/>
+      <c r="C42" s="111"/>
+      <c r="D42" s="116"/>
+      <c r="E42" s="138"/>
+      <c r="F42" s="138"/>
+      <c r="G42" s="138"/>
+      <c r="H42" s="120" t="s">
+        <v>227</v>
+      </c>
+      <c r="I42" s="118"/>
+      <c r="J42" s="114"/>
+    </row>
+    <row r="43" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="110" t="s">
         <v>230</v>
       </c>
-      <c r="B41" s="103"/>
-      <c r="C41" s="103"/>
-      <c r="D41" s="103"/>
-      <c r="E41" s="22" t="s">
-        <v>229</v>
-      </c>
-      <c r="F41" s="103"/>
-      <c r="G41" s="103"/>
-      <c r="H41" s="104"/>
-      <c r="I41" s="98"/>
-      <c r="J41" s="99"/>
-    </row>
-    <row r="42" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="102" t="s">
+      <c r="B43" s="111"/>
+      <c r="C43" s="111"/>
+      <c r="D43" s="116"/>
+      <c r="E43" s="138"/>
+      <c r="F43" s="138"/>
+      <c r="G43" s="138"/>
+      <c r="H43" s="120" t="s">
+        <v>227</v>
+      </c>
+      <c r="I43" s="118"/>
+      <c r="J43" s="114"/>
+    </row>
+    <row r="44" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="110" t="s">
         <v>231</v>
       </c>
-      <c r="B42" s="103"/>
-      <c r="C42" s="103"/>
-      <c r="D42" s="103"/>
-      <c r="E42" s="22" t="s">
-        <v>229</v>
-      </c>
-      <c r="F42" s="103"/>
-      <c r="G42" s="103"/>
-      <c r="H42" s="104"/>
-      <c r="I42" s="98"/>
-      <c r="J42" s="99"/>
-    </row>
-    <row r="43" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="102" t="s">
+      <c r="B44" s="111"/>
+      <c r="C44" s="111"/>
+      <c r="D44" s="116"/>
+      <c r="E44" s="138"/>
+      <c r="F44" s="138"/>
+      <c r="G44" s="138"/>
+      <c r="H44" s="120" t="s">
+        <v>227</v>
+      </c>
+      <c r="I44" s="118"/>
+      <c r="J44" s="114"/>
+    </row>
+    <row r="45" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="110" t="s">
         <v>232</v>
       </c>
-      <c r="B43" s="103"/>
-      <c r="C43" s="103"/>
-      <c r="D43" s="103"/>
-      <c r="E43" s="22" t="s">
-        <v>229</v>
-      </c>
-      <c r="F43" s="103"/>
-      <c r="G43" s="103"/>
-      <c r="H43" s="104"/>
-      <c r="I43" s="98"/>
-      <c r="J43" s="99"/>
-    </row>
-    <row r="44" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="102" t="s">
+      <c r="B45" s="111"/>
+      <c r="C45" s="111"/>
+      <c r="D45" s="116"/>
+      <c r="E45" s="138" t="s">
+        <v>270</v>
+      </c>
+      <c r="F45" s="138" t="s">
+        <v>270</v>
+      </c>
+      <c r="G45" s="138" t="s">
+        <v>270</v>
+      </c>
+      <c r="H45" s="120" t="s">
+        <v>227</v>
+      </c>
+      <c r="I45" s="118"/>
+      <c r="J45" s="114"/>
+    </row>
+    <row r="46" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="110" t="s">
         <v>233</v>
       </c>
-      <c r="B44" s="103"/>
-      <c r="C44" s="103"/>
-      <c r="D44" s="103"/>
-      <c r="E44" s="22" t="s">
-        <v>229</v>
-      </c>
-      <c r="F44" s="103"/>
-      <c r="G44" s="103"/>
-      <c r="H44" s="104"/>
-      <c r="I44" s="98"/>
-      <c r="J44" s="99"/>
-    </row>
-    <row r="45" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="102" t="s">
+      <c r="B46" s="111"/>
+      <c r="C46" s="111"/>
+      <c r="D46" s="116"/>
+      <c r="E46" s="138"/>
+      <c r="F46" s="138"/>
+      <c r="G46" s="138"/>
+      <c r="H46" s="120" t="s">
+        <v>227</v>
+      </c>
+      <c r="I46" s="118"/>
+      <c r="J46" s="114"/>
+    </row>
+    <row r="47" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="110" t="s">
         <v>234</v>
       </c>
-      <c r="B45" s="103"/>
-      <c r="C45" s="103"/>
-      <c r="D45" s="103"/>
-      <c r="E45" s="22" t="s">
-        <v>229</v>
-      </c>
-      <c r="F45" s="103"/>
-      <c r="G45" s="103"/>
-      <c r="H45" s="104"/>
-      <c r="I45" s="98"/>
-      <c r="J45" s="99"/>
-    </row>
-    <row r="46" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="102" t="s">
+      <c r="B47" s="111"/>
+      <c r="C47" s="111"/>
+      <c r="D47" s="116"/>
+      <c r="E47" s="138"/>
+      <c r="F47" s="138"/>
+      <c r="G47" s="138"/>
+      <c r="H47" s="120" t="s">
+        <v>227</v>
+      </c>
+      <c r="I47" s="118"/>
+      <c r="J47" s="114"/>
+    </row>
+    <row r="48" spans="1:17" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="112" t="s">
         <v>235</v>
       </c>
-      <c r="B46" s="103"/>
-      <c r="C46" s="103"/>
-      <c r="D46" s="103"/>
-      <c r="E46" s="22" t="s">
-        <v>229</v>
-      </c>
-      <c r="F46" s="103"/>
-      <c r="G46" s="103"/>
-      <c r="H46" s="104"/>
-      <c r="I46" s="98"/>
-      <c r="J46" s="99"/>
-    </row>
-    <row r="47" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="102" t="s">
-        <v>236</v>
-      </c>
-      <c r="B47" s="103"/>
-      <c r="C47" s="103"/>
-      <c r="D47" s="103"/>
-      <c r="E47" s="22" t="s">
-        <v>229</v>
-      </c>
-      <c r="F47" s="103"/>
-      <c r="G47" s="103"/>
-      <c r="H47" s="104"/>
-      <c r="I47" s="98"/>
-      <c r="J47" s="99"/>
-    </row>
-    <row r="48" spans="1:17" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="114" t="s">
-        <v>237</v>
-      </c>
-      <c r="B48" s="115"/>
-      <c r="C48" s="115"/>
-      <c r="D48" s="115"/>
-      <c r="E48" s="23" t="s">
-        <v>229</v>
-      </c>
-      <c r="F48" s="115"/>
-      <c r="G48" s="115"/>
-      <c r="H48" s="116"/>
-      <c r="I48" s="100"/>
-      <c r="J48" s="101"/>
+      <c r="B48" s="113"/>
+      <c r="C48" s="113"/>
+      <c r="D48" s="117"/>
+      <c r="E48" s="139"/>
+      <c r="F48" s="139"/>
+      <c r="G48" s="139"/>
+      <c r="H48" s="121" t="s">
+        <v>227</v>
+      </c>
+      <c r="I48" s="119"/>
+      <c r="J48" s="115"/>
     </row>
   </sheetData>
-  <mergeCells count="57">
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="A47:D47"/>
-    <mergeCell ref="F47:H47"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="F44:H44"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="F45:H45"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:G25"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="I40:J48"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="A43:D43"/>
-    <mergeCell ref="A48:D48"/>
-    <mergeCell ref="F48:H48"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A25:B26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A46:D46"/>
+  <mergeCells count="61">
+    <mergeCell ref="G40:G44"/>
+    <mergeCell ref="F45:F48"/>
+    <mergeCell ref="G45:G48"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="I47:J47"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A5:B6"/>
@@ -3520,6 +3528,46 @@
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A25:B26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="A48:D48"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="E40:E44"/>
+    <mergeCell ref="E45:E48"/>
+    <mergeCell ref="F40:F44"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E17 G17 I17">
@@ -3581,222 +3629,222 @@
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A4" s="126" t="s">
+      <c r="A4" s="102" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="130" t="s">
+      <c r="B4" s="106" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="132" t="s">
+      <c r="C4" s="108" t="s">
         <v>145</v>
       </c>
-      <c r="D4" s="128" t="s">
+      <c r="D4" s="104" t="s">
         <v>146</v>
       </c>
-      <c r="E4" s="129"/>
-      <c r="F4" s="120" t="s">
+      <c r="E4" s="105"/>
+      <c r="F4" s="96" t="s">
         <v>147</v>
       </c>
-      <c r="G4" s="121"/>
-      <c r="H4" s="121"/>
-      <c r="I4" s="121"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="121"/>
-      <c r="L4" s="121"/>
-      <c r="M4" s="121"/>
-      <c r="N4" s="121"/>
-      <c r="O4" s="121"/>
-      <c r="P4" s="121"/>
-      <c r="Q4" s="122"/>
-      <c r="R4" s="123" t="s">
+      <c r="G4" s="97"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="97"/>
+      <c r="K4" s="97"/>
+      <c r="L4" s="97"/>
+      <c r="M4" s="97"/>
+      <c r="N4" s="97"/>
+      <c r="O4" s="97"/>
+      <c r="P4" s="97"/>
+      <c r="Q4" s="98"/>
+      <c r="R4" s="99" t="s">
         <v>148</v>
       </c>
-      <c r="S4" s="121"/>
-      <c r="T4" s="121"/>
-      <c r="U4" s="121"/>
-      <c r="V4" s="121"/>
-      <c r="W4" s="121"/>
-      <c r="X4" s="121"/>
-      <c r="Y4" s="121"/>
-      <c r="Z4" s="121"/>
-      <c r="AA4" s="121"/>
-      <c r="AB4" s="122"/>
+      <c r="S4" s="97"/>
+      <c r="T4" s="97"/>
+      <c r="U4" s="97"/>
+      <c r="V4" s="97"/>
+      <c r="W4" s="97"/>
+      <c r="X4" s="97"/>
+      <c r="Y4" s="97"/>
+      <c r="Z4" s="97"/>
+      <c r="AA4" s="97"/>
+      <c r="AB4" s="98"/>
     </row>
     <row r="5" spans="1:28" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="127"/>
-      <c r="B5" s="131"/>
-      <c r="C5" s="133"/>
-      <c r="D5" s="48" t="s">
+      <c r="A5" s="103"/>
+      <c r="B5" s="107"/>
+      <c r="C5" s="109"/>
+      <c r="D5" s="44" t="s">
         <v>149</v>
       </c>
-      <c r="E5" s="49" t="s">
+      <c r="E5" s="45" t="s">
         <v>150</v>
       </c>
-      <c r="F5" s="48" t="s">
+      <c r="F5" s="44" t="s">
         <v>151</v>
       </c>
-      <c r="G5" s="51" t="s">
+      <c r="G5" s="47" t="s">
         <v>152</v>
       </c>
-      <c r="H5" s="51" t="s">
+      <c r="H5" s="47" t="s">
         <v>153</v>
       </c>
-      <c r="I5" s="51" t="s">
+      <c r="I5" s="47" t="s">
         <v>154</v>
       </c>
-      <c r="J5" s="51" t="s">
+      <c r="J5" s="47" t="s">
         <v>155</v>
       </c>
-      <c r="K5" s="51" t="s">
+      <c r="K5" s="47" t="s">
         <v>156</v>
       </c>
-      <c r="L5" s="51" t="s">
+      <c r="L5" s="47" t="s">
         <v>157</v>
       </c>
-      <c r="M5" s="51" t="s">
+      <c r="M5" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="N5" s="51" t="s">
+      <c r="N5" s="47" t="s">
         <v>159</v>
       </c>
-      <c r="O5" s="51" t="s">
+      <c r="O5" s="47" t="s">
         <v>160</v>
       </c>
-      <c r="P5" s="51" t="s">
+      <c r="P5" s="47" t="s">
         <v>161</v>
       </c>
-      <c r="Q5" s="49" t="s">
+      <c r="Q5" s="45" t="s">
         <v>162</v>
       </c>
-      <c r="R5" s="50" t="s">
+      <c r="R5" s="46" t="s">
         <v>151</v>
       </c>
-      <c r="S5" s="51" t="s">
+      <c r="S5" s="47" t="s">
         <v>152</v>
       </c>
-      <c r="T5" s="51" t="s">
+      <c r="T5" s="47" t="s">
         <v>153</v>
       </c>
-      <c r="U5" s="51" t="s">
+      <c r="U5" s="47" t="s">
         <v>154</v>
       </c>
-      <c r="V5" s="51" t="s">
+      <c r="V5" s="47" t="s">
         <v>155</v>
       </c>
-      <c r="W5" s="51" t="s">
+      <c r="W5" s="47" t="s">
         <v>156</v>
       </c>
-      <c r="X5" s="51" t="s">
+      <c r="X5" s="47" t="s">
         <v>157</v>
       </c>
-      <c r="Y5" s="51" t="s">
+      <c r="Y5" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="Z5" s="51" t="s">
+      <c r="Z5" s="47" t="s">
         <v>159</v>
       </c>
-      <c r="AA5" s="51" t="s">
+      <c r="AA5" s="47" t="s">
         <v>161</v>
       </c>
-      <c r="AB5" s="49" t="s">
+      <c r="AB5" s="45" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A6" s="43">
+      <c r="A6" s="39">
         <v>0</v>
       </c>
-      <c r="B6" s="44" t="s">
+      <c r="B6" s="40" t="s">
         <v>164</v>
       </c>
-      <c r="C6" s="45" t="s">
+      <c r="C6" s="41" t="s">
         <v>165</v>
       </c>
-      <c r="D6" s="44" t="s">
+      <c r="D6" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="E6" s="45" t="s">
+      <c r="E6" s="41" t="s">
         <v>96</v>
       </c>
-      <c r="F6" s="44" t="s">
+      <c r="F6" s="40" t="s">
         <v>97</v>
       </c>
-      <c r="G6" s="47" t="s">
+      <c r="G6" s="43" t="s">
         <v>98</v>
       </c>
-      <c r="H6" s="47" t="s">
+      <c r="H6" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="I6" s="47" t="s">
+      <c r="I6" s="43" t="s">
         <v>100</v>
       </c>
-      <c r="J6" s="47" t="s">
+      <c r="J6" s="43" t="s">
         <v>101</v>
       </c>
-      <c r="K6" s="47" t="s">
+      <c r="K6" s="43" t="s">
         <v>102</v>
       </c>
-      <c r="L6" s="47" t="s">
+      <c r="L6" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="M6" s="47" t="s">
+      <c r="M6" s="43" t="s">
         <v>104</v>
       </c>
-      <c r="N6" s="47" t="s">
+      <c r="N6" s="43" t="s">
         <v>105</v>
       </c>
-      <c r="O6" s="47" t="s">
+      <c r="O6" s="43" t="s">
         <v>106</v>
       </c>
-      <c r="P6" s="47" t="s">
+      <c r="P6" s="43" t="s">
         <v>107</v>
       </c>
-      <c r="Q6" s="45" t="s">
+      <c r="Q6" s="41" t="s">
         <v>108</v>
       </c>
-      <c r="R6" s="46" t="s">
+      <c r="R6" s="42" t="s">
         <v>109</v>
       </c>
-      <c r="S6" s="47" t="s">
+      <c r="S6" s="43" t="s">
         <v>110</v>
       </c>
-      <c r="T6" s="47" t="s">
+      <c r="T6" s="43" t="s">
         <v>111</v>
       </c>
-      <c r="U6" s="47" t="s">
+      <c r="U6" s="43" t="s">
         <v>112</v>
       </c>
-      <c r="V6" s="47" t="s">
+      <c r="V6" s="43" t="s">
         <v>113</v>
       </c>
-      <c r="W6" s="47" t="s">
+      <c r="W6" s="43" t="s">
         <v>114</v>
       </c>
-      <c r="X6" s="47" t="s">
+      <c r="X6" s="43" t="s">
         <v>115</v>
       </c>
-      <c r="Y6" s="47" t="s">
+      <c r="Y6" s="43" t="s">
         <v>116</v>
       </c>
-      <c r="Z6" s="47" t="s">
+      <c r="Z6" s="43" t="s">
         <v>117</v>
       </c>
-      <c r="AA6" s="47" t="s">
+      <c r="AA6" s="43" t="s">
         <v>118</v>
       </c>
-      <c r="AB6" s="47" t="s">
+      <c r="AB6" s="43" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A7" s="41">
+      <c r="A7" s="37">
         <v>1</v>
       </c>
-      <c r="B7" s="39"/>
-      <c r="C7" s="40"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="39"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="35"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -3807,8 +3855,8 @@
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
-      <c r="Q7" s="40"/>
-      <c r="R7" s="35"/>
+      <c r="Q7" s="36"/>
+      <c r="R7" s="31"/>
       <c r="S7" s="1"/>
       <c r="T7" s="1"/>
       <c r="U7" s="1"/>
@@ -3821,14 +3869,14 @@
       <c r="AB7" s="1"/>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A8" s="41">
+      <c r="A8" s="37">
         <v>2</v>
       </c>
-      <c r="B8" s="39"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="39"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="39"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="35"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -3839,8 +3887,8 @@
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
-      <c r="Q8" s="40"/>
-      <c r="R8" s="35"/>
+      <c r="Q8" s="36"/>
+      <c r="R8" s="31"/>
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
       <c r="U8" s="1"/>
@@ -3853,14 +3901,14 @@
       <c r="AB8" s="1"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A9" s="41">
+      <c r="A9" s="37">
         <v>3</v>
       </c>
-      <c r="B9" s="39"/>
-      <c r="C9" s="40"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="40"/>
-      <c r="F9" s="39"/>
+      <c r="B9" s="35"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="35"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -3871,8 +3919,8 @@
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
-      <c r="Q9" s="40"/>
-      <c r="R9" s="35"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="31"/>
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
       <c r="U9" s="1"/>
@@ -3885,14 +3933,14 @@
       <c r="AB9" s="1"/>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A10" s="41">
+      <c r="A10" s="37">
         <v>4</v>
       </c>
-      <c r="B10" s="39"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="39"/>
+      <c r="B10" s="35"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="35"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -3903,8 +3951,8 @@
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
-      <c r="Q10" s="40"/>
-      <c r="R10" s="35"/>
+      <c r="Q10" s="36"/>
+      <c r="R10" s="31"/>
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
       <c r="U10" s="1"/>
@@ -3917,14 +3965,14 @@
       <c r="AB10" s="1"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A11" s="41">
+      <c r="A11" s="37">
         <v>5</v>
       </c>
-      <c r="B11" s="39"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="39"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="35"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -3935,8 +3983,8 @@
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
-      <c r="Q11" s="40"/>
-      <c r="R11" s="35"/>
+      <c r="Q11" s="36"/>
+      <c r="R11" s="31"/>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
       <c r="U11" s="1"/>
@@ -3949,14 +3997,14 @@
       <c r="AB11" s="1"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A12" s="41">
+      <c r="A12" s="37">
         <v>6</v>
       </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="39"/>
+      <c r="B12" s="35"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="35"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -3967,8 +4015,8 @@
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
-      <c r="Q12" s="40"/>
-      <c r="R12" s="35"/>
+      <c r="Q12" s="36"/>
+      <c r="R12" s="31"/>
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
       <c r="U12" s="1"/>
@@ -3981,14 +4029,14 @@
       <c r="AB12" s="1"/>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A13" s="41">
+      <c r="A13" s="37">
         <v>7</v>
       </c>
-      <c r="B13" s="39"/>
-      <c r="C13" s="40"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="39"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="35"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -3999,8 +4047,8 @@
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
-      <c r="Q13" s="40"/>
-      <c r="R13" s="35"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="31"/>
       <c r="S13" s="1"/>
       <c r="T13" s="1"/>
       <c r="U13" s="1"/>
@@ -4013,14 +4061,14 @@
       <c r="AB13" s="1"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A14" s="41">
+      <c r="A14" s="37">
         <v>8</v>
       </c>
-      <c r="B14" s="39"/>
-      <c r="C14" s="40"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="39"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="35"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -4031,8 +4079,8 @@
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
-      <c r="Q14" s="40"/>
-      <c r="R14" s="35"/>
+      <c r="Q14" s="36"/>
+      <c r="R14" s="31"/>
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
       <c r="U14" s="1"/>
@@ -4045,14 +4093,14 @@
       <c r="AB14" s="1"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A15" s="41">
+      <c r="A15" s="37">
         <v>9</v>
       </c>
-      <c r="B15" s="39"/>
-      <c r="C15" s="40"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="39"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="35"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -4063,8 +4111,8 @@
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
-      <c r="Q15" s="40"/>
-      <c r="R15" s="35"/>
+      <c r="Q15" s="36"/>
+      <c r="R15" s="31"/>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
       <c r="U15" s="1"/>
@@ -4077,14 +4125,14 @@
       <c r="AB15" s="1"/>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A16" s="41">
+      <c r="A16" s="37">
         <v>10</v>
       </c>
-      <c r="B16" s="39"/>
-      <c r="C16" s="40"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="39"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="35"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -4095,8 +4143,8 @@
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
-      <c r="Q16" s="40"/>
-      <c r="R16" s="35"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="31"/>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
       <c r="U16" s="1"/>
@@ -4109,14 +4157,14 @@
       <c r="AB16" s="1"/>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A17" s="41">
+      <c r="A17" s="37">
         <v>11</v>
       </c>
-      <c r="B17" s="39"/>
-      <c r="C17" s="40"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="39"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="35"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -4127,8 +4175,8 @@
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
-      <c r="Q17" s="40"/>
-      <c r="R17" s="35"/>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="31"/>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
       <c r="U17" s="1"/>
@@ -4141,14 +4189,14 @@
       <c r="AB17" s="1"/>
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A18" s="41">
+      <c r="A18" s="37">
         <v>12</v>
       </c>
-      <c r="B18" s="39"/>
-      <c r="C18" s="40"/>
-      <c r="D18" s="39"/>
-      <c r="E18" s="40"/>
-      <c r="F18" s="39"/>
+      <c r="B18" s="35"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="35"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -4159,8 +4207,8 @@
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
-      <c r="Q18" s="40"/>
-      <c r="R18" s="35"/>
+      <c r="Q18" s="36"/>
+      <c r="R18" s="31"/>
       <c r="S18" s="1"/>
       <c r="T18" s="1"/>
       <c r="U18" s="1"/>
@@ -4173,14 +4221,14 @@
       <c r="AB18" s="1"/>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A19" s="41">
+      <c r="A19" s="37">
         <v>13</v>
       </c>
-      <c r="B19" s="39"/>
-      <c r="C19" s="40"/>
-      <c r="D19" s="39"/>
-      <c r="E19" s="40"/>
-      <c r="F19" s="39"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="35"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -4191,8 +4239,8 @@
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
-      <c r="Q19" s="40"/>
-      <c r="R19" s="35"/>
+      <c r="Q19" s="36"/>
+      <c r="R19" s="31"/>
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
       <c r="U19" s="1"/>
@@ -4205,14 +4253,14 @@
       <c r="AB19" s="1"/>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A20" s="41">
+      <c r="A20" s="37">
         <v>14</v>
       </c>
-      <c r="B20" s="39"/>
-      <c r="C20" s="40"/>
-      <c r="D20" s="39"/>
-      <c r="E20" s="40"/>
-      <c r="F20" s="39"/>
+      <c r="B20" s="35"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="35"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -4223,8 +4271,8 @@
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
-      <c r="Q20" s="40"/>
-      <c r="R20" s="35"/>
+      <c r="Q20" s="36"/>
+      <c r="R20" s="31"/>
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
       <c r="U20" s="1"/>
@@ -4237,14 +4285,14 @@
       <c r="AB20" s="1"/>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A21" s="41">
+      <c r="A21" s="37">
         <v>15</v>
       </c>
-      <c r="B21" s="39"/>
-      <c r="C21" s="40"/>
-      <c r="D21" s="39"/>
-      <c r="E21" s="40"/>
-      <c r="F21" s="39"/>
+      <c r="B21" s="35"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="35"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -4255,8 +4303,8 @@
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
-      <c r="Q21" s="40"/>
-      <c r="R21" s="35"/>
+      <c r="Q21" s="36"/>
+      <c r="R21" s="31"/>
       <c r="S21" s="1"/>
       <c r="T21" s="1"/>
       <c r="U21" s="1"/>
@@ -4269,14 +4317,14 @@
       <c r="AB21" s="1"/>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A22" s="41">
+      <c r="A22" s="37">
         <v>16</v>
       </c>
-      <c r="B22" s="39"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="39"/>
-      <c r="E22" s="40"/>
-      <c r="F22" s="39"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="35"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -4287,8 +4335,8 @@
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
-      <c r="Q22" s="40"/>
-      <c r="R22" s="35"/>
+      <c r="Q22" s="36"/>
+      <c r="R22" s="31"/>
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
       <c r="U22" s="1"/>
@@ -4301,14 +4349,14 @@
       <c r="AB22" s="1"/>
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A23" s="41">
+      <c r="A23" s="37">
         <v>17</v>
       </c>
-      <c r="B23" s="39"/>
-      <c r="C23" s="40"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="40"/>
-      <c r="F23" s="39"/>
+      <c r="B23" s="35"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="35"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -4319,8 +4367,8 @@
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
-      <c r="Q23" s="40"/>
-      <c r="R23" s="35"/>
+      <c r="Q23" s="36"/>
+      <c r="R23" s="31"/>
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
       <c r="U23" s="1"/>
@@ -4333,14 +4381,14 @@
       <c r="AB23" s="1"/>
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A24" s="41">
+      <c r="A24" s="37">
         <v>18</v>
       </c>
-      <c r="B24" s="39"/>
-      <c r="C24" s="40"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="39"/>
+      <c r="B24" s="35"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="35"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -4351,8 +4399,8 @@
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
-      <c r="Q24" s="40"/>
-      <c r="R24" s="35"/>
+      <c r="Q24" s="36"/>
+      <c r="R24" s="31"/>
       <c r="S24" s="1"/>
       <c r="T24" s="1"/>
       <c r="U24" s="1"/>
@@ -4365,14 +4413,14 @@
       <c r="AB24" s="1"/>
     </row>
     <row r="25" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A25" s="41">
+      <c r="A25" s="37">
         <v>19</v>
       </c>
-      <c r="B25" s="39"/>
-      <c r="C25" s="40"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="40"/>
-      <c r="F25" s="39"/>
+      <c r="B25" s="35"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="36"/>
+      <c r="F25" s="35"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
@@ -4383,8 +4431,8 @@
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
-      <c r="Q25" s="40"/>
-      <c r="R25" s="35"/>
+      <c r="Q25" s="36"/>
+      <c r="R25" s="31"/>
       <c r="S25" s="1"/>
       <c r="T25" s="1"/>
       <c r="U25" s="1"/>
@@ -4397,14 +4445,14 @@
       <c r="AB25" s="1"/>
     </row>
     <row r="26" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A26" s="41">
+      <c r="A26" s="37">
         <v>20</v>
       </c>
-      <c r="B26" s="39"/>
-      <c r="C26" s="40"/>
-      <c r="D26" s="39"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="39"/>
+      <c r="B26" s="35"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="35"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -4415,8 +4463,8 @@
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
-      <c r="Q26" s="40"/>
-      <c r="R26" s="35"/>
+      <c r="Q26" s="36"/>
+      <c r="R26" s="31"/>
       <c r="S26" s="1"/>
       <c r="T26" s="1"/>
       <c r="U26" s="1"/>
@@ -4429,14 +4477,14 @@
       <c r="AB26" s="1"/>
     </row>
     <row r="27" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A27" s="41">
+      <c r="A27" s="37">
         <v>21</v>
       </c>
-      <c r="B27" s="39"/>
-      <c r="C27" s="40"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="40"/>
-      <c r="F27" s="39"/>
+      <c r="B27" s="35"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="35"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -4447,8 +4495,8 @@
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
-      <c r="Q27" s="40"/>
-      <c r="R27" s="35"/>
+      <c r="Q27" s="36"/>
+      <c r="R27" s="31"/>
       <c r="S27" s="1"/>
       <c r="T27" s="1"/>
       <c r="U27" s="1"/>
@@ -4461,14 +4509,14 @@
       <c r="AB27" s="1"/>
     </row>
     <row r="28" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A28" s="41">
+      <c r="A28" s="37">
         <v>22</v>
       </c>
-      <c r="B28" s="39"/>
-      <c r="C28" s="40"/>
-      <c r="D28" s="39"/>
-      <c r="E28" s="40"/>
-      <c r="F28" s="39"/>
+      <c r="B28" s="35"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="35"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -4479,8 +4527,8 @@
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
-      <c r="Q28" s="40"/>
-      <c r="R28" s="35"/>
+      <c r="Q28" s="36"/>
+      <c r="R28" s="31"/>
       <c r="S28" s="1"/>
       <c r="T28" s="1"/>
       <c r="U28" s="1"/>
@@ -4493,7 +4541,7 @@
       <c r="AB28" s="1"/>
     </row>
     <row r="29" spans="1:28" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="42">
+      <c r="A29" s="38">
         <v>23</v>
       </c>
       <c r="B29" s="7"/>
@@ -4512,7 +4560,7 @@
       <c r="O29" s="8"/>
       <c r="P29" s="8"/>
       <c r="Q29" s="9"/>
-      <c r="R29" s="35"/>
+      <c r="R29" s="31"/>
       <c r="S29" s="1"/>
       <c r="T29" s="1"/>
       <c r="U29" s="1"/>
@@ -4526,102 +4574,102 @@
     </row>
     <row r="31" spans="1:28" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="32" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A32" s="124" t="s">
+      <c r="A32" s="100" t="s">
         <v>144</v>
       </c>
-      <c r="B32" s="85" t="s">
+      <c r="B32" s="93" t="s">
         <v>166</v>
       </c>
-      <c r="C32" s="87"/>
-      <c r="D32" s="87"/>
-      <c r="E32" s="87"/>
-      <c r="F32" s="87"/>
-      <c r="G32" s="87"/>
-      <c r="H32" s="87"/>
-      <c r="I32" s="87"/>
-      <c r="J32" s="87"/>
-      <c r="K32" s="87"/>
-      <c r="L32" s="86"/>
-      <c r="M32" s="85" t="s">
+      <c r="C32" s="94"/>
+      <c r="D32" s="94"/>
+      <c r="E32" s="94"/>
+      <c r="F32" s="94"/>
+      <c r="G32" s="94"/>
+      <c r="H32" s="94"/>
+      <c r="I32" s="94"/>
+      <c r="J32" s="94"/>
+      <c r="K32" s="94"/>
+      <c r="L32" s="95"/>
+      <c r="M32" s="93" t="s">
         <v>167</v>
       </c>
-      <c r="N32" s="87"/>
-      <c r="O32" s="87"/>
-      <c r="P32" s="87"/>
-      <c r="Q32" s="87"/>
-      <c r="R32" s="87"/>
-      <c r="S32" s="87"/>
-      <c r="T32" s="87"/>
-      <c r="U32" s="87"/>
-      <c r="V32" s="87"/>
-      <c r="W32" s="86"/>
+      <c r="N32" s="94"/>
+      <c r="O32" s="94"/>
+      <c r="P32" s="94"/>
+      <c r="Q32" s="94"/>
+      <c r="R32" s="94"/>
+      <c r="S32" s="94"/>
+      <c r="T32" s="94"/>
+      <c r="U32" s="94"/>
+      <c r="V32" s="94"/>
+      <c r="W32" s="95"/>
     </row>
     <row r="33" spans="1:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="125"/>
-      <c r="B33" s="36" t="s">
+      <c r="A33" s="101"/>
+      <c r="B33" s="32" t="s">
         <v>151</v>
       </c>
-      <c r="C33" s="33" t="s">
+      <c r="C33" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="D33" s="33" t="s">
+      <c r="D33" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="E33" s="33" t="s">
+      <c r="E33" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="F33" s="33" t="s">
+      <c r="F33" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="G33" s="33" t="s">
+      <c r="G33" s="29" t="s">
         <v>156</v>
       </c>
-      <c r="H33" s="33" t="s">
+      <c r="H33" s="29" t="s">
         <v>157</v>
       </c>
-      <c r="I33" s="33" t="s">
+      <c r="I33" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="J33" s="33" t="s">
+      <c r="J33" s="29" t="s">
         <v>159</v>
       </c>
-      <c r="K33" s="33" t="s">
+      <c r="K33" s="29" t="s">
         <v>161</v>
       </c>
-      <c r="L33" s="34" t="s">
+      <c r="L33" s="30" t="s">
         <v>163</v>
       </c>
-      <c r="M33" s="36" t="s">
+      <c r="M33" s="32" t="s">
         <v>151</v>
       </c>
-      <c r="N33" s="33" t="s">
+      <c r="N33" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="O33" s="33" t="s">
+      <c r="O33" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="P33" s="33" t="s">
+      <c r="P33" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="Q33" s="33" t="s">
+      <c r="Q33" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="R33" s="33" t="s">
+      <c r="R33" s="29" t="s">
         <v>156</v>
       </c>
-      <c r="S33" s="33" t="s">
+      <c r="S33" s="29" t="s">
         <v>157</v>
       </c>
-      <c r="T33" s="33" t="s">
+      <c r="T33" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="U33" s="33" t="s">
+      <c r="U33" s="29" t="s">
         <v>159</v>
       </c>
-      <c r="V33" s="33" t="s">
+      <c r="V33" s="29" t="s">
         <v>161</v>
       </c>
-      <c r="W33" s="34" t="s">
+      <c r="W33" s="30" t="s">
         <v>163</v>
       </c>
     </row>
@@ -4629,70 +4677,70 @@
       <c r="A34" s="11">
         <v>0</v>
       </c>
-      <c r="B34" s="37" t="s">
+      <c r="B34" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="C34" s="32" t="s">
+      <c r="C34" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="D34" s="32" t="s">
+      <c r="D34" s="28" t="s">
         <v>122</v>
       </c>
-      <c r="E34" s="32" t="s">
+      <c r="E34" s="28" t="s">
         <v>123</v>
       </c>
-      <c r="F34" s="32" t="s">
+      <c r="F34" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="G34" s="32" t="s">
+      <c r="G34" s="28" t="s">
         <v>125</v>
       </c>
-      <c r="H34" s="32" t="s">
+      <c r="H34" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="I34" s="32" t="s">
+      <c r="I34" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="J34" s="32" t="s">
+      <c r="J34" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="K34" s="32" t="s">
+      <c r="K34" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="L34" s="38" t="s">
+      <c r="L34" s="34" t="s">
         <v>130</v>
       </c>
-      <c r="M34" s="37" t="s">
+      <c r="M34" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="N34" s="32" t="s">
+      <c r="N34" s="28" t="s">
         <v>132</v>
       </c>
-      <c r="O34" s="32" t="s">
+      <c r="O34" s="28" t="s">
         <v>133</v>
       </c>
-      <c r="P34" s="32" t="s">
+      <c r="P34" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="Q34" s="32" t="s">
+      <c r="Q34" s="28" t="s">
         <v>135</v>
       </c>
-      <c r="R34" s="32" t="s">
+      <c r="R34" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="S34" s="32" t="s">
+      <c r="S34" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="T34" s="32" t="s">
+      <c r="T34" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="U34" s="32" t="s">
+      <c r="U34" s="28" t="s">
         <v>139</v>
       </c>
-      <c r="V34" s="32" t="s">
+      <c r="V34" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="W34" s="38" t="s">
+      <c r="W34" s="34" t="s">
         <v>141</v>
       </c>
     </row>
@@ -4700,7 +4748,7 @@
       <c r="A35" s="3">
         <v>1</v>
       </c>
-      <c r="B35" s="39"/>
+      <c r="B35" s="35"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
@@ -4710,8 +4758,8 @@
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
-      <c r="L35" s="40"/>
-      <c r="M35" s="39"/>
+      <c r="L35" s="36"/>
+      <c r="M35" s="35"/>
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
       <c r="P35" s="1"/>
@@ -4721,13 +4769,13 @@
       <c r="T35" s="1"/>
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
-      <c r="W35" s="40"/>
+      <c r="W35" s="36"/>
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>2</v>
       </c>
-      <c r="B36" s="39"/>
+      <c r="B36" s="35"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
@@ -4737,8 +4785,8 @@
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
-      <c r="L36" s="40"/>
-      <c r="M36" s="39"/>
+      <c r="L36" s="36"/>
+      <c r="M36" s="35"/>
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
@@ -4748,13 +4796,13 @@
       <c r="T36" s="1"/>
       <c r="U36" s="1"/>
       <c r="V36" s="1"/>
-      <c r="W36" s="40"/>
+      <c r="W36" s="36"/>
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>3</v>
       </c>
-      <c r="B37" s="39"/>
+      <c r="B37" s="35"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
@@ -4764,8 +4812,8 @@
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
-      <c r="L37" s="40"/>
-      <c r="M37" s="39"/>
+      <c r="L37" s="36"/>
+      <c r="M37" s="35"/>
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
@@ -4775,13 +4823,13 @@
       <c r="T37" s="1"/>
       <c r="U37" s="1"/>
       <c r="V37" s="1"/>
-      <c r="W37" s="40"/>
+      <c r="W37" s="36"/>
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>4</v>
       </c>
-      <c r="B38" s="39"/>
+      <c r="B38" s="35"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
@@ -4791,8 +4839,8 @@
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
-      <c r="L38" s="40"/>
-      <c r="M38" s="39"/>
+      <c r="L38" s="36"/>
+      <c r="M38" s="35"/>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
@@ -4802,13 +4850,13 @@
       <c r="T38" s="1"/>
       <c r="U38" s="1"/>
       <c r="V38" s="1"/>
-      <c r="W38" s="40"/>
+      <c r="W38" s="36"/>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>5</v>
       </c>
-      <c r="B39" s="39"/>
+      <c r="B39" s="35"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
@@ -4818,8 +4866,8 @@
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
-      <c r="L39" s="40"/>
-      <c r="M39" s="39"/>
+      <c r="L39" s="36"/>
+      <c r="M39" s="35"/>
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
       <c r="P39" s="1"/>
@@ -4829,13 +4877,13 @@
       <c r="T39" s="1"/>
       <c r="U39" s="1"/>
       <c r="V39" s="1"/>
-      <c r="W39" s="40"/>
+      <c r="W39" s="36"/>
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>6</v>
       </c>
-      <c r="B40" s="39"/>
+      <c r="B40" s="35"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
@@ -4845,8 +4893,8 @@
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
-      <c r="L40" s="40"/>
-      <c r="M40" s="39"/>
+      <c r="L40" s="36"/>
+      <c r="M40" s="35"/>
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
@@ -4856,13 +4904,13 @@
       <c r="T40" s="1"/>
       <c r="U40" s="1"/>
       <c r="V40" s="1"/>
-      <c r="W40" s="40"/>
+      <c r="W40" s="36"/>
     </row>
     <row r="41" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>7</v>
       </c>
-      <c r="B41" s="39"/>
+      <c r="B41" s="35"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
@@ -4872,8 +4920,8 @@
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
-      <c r="L41" s="40"/>
-      <c r="M41" s="39"/>
+      <c r="L41" s="36"/>
+      <c r="M41" s="35"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
       <c r="P41" s="1"/>
@@ -4883,13 +4931,13 @@
       <c r="T41" s="1"/>
       <c r="U41" s="1"/>
       <c r="V41" s="1"/>
-      <c r="W41" s="40"/>
+      <c r="W41" s="36"/>
     </row>
     <row r="42" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>8</v>
       </c>
-      <c r="B42" s="39"/>
+      <c r="B42" s="35"/>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
@@ -4899,8 +4947,8 @@
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
-      <c r="L42" s="40"/>
-      <c r="M42" s="39"/>
+      <c r="L42" s="36"/>
+      <c r="M42" s="35"/>
       <c r="N42" s="1"/>
       <c r="O42" s="1"/>
       <c r="P42" s="1"/>
@@ -4910,13 +4958,13 @@
       <c r="T42" s="1"/>
       <c r="U42" s="1"/>
       <c r="V42" s="1"/>
-      <c r="W42" s="40"/>
+      <c r="W42" s="36"/>
     </row>
     <row r="43" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>9</v>
       </c>
-      <c r="B43" s="39"/>
+      <c r="B43" s="35"/>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
@@ -4926,8 +4974,8 @@
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
-      <c r="L43" s="40"/>
-      <c r="M43" s="39"/>
+      <c r="L43" s="36"/>
+      <c r="M43" s="35"/>
       <c r="N43" s="1"/>
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
@@ -4937,13 +4985,13 @@
       <c r="T43" s="1"/>
       <c r="U43" s="1"/>
       <c r="V43" s="1"/>
-      <c r="W43" s="40"/>
+      <c r="W43" s="36"/>
     </row>
     <row r="44" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>10</v>
       </c>
-      <c r="B44" s="39"/>
+      <c r="B44" s="35"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
@@ -4953,8 +5001,8 @@
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
-      <c r="L44" s="40"/>
-      <c r="M44" s="39"/>
+      <c r="L44" s="36"/>
+      <c r="M44" s="35"/>
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
@@ -4964,13 +5012,13 @@
       <c r="T44" s="1"/>
       <c r="U44" s="1"/>
       <c r="V44" s="1"/>
-      <c r="W44" s="40"/>
+      <c r="W44" s="36"/>
     </row>
     <row r="45" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>11</v>
       </c>
-      <c r="B45" s="39"/>
+      <c r="B45" s="35"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
@@ -4980,8 +5028,8 @@
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
-      <c r="L45" s="40"/>
-      <c r="M45" s="39"/>
+      <c r="L45" s="36"/>
+      <c r="M45" s="35"/>
       <c r="N45" s="1"/>
       <c r="O45" s="1"/>
       <c r="P45" s="1"/>
@@ -4991,13 +5039,13 @@
       <c r="T45" s="1"/>
       <c r="U45" s="1"/>
       <c r="V45" s="1"/>
-      <c r="W45" s="40"/>
+      <c r="W45" s="36"/>
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <v>12</v>
       </c>
-      <c r="B46" s="39"/>
+      <c r="B46" s="35"/>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
@@ -5007,8 +5055,8 @@
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
-      <c r="L46" s="40"/>
-      <c r="M46" s="39"/>
+      <c r="L46" s="36"/>
+      <c r="M46" s="35"/>
       <c r="N46" s="1"/>
       <c r="O46" s="1"/>
       <c r="P46" s="1"/>
@@ -5018,13 +5066,13 @@
       <c r="T46" s="1"/>
       <c r="U46" s="1"/>
       <c r="V46" s="1"/>
-      <c r="W46" s="40"/>
+      <c r="W46" s="36"/>
     </row>
     <row r="47" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>13</v>
       </c>
-      <c r="B47" s="39"/>
+      <c r="B47" s="35"/>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
@@ -5034,8 +5082,8 @@
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
-      <c r="L47" s="40"/>
-      <c r="M47" s="39"/>
+      <c r="L47" s="36"/>
+      <c r="M47" s="35"/>
       <c r="N47" s="1"/>
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
@@ -5045,13 +5093,13 @@
       <c r="T47" s="1"/>
       <c r="U47" s="1"/>
       <c r="V47" s="1"/>
-      <c r="W47" s="40"/>
+      <c r="W47" s="36"/>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>14</v>
       </c>
-      <c r="B48" s="39"/>
+      <c r="B48" s="35"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
@@ -5061,8 +5109,8 @@
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
-      <c r="L48" s="40"/>
-      <c r="M48" s="39"/>
+      <c r="L48" s="36"/>
+      <c r="M48" s="35"/>
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
       <c r="P48" s="1"/>
@@ -5072,13 +5120,13 @@
       <c r="T48" s="1"/>
       <c r="U48" s="1"/>
       <c r="V48" s="1"/>
-      <c r="W48" s="40"/>
+      <c r="W48" s="36"/>
     </row>
     <row r="49" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>15</v>
       </c>
-      <c r="B49" s="39"/>
+      <c r="B49" s="35"/>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
@@ -5088,8 +5136,8 @@
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
-      <c r="L49" s="40"/>
-      <c r="M49" s="39"/>
+      <c r="L49" s="36"/>
+      <c r="M49" s="35"/>
       <c r="N49" s="1"/>
       <c r="O49" s="1"/>
       <c r="P49" s="1"/>
@@ -5099,13 +5147,13 @@
       <c r="T49" s="1"/>
       <c r="U49" s="1"/>
       <c r="V49" s="1"/>
-      <c r="W49" s="40"/>
+      <c r="W49" s="36"/>
     </row>
     <row r="50" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <v>16</v>
       </c>
-      <c r="B50" s="39"/>
+      <c r="B50" s="35"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
@@ -5115,8 +5163,8 @@
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
-      <c r="L50" s="40"/>
-      <c r="M50" s="39"/>
+      <c r="L50" s="36"/>
+      <c r="M50" s="35"/>
       <c r="N50" s="1"/>
       <c r="O50" s="1"/>
       <c r="P50" s="1"/>
@@ -5126,13 +5174,13 @@
       <c r="T50" s="1"/>
       <c r="U50" s="1"/>
       <c r="V50" s="1"/>
-      <c r="W50" s="40"/>
+      <c r="W50" s="36"/>
     </row>
     <row r="51" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>17</v>
       </c>
-      <c r="B51" s="39"/>
+      <c r="B51" s="35"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -5142,8 +5190,8 @@
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
-      <c r="L51" s="40"/>
-      <c r="M51" s="39"/>
+      <c r="L51" s="36"/>
+      <c r="M51" s="35"/>
       <c r="N51" s="1"/>
       <c r="O51" s="1"/>
       <c r="P51" s="1"/>
@@ -5153,13 +5201,13 @@
       <c r="T51" s="1"/>
       <c r="U51" s="1"/>
       <c r="V51" s="1"/>
-      <c r="W51" s="40"/>
+      <c r="W51" s="36"/>
     </row>
     <row r="52" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <v>18</v>
       </c>
-      <c r="B52" s="39"/>
+      <c r="B52" s="35"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
@@ -5169,8 +5217,8 @@
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
-      <c r="L52" s="40"/>
-      <c r="M52" s="39"/>
+      <c r="L52" s="36"/>
+      <c r="M52" s="35"/>
       <c r="N52" s="1"/>
       <c r="O52" s="1"/>
       <c r="P52" s="1"/>
@@ -5180,13 +5228,13 @@
       <c r="T52" s="1"/>
       <c r="U52" s="1"/>
       <c r="V52" s="1"/>
-      <c r="W52" s="40"/>
+      <c r="W52" s="36"/>
     </row>
     <row r="53" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <v>19</v>
       </c>
-      <c r="B53" s="39"/>
+      <c r="B53" s="35"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -5196,8 +5244,8 @@
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
-      <c r="L53" s="40"/>
-      <c r="M53" s="39"/>
+      <c r="L53" s="36"/>
+      <c r="M53" s="35"/>
       <c r="N53" s="1"/>
       <c r="O53" s="1"/>
       <c r="P53" s="1"/>
@@ -5207,13 +5255,13 @@
       <c r="T53" s="1"/>
       <c r="U53" s="1"/>
       <c r="V53" s="1"/>
-      <c r="W53" s="40"/>
+      <c r="W53" s="36"/>
     </row>
     <row r="54" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
         <v>20</v>
       </c>
-      <c r="B54" s="39"/>
+      <c r="B54" s="35"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
@@ -5223,8 +5271,8 @@
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
-      <c r="L54" s="40"/>
-      <c r="M54" s="39"/>
+      <c r="L54" s="36"/>
+      <c r="M54" s="35"/>
       <c r="N54" s="1"/>
       <c r="O54" s="1"/>
       <c r="P54" s="1"/>
@@ -5234,13 +5282,13 @@
       <c r="T54" s="1"/>
       <c r="U54" s="1"/>
       <c r="V54" s="1"/>
-      <c r="W54" s="40"/>
+      <c r="W54" s="36"/>
     </row>
     <row r="55" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <v>21</v>
       </c>
-      <c r="B55" s="39"/>
+      <c r="B55" s="35"/>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
@@ -5250,8 +5298,8 @@
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
-      <c r="L55" s="40"/>
-      <c r="M55" s="39"/>
+      <c r="L55" s="36"/>
+      <c r="M55" s="35"/>
       <c r="N55" s="1"/>
       <c r="O55" s="1"/>
       <c r="P55" s="1"/>
@@ -5261,13 +5309,13 @@
       <c r="T55" s="1"/>
       <c r="U55" s="1"/>
       <c r="V55" s="1"/>
-      <c r="W55" s="40"/>
+      <c r="W55" s="36"/>
     </row>
     <row r="56" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
         <v>22</v>
       </c>
-      <c r="B56" s="39"/>
+      <c r="B56" s="35"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
@@ -5277,8 +5325,8 @@
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
-      <c r="L56" s="40"/>
-      <c r="M56" s="39"/>
+      <c r="L56" s="36"/>
+      <c r="M56" s="35"/>
       <c r="N56" s="1"/>
       <c r="O56" s="1"/>
       <c r="P56" s="1"/>
@@ -5288,13 +5336,13 @@
       <c r="T56" s="1"/>
       <c r="U56" s="1"/>
       <c r="V56" s="1"/>
-      <c r="W56" s="40"/>
+      <c r="W56" s="36"/>
     </row>
     <row r="57" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <v>22</v>
       </c>
-      <c r="B57" s="39"/>
+      <c r="B57" s="35"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
@@ -5304,8 +5352,8 @@
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
       <c r="K57" s="1"/>
-      <c r="L57" s="40"/>
-      <c r="M57" s="39"/>
+      <c r="L57" s="36"/>
+      <c r="M57" s="35"/>
       <c r="N57" s="1"/>
       <c r="O57" s="1"/>
       <c r="P57" s="1"/>
@@ -5315,7 +5363,7 @@
       <c r="T57" s="1"/>
       <c r="U57" s="1"/>
       <c r="V57" s="1"/>
-      <c r="W57" s="40"/>
+      <c r="W57" s="36"/>
     </row>
     <row r="58" spans="1:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="3">

--- a/elec_room_project/template_전기실_운영일지.xlsx
+++ b/elec_room_project/template_전기실_운영일지.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\elec_room_project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\pygame\pygame\elec_room_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA5D9837-3051-456D-8789-5F5BD9F3FBCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{711E7B5D-E314-450C-BC69-33BF9DCA8E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="210" yWindow="315" windowWidth="18345" windowHeight="14295" xr2:uid="{943AB7D1-EB27-49C3-9C36-555299583416}"/>
+    <workbookView xWindow="1290" yWindow="2955" windowWidth="25455" windowHeight="11295" activeTab="1" xr2:uid="{943AB7D1-EB27-49C3-9C36-555299583416}"/>
   </bookViews>
   <sheets>
     <sheet name="전력설비_운전현황" sheetId="4" r:id="rId1"/>
@@ -24,21 +24,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="275">
   <si>
     <t>실내온도</t>
   </si>
@@ -885,11 +876,27 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1차("점검자)</t>
+    <t>1차 점검자</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1("점검시간")</t>
+    <t>2차 점검자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3차 점검자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1차 시간</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2차 시간</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3차 시간</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1044,7 +1051,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="43">
+  <borders count="46">
     <border>
       <left/>
       <right/>
@@ -1596,13 +1603,46 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="140">
+  <cellXfs count="148">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1782,58 +1822,37 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -1845,6 +1864,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1872,56 +1894,41 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1929,82 +1936,52 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2012,6 +1989,93 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2452,15 +2516,15 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="86.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="78" t="s">
+      <c r="A2" s="70" t="s">
         <v>168</v>
       </c>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
       <c r="H2" s="7"/>
       <c r="I2" s="8"/>
       <c r="J2" s="9"/>
@@ -2484,30 +2548,30 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="69" t="s">
+      <c r="A5" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="79"/>
-      <c r="C5" s="69" t="s">
+      <c r="B5" s="72"/>
+      <c r="C5" s="71" t="s">
         <v>173</v>
       </c>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69" t="s">
+      <c r="D5" s="71"/>
+      <c r="E5" s="71" t="s">
         <v>174</v>
       </c>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69" t="s">
+      <c r="F5" s="71"/>
+      <c r="G5" s="71" t="s">
         <v>175</v>
       </c>
-      <c r="H5" s="69"/>
-      <c r="I5" s="69" t="s">
+      <c r="H5" s="71"/>
+      <c r="I5" s="71" t="s">
         <v>176</v>
       </c>
-      <c r="J5" s="69"/>
+      <c r="J5" s="71"/>
     </row>
     <row r="6" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="80"/>
-      <c r="B6" s="81"/>
+      <c r="A6" s="73"/>
+      <c r="B6" s="74"/>
       <c r="C6" s="10" t="s">
         <v>177</v>
       </c>
@@ -2534,7 +2598,7 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="69" t="s">
+      <c r="A7" s="71" t="s">
         <v>179</v>
       </c>
       <c r="B7" s="10" t="s">
@@ -2566,7 +2630,7 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="69"/>
+      <c r="A8" s="71"/>
       <c r="B8" s="10" t="s">
         <v>182</v>
       </c>
@@ -2596,7 +2660,7 @@
       </c>
     </row>
     <row r="9" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="69"/>
+      <c r="A9" s="71"/>
       <c r="B9" s="10" t="s">
         <v>184</v>
       </c>
@@ -2626,7 +2690,7 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="69" t="s">
+      <c r="A10" s="71" t="s">
         <v>186</v>
       </c>
       <c r="B10" s="10" t="s">
@@ -2658,7 +2722,7 @@
       </c>
     </row>
     <row r="11" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="69"/>
+      <c r="A11" s="71"/>
       <c r="B11" s="10" t="s">
         <v>189</v>
       </c>
@@ -2688,7 +2752,7 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="69"/>
+      <c r="A12" s="71"/>
       <c r="B12" s="10" t="s">
         <v>191</v>
       </c>
@@ -2718,7 +2782,7 @@
       </c>
     </row>
     <row r="13" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="69" t="s">
+      <c r="A13" s="71" t="s">
         <v>193</v>
       </c>
       <c r="B13" s="10" t="s">
@@ -2750,7 +2814,7 @@
       </c>
     </row>
     <row r="14" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="69"/>
+      <c r="A14" s="71"/>
       <c r="B14" s="10" t="s">
         <v>182</v>
       </c>
@@ -2780,7 +2844,7 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="69"/>
+      <c r="A15" s="71"/>
       <c r="B15" s="10" t="s">
         <v>184</v>
       </c>
@@ -2842,10 +2906,10 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="72" t="s">
+      <c r="A17" s="91" t="s">
         <v>199</v>
       </c>
-      <c r="B17" s="73"/>
+      <c r="B17" s="92"/>
       <c r="C17" s="48"/>
       <c r="D17" s="48"/>
       <c r="E17" s="48" t="s">
@@ -2868,10 +2932,10 @@
       </c>
     </row>
     <row r="18" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="74" t="s">
+      <c r="A18" s="93" t="s">
         <v>222</v>
       </c>
-      <c r="B18" s="74"/>
+      <c r="B18" s="93"/>
       <c r="C18" s="48"/>
       <c r="D18" s="48"/>
       <c r="E18" s="49" t="e">
@@ -2905,60 +2969,60 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="89" t="s">
+      <c r="A20" s="83" t="s">
         <v>207</v>
       </c>
-      <c r="B20" s="85"/>
-      <c r="C20" s="85" t="s">
+      <c r="B20" s="79"/>
+      <c r="C20" s="79" t="s">
         <v>208</v>
       </c>
-      <c r="D20" s="85"/>
-      <c r="E20" s="86" t="s">
+      <c r="D20" s="79"/>
+      <c r="E20" s="80" t="s">
         <v>209</v>
       </c>
-      <c r="F20" s="87"/>
-      <c r="G20" s="85" t="s">
+      <c r="F20" s="81"/>
+      <c r="G20" s="79" t="s">
         <v>210</v>
       </c>
-      <c r="H20" s="88"/>
+      <c r="H20" s="82"/>
     </row>
     <row r="21" spans="1:10" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="90" t="s">
+      <c r="A21" s="84" t="s">
         <v>211</v>
       </c>
-      <c r="B21" s="69"/>
-      <c r="C21" s="62" t="s">
+      <c r="B21" s="71"/>
+      <c r="C21" s="69" t="s">
         <v>221</v>
       </c>
-      <c r="D21" s="62"/>
-      <c r="E21" s="70" t="s">
+      <c r="D21" s="69"/>
+      <c r="E21" s="123" t="s">
         <v>212</v>
       </c>
-      <c r="F21" s="71"/>
-      <c r="G21" s="62" t="e">
+      <c r="F21" s="124"/>
+      <c r="G21" s="69" t="e">
         <f>E21-C21</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H21" s="83"/>
+      <c r="H21" s="76"/>
     </row>
     <row r="22" spans="1:10" ht="35.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="91" t="s">
+      <c r="A22" s="85" t="s">
         <v>213</v>
       </c>
-      <c r="B22" s="92"/>
-      <c r="C22" s="82" t="s">
+      <c r="B22" s="86"/>
+      <c r="C22" s="75" t="s">
         <v>236</v>
       </c>
-      <c r="D22" s="82"/>
-      <c r="E22" s="82" t="s">
+      <c r="D22" s="75"/>
+      <c r="E22" s="75" t="s">
         <v>237</v>
       </c>
-      <c r="F22" s="82"/>
-      <c r="G22" s="64" t="e">
+      <c r="F22" s="75"/>
+      <c r="G22" s="77" t="e">
         <f>+E22-C22</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H22" s="84"/>
+      <c r="H22" s="78"/>
     </row>
     <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="24" spans="1:10" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -2967,28 +3031,28 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="75" t="s">
+      <c r="A25" s="87" t="s">
         <v>1</v>
       </c>
-      <c r="B25" s="67"/>
-      <c r="C25" s="67" t="s">
+      <c r="B25" s="88"/>
+      <c r="C25" s="88" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="67"/>
-      <c r="E25" s="67" t="s">
+      <c r="D25" s="88"/>
+      <c r="E25" s="88" t="s">
         <v>2</v>
       </c>
-      <c r="F25" s="67"/>
-      <c r="G25" s="67"/>
-      <c r="H25" s="67" t="s">
+      <c r="F25" s="88"/>
+      <c r="G25" s="88"/>
+      <c r="H25" s="88" t="s">
         <v>3</v>
       </c>
-      <c r="I25" s="67"/>
-      <c r="J25" s="68"/>
+      <c r="I25" s="88"/>
+      <c r="J25" s="122"/>
     </row>
     <row r="26" spans="1:10" ht="35.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="76"/>
-      <c r="B26" s="77"/>
+      <c r="A26" s="89"/>
+      <c r="B26" s="90"/>
       <c r="C26" s="53" t="s">
         <v>4</v>
       </c>
@@ -3015,10 +3079,10 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="75" t="s">
+      <c r="A27" s="87" t="s">
         <v>238</v>
       </c>
-      <c r="B27" s="67"/>
+      <c r="B27" s="88"/>
       <c r="C27" s="57" t="s">
         <v>239</v>
       </c>
@@ -3045,10 +3109,10 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="61" t="s">
+      <c r="A28" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="B28" s="62"/>
+      <c r="B28" s="69"/>
       <c r="C28" s="48" t="s">
         <v>255</v>
       </c>
@@ -3075,10 +3139,10 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="61" t="s">
+      <c r="A29" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="B29" s="62"/>
+      <c r="B29" s="69"/>
       <c r="C29" s="48" t="s">
         <v>247</v>
       </c>
@@ -3105,10 +3169,10 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="61" t="s">
+      <c r="A30" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="B30" s="62"/>
+      <c r="B30" s="69"/>
       <c r="C30" s="51" t="e">
         <f>+C28-C29</f>
         <v>#VALUE!</v>
@@ -3143,10 +3207,10 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="61" t="s">
+      <c r="A31" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="62"/>
+      <c r="B31" s="69"/>
       <c r="C31" s="51" t="e">
         <f>+C30*2400</f>
         <v>#VALUE!</v>
@@ -3181,10 +3245,10 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="61" t="s">
+      <c r="A32" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="B32" s="62"/>
+      <c r="B32" s="69"/>
       <c r="C32" s="51" t="e">
         <f>(C28-C27)*2400</f>
         <v>#VALUE!</v>
@@ -3219,10 +3283,10 @@
       </c>
     </row>
     <row r="33" spans="1:17" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="63" t="s">
+      <c r="A33" s="125" t="s">
         <v>17</v>
       </c>
-      <c r="B33" s="64"/>
+      <c r="B33" s="77"/>
       <c r="C33" s="14" t="e">
         <f>C30/(SQRT(C30^2+D30^2*100))</f>
         <v>#VALUE!</v>
@@ -3244,10 +3308,10 @@
       </c>
     </row>
     <row r="34" spans="1:17" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="65" t="s">
+      <c r="A34" s="126" t="s">
         <v>19</v>
       </c>
-      <c r="B34" s="66"/>
+      <c r="B34" s="127"/>
       <c r="C34" s="22"/>
       <c r="D34" s="22"/>
       <c r="E34" s="22"/>
@@ -3323,198 +3387,235 @@
       <c r="J38" s="21"/>
     </row>
     <row r="39" spans="1:17" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="122" t="s">
+      <c r="A39" s="128" t="s">
         <v>224</v>
       </c>
-      <c r="B39" s="123"/>
-      <c r="C39" s="123"/>
-      <c r="D39" s="124"/>
-      <c r="E39" s="125" t="s">
+      <c r="B39" s="129"/>
+      <c r="C39" s="129"/>
+      <c r="D39" s="130"/>
+      <c r="E39" s="64" t="s">
         <v>265</v>
       </c>
-      <c r="F39" s="126" t="s">
+      <c r="F39" s="63" t="s">
         <v>266</v>
       </c>
-      <c r="G39" s="127" t="s">
+      <c r="G39" s="65" t="s">
         <v>267</v>
       </c>
-      <c r="H39" s="128" t="s">
+      <c r="H39" s="66" t="s">
         <v>268</v>
       </c>
-      <c r="I39" s="129" t="s">
+      <c r="I39" s="94" t="s">
         <v>225</v>
       </c>
-      <c r="J39" s="130"/>
+      <c r="J39" s="95"/>
       <c r="Q39" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="131" t="s">
+      <c r="A40" s="96" t="s">
         <v>226</v>
       </c>
-      <c r="B40" s="132"/>
-      <c r="C40" s="132"/>
-      <c r="D40" s="133"/>
-      <c r="E40" s="137" t="s">
+      <c r="B40" s="97"/>
+      <c r="C40" s="97"/>
+      <c r="D40" s="98"/>
+      <c r="E40" s="114" t="s">
         <v>269</v>
       </c>
-      <c r="F40" s="137" t="s">
-        <v>269</v>
-      </c>
-      <c r="G40" s="137" t="s">
-        <v>269</v>
-      </c>
-      <c r="H40" s="134" t="s">
+      <c r="F40" s="119" t="s">
+        <v>270</v>
+      </c>
+      <c r="G40" s="102" t="s">
+        <v>271</v>
+      </c>
+      <c r="H40" s="67" t="s">
         <v>227</v>
       </c>
-      <c r="I40" s="135"/>
-      <c r="J40" s="136"/>
+      <c r="I40" s="110"/>
+      <c r="J40" s="111"/>
     </row>
     <row r="41" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="110" t="s">
+      <c r="A41" s="99" t="s">
         <v>228</v>
       </c>
-      <c r="B41" s="111"/>
-      <c r="C41" s="111"/>
-      <c r="D41" s="116"/>
-      <c r="E41" s="138"/>
-      <c r="F41" s="138"/>
-      <c r="G41" s="138"/>
-      <c r="H41" s="120" t="s">
+      <c r="B41" s="100"/>
+      <c r="C41" s="100"/>
+      <c r="D41" s="101"/>
+      <c r="E41" s="115"/>
+      <c r="F41" s="120"/>
+      <c r="G41" s="103"/>
+      <c r="H41" s="61" t="s">
         <v>227</v>
       </c>
-      <c r="I41" s="118"/>
-      <c r="J41" s="114"/>
+      <c r="I41" s="105"/>
+      <c r="J41" s="106"/>
     </row>
     <row r="42" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="110" t="s">
+      <c r="A42" s="99" t="s">
         <v>229</v>
       </c>
-      <c r="B42" s="111"/>
-      <c r="C42" s="111"/>
-      <c r="D42" s="116"/>
-      <c r="E42" s="138"/>
-      <c r="F42" s="138"/>
-      <c r="G42" s="138"/>
-      <c r="H42" s="120" t="s">
+      <c r="B42" s="100"/>
+      <c r="C42" s="100"/>
+      <c r="D42" s="101"/>
+      <c r="E42" s="115"/>
+      <c r="F42" s="120"/>
+      <c r="G42" s="103"/>
+      <c r="H42" s="61" t="s">
         <v>227</v>
       </c>
-      <c r="I42" s="118"/>
-      <c r="J42" s="114"/>
+      <c r="I42" s="105"/>
+      <c r="J42" s="106"/>
     </row>
     <row r="43" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="110" t="s">
+      <c r="A43" s="99" t="s">
         <v>230</v>
       </c>
-      <c r="B43" s="111"/>
-      <c r="C43" s="111"/>
-      <c r="D43" s="116"/>
-      <c r="E43" s="138"/>
-      <c r="F43" s="138"/>
-      <c r="G43" s="138"/>
-      <c r="H43" s="120" t="s">
+      <c r="B43" s="100"/>
+      <c r="C43" s="100"/>
+      <c r="D43" s="101"/>
+      <c r="E43" s="115"/>
+      <c r="F43" s="120"/>
+      <c r="G43" s="103"/>
+      <c r="H43" s="61" t="s">
         <v>227</v>
       </c>
-      <c r="I43" s="118"/>
-      <c r="J43" s="114"/>
+      <c r="I43" s="105"/>
+      <c r="J43" s="106"/>
     </row>
     <row r="44" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="110" t="s">
+      <c r="A44" s="99" t="s">
         <v>231</v>
       </c>
-      <c r="B44" s="111"/>
-      <c r="C44" s="111"/>
-      <c r="D44" s="116"/>
-      <c r="E44" s="138"/>
-      <c r="F44" s="138"/>
-      <c r="G44" s="138"/>
-      <c r="H44" s="120" t="s">
+      <c r="B44" s="100"/>
+      <c r="C44" s="100"/>
+      <c r="D44" s="101"/>
+      <c r="E44" s="116"/>
+      <c r="F44" s="121"/>
+      <c r="G44" s="104"/>
+      <c r="H44" s="61" t="s">
         <v>227</v>
       </c>
-      <c r="I44" s="118"/>
-      <c r="J44" s="114"/>
+      <c r="I44" s="105"/>
+      <c r="J44" s="106"/>
     </row>
     <row r="45" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="110" t="s">
+      <c r="A45" s="99" t="s">
         <v>232</v>
       </c>
-      <c r="B45" s="111"/>
-      <c r="C45" s="111"/>
-      <c r="D45" s="116"/>
-      <c r="E45" s="138" t="s">
-        <v>270</v>
-      </c>
-      <c r="F45" s="138" t="s">
-        <v>270</v>
-      </c>
-      <c r="G45" s="138" t="s">
-        <v>270</v>
-      </c>
-      <c r="H45" s="120" t="s">
+      <c r="B45" s="100"/>
+      <c r="C45" s="100"/>
+      <c r="D45" s="101"/>
+      <c r="E45" s="117" t="s">
+        <v>272</v>
+      </c>
+      <c r="F45" s="117" t="s">
+        <v>273</v>
+      </c>
+      <c r="G45" s="117" t="s">
+        <v>274</v>
+      </c>
+      <c r="H45" s="61" t="s">
         <v>227</v>
       </c>
-      <c r="I45" s="118"/>
-      <c r="J45" s="114"/>
+      <c r="I45" s="105"/>
+      <c r="J45" s="106"/>
     </row>
     <row r="46" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="110" t="s">
+      <c r="A46" s="99" t="s">
         <v>233</v>
       </c>
-      <c r="B46" s="111"/>
-      <c r="C46" s="111"/>
-      <c r="D46" s="116"/>
-      <c r="E46" s="138"/>
-      <c r="F46" s="138"/>
-      <c r="G46" s="138"/>
-      <c r="H46" s="120" t="s">
+      <c r="B46" s="100"/>
+      <c r="C46" s="100"/>
+      <c r="D46" s="101"/>
+      <c r="E46" s="117"/>
+      <c r="F46" s="117"/>
+      <c r="G46" s="117"/>
+      <c r="H46" s="61" t="s">
         <v>227</v>
       </c>
-      <c r="I46" s="118"/>
-      <c r="J46" s="114"/>
+      <c r="I46" s="105"/>
+      <c r="J46" s="106"/>
     </row>
     <row r="47" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="110" t="s">
+      <c r="A47" s="99" t="s">
         <v>234</v>
       </c>
-      <c r="B47" s="111"/>
-      <c r="C47" s="111"/>
-      <c r="D47" s="116"/>
-      <c r="E47" s="138"/>
-      <c r="F47" s="138"/>
-      <c r="G47" s="138"/>
-      <c r="H47" s="120" t="s">
+      <c r="B47" s="100"/>
+      <c r="C47" s="100"/>
+      <c r="D47" s="101"/>
+      <c r="E47" s="117"/>
+      <c r="F47" s="117"/>
+      <c r="G47" s="117"/>
+      <c r="H47" s="61" t="s">
         <v>227</v>
       </c>
-      <c r="I47" s="118"/>
-      <c r="J47" s="114"/>
+      <c r="I47" s="105"/>
+      <c r="J47" s="106"/>
     </row>
     <row r="48" spans="1:17" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="112" t="s">
+      <c r="A48" s="107" t="s">
         <v>235</v>
       </c>
-      <c r="B48" s="113"/>
-      <c r="C48" s="113"/>
-      <c r="D48" s="117"/>
-      <c r="E48" s="139"/>
-      <c r="F48" s="139"/>
-      <c r="G48" s="139"/>
-      <c r="H48" s="121" t="s">
+      <c r="B48" s="108"/>
+      <c r="C48" s="108"/>
+      <c r="D48" s="109"/>
+      <c r="E48" s="118"/>
+      <c r="F48" s="118"/>
+      <c r="G48" s="118"/>
+      <c r="H48" s="62" t="s">
         <v>227</v>
       </c>
-      <c r="I48" s="119"/>
-      <c r="J48" s="115"/>
+      <c r="I48" s="112"/>
+      <c r="J48" s="113"/>
     </row>
   </sheetData>
   <mergeCells count="61">
-    <mergeCell ref="G40:G44"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="A48:D48"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="E40:E44"/>
+    <mergeCell ref="E45:E48"/>
+    <mergeCell ref="F40:F44"/>
     <mergeCell ref="F45:F48"/>
     <mergeCell ref="G45:G48"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="I44:J44"/>
     <mergeCell ref="I45:J45"/>
     <mergeCell ref="I46:J46"/>
     <mergeCell ref="I47:J47"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="G40:G44"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="A18:B18"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A5:B6"/>
@@ -3531,43 +3632,6 @@
     <mergeCell ref="A25:B26"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="A43:D43"/>
-    <mergeCell ref="A48:D48"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:G25"/>
-    <mergeCell ref="A47:D47"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="E40:E44"/>
-    <mergeCell ref="E45:E48"/>
-    <mergeCell ref="F40:F44"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E17 G17 I17">
@@ -3629,51 +3693,51 @@
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A4" s="102" t="s">
+      <c r="A4" s="140" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="106" t="s">
+      <c r="B4" s="144" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="108" t="s">
+      <c r="C4" s="146" t="s">
         <v>145</v>
       </c>
-      <c r="D4" s="104" t="s">
+      <c r="D4" s="142" t="s">
         <v>146</v>
       </c>
-      <c r="E4" s="105"/>
-      <c r="F4" s="96" t="s">
+      <c r="E4" s="143"/>
+      <c r="F4" s="134" t="s">
         <v>147</v>
       </c>
-      <c r="G4" s="97"/>
-      <c r="H4" s="97"/>
-      <c r="I4" s="97"/>
-      <c r="J4" s="97"/>
-      <c r="K4" s="97"/>
-      <c r="L4" s="97"/>
-      <c r="M4" s="97"/>
-      <c r="N4" s="97"/>
-      <c r="O4" s="97"/>
-      <c r="P4" s="97"/>
-      <c r="Q4" s="98"/>
-      <c r="R4" s="99" t="s">
+      <c r="G4" s="135"/>
+      <c r="H4" s="135"/>
+      <c r="I4" s="135"/>
+      <c r="J4" s="135"/>
+      <c r="K4" s="135"/>
+      <c r="L4" s="135"/>
+      <c r="M4" s="135"/>
+      <c r="N4" s="135"/>
+      <c r="O4" s="135"/>
+      <c r="P4" s="135"/>
+      <c r="Q4" s="136"/>
+      <c r="R4" s="137" t="s">
         <v>148</v>
       </c>
-      <c r="S4" s="97"/>
-      <c r="T4" s="97"/>
-      <c r="U4" s="97"/>
-      <c r="V4" s="97"/>
-      <c r="W4" s="97"/>
-      <c r="X4" s="97"/>
-      <c r="Y4" s="97"/>
-      <c r="Z4" s="97"/>
-      <c r="AA4" s="97"/>
-      <c r="AB4" s="98"/>
+      <c r="S4" s="135"/>
+      <c r="T4" s="135"/>
+      <c r="U4" s="135"/>
+      <c r="V4" s="135"/>
+      <c r="W4" s="135"/>
+      <c r="X4" s="135"/>
+      <c r="Y4" s="135"/>
+      <c r="Z4" s="135"/>
+      <c r="AA4" s="135"/>
+      <c r="AB4" s="136"/>
     </row>
     <row r="5" spans="1:28" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="103"/>
-      <c r="B5" s="107"/>
-      <c r="C5" s="109"/>
+      <c r="A5" s="141"/>
+      <c r="B5" s="145"/>
+      <c r="C5" s="147"/>
       <c r="D5" s="44" t="s">
         <v>149</v>
       </c>
@@ -4574,38 +4638,38 @@
     </row>
     <row r="31" spans="1:28" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="32" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A32" s="100" t="s">
+      <c r="A32" s="138" t="s">
         <v>144</v>
       </c>
-      <c r="B32" s="93" t="s">
+      <c r="B32" s="131" t="s">
         <v>166</v>
       </c>
-      <c r="C32" s="94"/>
-      <c r="D32" s="94"/>
-      <c r="E32" s="94"/>
-      <c r="F32" s="94"/>
-      <c r="G32" s="94"/>
-      <c r="H32" s="94"/>
-      <c r="I32" s="94"/>
-      <c r="J32" s="94"/>
-      <c r="K32" s="94"/>
-      <c r="L32" s="95"/>
-      <c r="M32" s="93" t="s">
+      <c r="C32" s="132"/>
+      <c r="D32" s="132"/>
+      <c r="E32" s="132"/>
+      <c r="F32" s="132"/>
+      <c r="G32" s="132"/>
+      <c r="H32" s="132"/>
+      <c r="I32" s="132"/>
+      <c r="J32" s="132"/>
+      <c r="K32" s="132"/>
+      <c r="L32" s="133"/>
+      <c r="M32" s="131" t="s">
         <v>167</v>
       </c>
-      <c r="N32" s="94"/>
-      <c r="O32" s="94"/>
-      <c r="P32" s="94"/>
-      <c r="Q32" s="94"/>
-      <c r="R32" s="94"/>
-      <c r="S32" s="94"/>
-      <c r="T32" s="94"/>
-      <c r="U32" s="94"/>
-      <c r="V32" s="94"/>
-      <c r="W32" s="95"/>
+      <c r="N32" s="132"/>
+      <c r="O32" s="132"/>
+      <c r="P32" s="132"/>
+      <c r="Q32" s="132"/>
+      <c r="R32" s="132"/>
+      <c r="S32" s="132"/>
+      <c r="T32" s="132"/>
+      <c r="U32" s="132"/>
+      <c r="V32" s="132"/>
+      <c r="W32" s="133"/>
     </row>
     <row r="33" spans="1:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="101"/>
+      <c r="A33" s="139"/>
       <c r="B33" s="32" t="s">
         <v>151</v>
       </c>

--- a/elec_room_project/template_전기실_운영일지.xlsx
+++ b/elec_room_project/template_전기실_운영일지.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\pygame\pygame\elec_room_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{711E7B5D-E314-450C-BC69-33BF9DCA8E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2672221E-5C5C-4DF3-9D04-A6E487382297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1290" yWindow="2955" windowWidth="25455" windowHeight="11295" activeTab="1" xr2:uid="{943AB7D1-EB27-49C3-9C36-555299583416}"/>
+    <workbookView xWindow="1290" yWindow="2955" windowWidth="25455" windowHeight="11295" xr2:uid="{943AB7D1-EB27-49C3-9C36-555299583416}"/>
   </bookViews>
   <sheets>
     <sheet name="전력설비_운전현황" sheetId="4" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="279">
   <si>
     <t>실내온도</t>
   </si>
@@ -897,6 +897,22 @@
   </si>
   <si>
     <t>3차 시간</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금일("geo_2")</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전일("geo_2")</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금일("geo_3")</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전일("geo_3")</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1849,10 +1865,139 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -1864,9 +2009,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1894,136 +2036,10 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2516,15 +2532,15 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="86.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="70" t="s">
+      <c r="A2" s="114" t="s">
         <v>168</v>
       </c>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
+      <c r="B2" s="114"/>
+      <c r="C2" s="114"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="114"/>
       <c r="H2" s="7"/>
       <c r="I2" s="8"/>
       <c r="J2" s="9"/>
@@ -2548,30 +2564,30 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="71" t="s">
+      <c r="A5" s="82" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="72"/>
-      <c r="C5" s="71" t="s">
+      <c r="B5" s="115"/>
+      <c r="C5" s="82" t="s">
         <v>173</v>
       </c>
-      <c r="D5" s="71"/>
-      <c r="E5" s="71" t="s">
+      <c r="D5" s="82"/>
+      <c r="E5" s="82" t="s">
         <v>174</v>
       </c>
-      <c r="F5" s="71"/>
-      <c r="G5" s="71" t="s">
+      <c r="F5" s="82"/>
+      <c r="G5" s="82" t="s">
         <v>175</v>
       </c>
-      <c r="H5" s="71"/>
-      <c r="I5" s="71" t="s">
+      <c r="H5" s="82"/>
+      <c r="I5" s="82" t="s">
         <v>176</v>
       </c>
-      <c r="J5" s="71"/>
+      <c r="J5" s="82"/>
     </row>
     <row r="6" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="73"/>
-      <c r="B6" s="74"/>
+      <c r="A6" s="116"/>
+      <c r="B6" s="117"/>
       <c r="C6" s="10" t="s">
         <v>177</v>
       </c>
@@ -2598,7 +2614,7 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="71" t="s">
+      <c r="A7" s="82" t="s">
         <v>179</v>
       </c>
       <c r="B7" s="10" t="s">
@@ -2630,7 +2646,7 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="71"/>
+      <c r="A8" s="82"/>
       <c r="B8" s="10" t="s">
         <v>182</v>
       </c>
@@ -2660,7 +2676,7 @@
       </c>
     </row>
     <row r="9" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="71"/>
+      <c r="A9" s="82"/>
       <c r="B9" s="10" t="s">
         <v>184</v>
       </c>
@@ -2690,7 +2706,7 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="71" t="s">
+      <c r="A10" s="82" t="s">
         <v>186</v>
       </c>
       <c r="B10" s="10" t="s">
@@ -2722,7 +2738,7 @@
       </c>
     </row>
     <row r="11" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="71"/>
+      <c r="A11" s="82"/>
       <c r="B11" s="10" t="s">
         <v>189</v>
       </c>
@@ -2752,7 +2768,7 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="71"/>
+      <c r="A12" s="82"/>
       <c r="B12" s="10" t="s">
         <v>191</v>
       </c>
@@ -2782,7 +2798,7 @@
       </c>
     </row>
     <row r="13" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="71" t="s">
+      <c r="A13" s="82" t="s">
         <v>193</v>
       </c>
       <c r="B13" s="10" t="s">
@@ -2814,7 +2830,7 @@
       </c>
     </row>
     <row r="14" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="71"/>
+      <c r="A14" s="82"/>
       <c r="B14" s="10" t="s">
         <v>182</v>
       </c>
@@ -2844,7 +2860,7 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="71"/>
+      <c r="A15" s="82"/>
       <c r="B15" s="10" t="s">
         <v>184</v>
       </c>
@@ -2906,10 +2922,10 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="91" t="s">
+      <c r="A17" s="111" t="s">
         <v>199</v>
       </c>
-      <c r="B17" s="92"/>
+      <c r="B17" s="112"/>
       <c r="C17" s="48"/>
       <c r="D17" s="48"/>
       <c r="E17" s="48" t="s">
@@ -2932,10 +2948,10 @@
       </c>
     </row>
     <row r="18" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="93" t="s">
+      <c r="A18" s="113" t="s">
         <v>222</v>
       </c>
-      <c r="B18" s="93"/>
+      <c r="B18" s="113"/>
       <c r="C18" s="48"/>
       <c r="D18" s="48"/>
       <c r="E18" s="49" t="e">
@@ -2969,60 +2985,60 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="83" t="s">
+      <c r="A20" s="125" t="s">
         <v>207</v>
       </c>
-      <c r="B20" s="79"/>
-      <c r="C20" s="79" t="s">
+      <c r="B20" s="121"/>
+      <c r="C20" s="121" t="s">
         <v>208</v>
       </c>
-      <c r="D20" s="79"/>
-      <c r="E20" s="80" t="s">
+      <c r="D20" s="121"/>
+      <c r="E20" s="122" t="s">
         <v>209</v>
       </c>
-      <c r="F20" s="81"/>
-      <c r="G20" s="79" t="s">
+      <c r="F20" s="123"/>
+      <c r="G20" s="121" t="s">
         <v>210</v>
       </c>
-      <c r="H20" s="82"/>
+      <c r="H20" s="124"/>
     </row>
     <row r="21" spans="1:10" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="84" t="s">
+      <c r="A21" s="126" t="s">
         <v>211</v>
       </c>
-      <c r="B21" s="71"/>
+      <c r="B21" s="82"/>
       <c r="C21" s="69" t="s">
         <v>221</v>
       </c>
       <c r="D21" s="69"/>
-      <c r="E21" s="123" t="s">
+      <c r="E21" s="83" t="s">
         <v>212</v>
       </c>
-      <c r="F21" s="124"/>
+      <c r="F21" s="84"/>
       <c r="G21" s="69" t="e">
         <f>E21-C21</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H21" s="76"/>
+      <c r="H21" s="119"/>
     </row>
     <row r="22" spans="1:10" ht="35.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="85" t="s">
+      <c r="A22" s="127" t="s">
         <v>213</v>
       </c>
-      <c r="B22" s="86"/>
-      <c r="C22" s="75" t="s">
+      <c r="B22" s="128"/>
+      <c r="C22" s="118" t="s">
         <v>236</v>
       </c>
-      <c r="D22" s="75"/>
-      <c r="E22" s="75" t="s">
+      <c r="D22" s="118"/>
+      <c r="E22" s="118" t="s">
         <v>237</v>
       </c>
-      <c r="F22" s="75"/>
-      <c r="G22" s="77" t="e">
+      <c r="F22" s="118"/>
+      <c r="G22" s="71" t="e">
         <f>+E22-C22</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H22" s="78"/>
+      <c r="H22" s="120"/>
     </row>
     <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="24" spans="1:10" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -3031,28 +3047,28 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="87" t="s">
+      <c r="A25" s="110" t="s">
         <v>1</v>
       </c>
-      <c r="B25" s="88"/>
-      <c r="C25" s="88" t="s">
+      <c r="B25" s="80"/>
+      <c r="C25" s="80" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="88"/>
-      <c r="E25" s="88" t="s">
+      <c r="D25" s="80"/>
+      <c r="E25" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="F25" s="88"/>
-      <c r="G25" s="88"/>
-      <c r="H25" s="88" t="s">
+      <c r="F25" s="80"/>
+      <c r="G25" s="80"/>
+      <c r="H25" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="I25" s="88"/>
-      <c r="J25" s="122"/>
+      <c r="I25" s="80"/>
+      <c r="J25" s="81"/>
     </row>
     <row r="26" spans="1:10" ht="35.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="89"/>
-      <c r="B26" s="90"/>
+      <c r="A26" s="129"/>
+      <c r="B26" s="130"/>
       <c r="C26" s="53" t="s">
         <v>4</v>
       </c>
@@ -3079,10 +3095,10 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="87" t="s">
+      <c r="A27" s="110" t="s">
         <v>238</v>
       </c>
-      <c r="B27" s="88"/>
+      <c r="B27" s="80"/>
       <c r="C27" s="57" t="s">
         <v>239</v>
       </c>
@@ -3283,10 +3299,10 @@
       </c>
     </row>
     <row r="33" spans="1:17" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="125" t="s">
+      <c r="A33" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="B33" s="77"/>
+      <c r="B33" s="71"/>
       <c r="C33" s="14" t="e">
         <f>C30/(SQRT(C30^2+D30^2*100))</f>
         <v>#VALUE!</v>
@@ -3308,10 +3324,10 @@
       </c>
     </row>
     <row r="34" spans="1:17" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="126" t="s">
+      <c r="A34" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="B34" s="127"/>
+      <c r="B34" s="73"/>
       <c r="C34" s="22"/>
       <c r="D34" s="22"/>
       <c r="E34" s="22"/>
@@ -3323,10 +3339,10 @@
         <v>263</v>
       </c>
       <c r="I34" s="24" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="J34" s="25" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3343,10 +3359,10 @@
         <v>264</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="J35" s="13" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="36" spans="1:17" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -3387,12 +3403,12 @@
       <c r="J38" s="21"/>
     </row>
     <row r="39" spans="1:17" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="128" t="s">
+      <c r="A39" s="77" t="s">
         <v>224</v>
       </c>
-      <c r="B39" s="129"/>
-      <c r="C39" s="129"/>
-      <c r="D39" s="130"/>
+      <c r="B39" s="78"/>
+      <c r="C39" s="78"/>
+      <c r="D39" s="79"/>
       <c r="E39" s="64" t="s">
         <v>265</v>
       </c>
@@ -3405,217 +3421,172 @@
       <c r="H39" s="66" t="s">
         <v>268</v>
       </c>
-      <c r="I39" s="94" t="s">
+      <c r="I39" s="102" t="s">
         <v>225</v>
       </c>
-      <c r="J39" s="95"/>
+      <c r="J39" s="103"/>
       <c r="Q39" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="96" t="s">
+      <c r="A40" s="104" t="s">
         <v>226</v>
       </c>
-      <c r="B40" s="97"/>
-      <c r="C40" s="97"/>
-      <c r="D40" s="98"/>
-      <c r="E40" s="114" t="s">
+      <c r="B40" s="105"/>
+      <c r="C40" s="105"/>
+      <c r="D40" s="106"/>
+      <c r="E40" s="94" t="s">
         <v>269</v>
       </c>
-      <c r="F40" s="119" t="s">
+      <c r="F40" s="99" t="s">
         <v>270</v>
       </c>
-      <c r="G40" s="102" t="s">
+      <c r="G40" s="107" t="s">
         <v>271</v>
       </c>
       <c r="H40" s="67" t="s">
         <v>227</v>
       </c>
-      <c r="I40" s="110"/>
-      <c r="J40" s="111"/>
+      <c r="I40" s="88"/>
+      <c r="J40" s="89"/>
     </row>
     <row r="41" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="99" t="s">
+      <c r="A41" s="74" t="s">
         <v>228</v>
       </c>
-      <c r="B41" s="100"/>
-      <c r="C41" s="100"/>
-      <c r="D41" s="101"/>
-      <c r="E41" s="115"/>
-      <c r="F41" s="120"/>
-      <c r="G41" s="103"/>
+      <c r="B41" s="75"/>
+      <c r="C41" s="75"/>
+      <c r="D41" s="76"/>
+      <c r="E41" s="95"/>
+      <c r="F41" s="100"/>
+      <c r="G41" s="108"/>
       <c r="H41" s="61" t="s">
         <v>227</v>
       </c>
-      <c r="I41" s="105"/>
-      <c r="J41" s="106"/>
+      <c r="I41" s="90"/>
+      <c r="J41" s="91"/>
     </row>
     <row r="42" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="99" t="s">
+      <c r="A42" s="74" t="s">
         <v>229</v>
       </c>
-      <c r="B42" s="100"/>
-      <c r="C42" s="100"/>
-      <c r="D42" s="101"/>
-      <c r="E42" s="115"/>
-      <c r="F42" s="120"/>
-      <c r="G42" s="103"/>
+      <c r="B42" s="75"/>
+      <c r="C42" s="75"/>
+      <c r="D42" s="76"/>
+      <c r="E42" s="95"/>
+      <c r="F42" s="100"/>
+      <c r="G42" s="108"/>
       <c r="H42" s="61" t="s">
         <v>227</v>
       </c>
-      <c r="I42" s="105"/>
-      <c r="J42" s="106"/>
+      <c r="I42" s="90"/>
+      <c r="J42" s="91"/>
     </row>
     <row r="43" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="99" t="s">
+      <c r="A43" s="74" t="s">
         <v>230</v>
       </c>
-      <c r="B43" s="100"/>
-      <c r="C43" s="100"/>
-      <c r="D43" s="101"/>
-      <c r="E43" s="115"/>
-      <c r="F43" s="120"/>
-      <c r="G43" s="103"/>
+      <c r="B43" s="75"/>
+      <c r="C43" s="75"/>
+      <c r="D43" s="76"/>
+      <c r="E43" s="95"/>
+      <c r="F43" s="100"/>
+      <c r="G43" s="108"/>
       <c r="H43" s="61" t="s">
         <v>227</v>
       </c>
-      <c r="I43" s="105"/>
-      <c r="J43" s="106"/>
+      <c r="I43" s="90"/>
+      <c r="J43" s="91"/>
     </row>
     <row r="44" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="99" t="s">
+      <c r="A44" s="74" t="s">
         <v>231</v>
       </c>
-      <c r="B44" s="100"/>
-      <c r="C44" s="100"/>
-      <c r="D44" s="101"/>
-      <c r="E44" s="116"/>
-      <c r="F44" s="121"/>
-      <c r="G44" s="104"/>
+      <c r="B44" s="75"/>
+      <c r="C44" s="75"/>
+      <c r="D44" s="76"/>
+      <c r="E44" s="96"/>
+      <c r="F44" s="101"/>
+      <c r="G44" s="109"/>
       <c r="H44" s="61" t="s">
         <v>227</v>
       </c>
-      <c r="I44" s="105"/>
-      <c r="J44" s="106"/>
+      <c r="I44" s="90"/>
+      <c r="J44" s="91"/>
     </row>
     <row r="45" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="99" t="s">
+      <c r="A45" s="74" t="s">
         <v>232</v>
       </c>
-      <c r="B45" s="100"/>
-      <c r="C45" s="100"/>
-      <c r="D45" s="101"/>
-      <c r="E45" s="117" t="s">
+      <c r="B45" s="75"/>
+      <c r="C45" s="75"/>
+      <c r="D45" s="76"/>
+      <c r="E45" s="97" t="s">
         <v>272</v>
       </c>
-      <c r="F45" s="117" t="s">
+      <c r="F45" s="97" t="s">
         <v>273</v>
       </c>
-      <c r="G45" s="117" t="s">
+      <c r="G45" s="97" t="s">
         <v>274</v>
       </c>
       <c r="H45" s="61" t="s">
         <v>227</v>
       </c>
-      <c r="I45" s="105"/>
-      <c r="J45" s="106"/>
+      <c r="I45" s="90"/>
+      <c r="J45" s="91"/>
     </row>
     <row r="46" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="99" t="s">
+      <c r="A46" s="74" t="s">
         <v>233</v>
       </c>
-      <c r="B46" s="100"/>
-      <c r="C46" s="100"/>
-      <c r="D46" s="101"/>
-      <c r="E46" s="117"/>
-      <c r="F46" s="117"/>
-      <c r="G46" s="117"/>
+      <c r="B46" s="75"/>
+      <c r="C46" s="75"/>
+      <c r="D46" s="76"/>
+      <c r="E46" s="97"/>
+      <c r="F46" s="97"/>
+      <c r="G46" s="97"/>
       <c r="H46" s="61" t="s">
         <v>227</v>
       </c>
-      <c r="I46" s="105"/>
-      <c r="J46" s="106"/>
+      <c r="I46" s="90"/>
+      <c r="J46" s="91"/>
     </row>
     <row r="47" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="99" t="s">
+      <c r="A47" s="74" t="s">
         <v>234</v>
       </c>
-      <c r="B47" s="100"/>
-      <c r="C47" s="100"/>
-      <c r="D47" s="101"/>
-      <c r="E47" s="117"/>
-      <c r="F47" s="117"/>
-      <c r="G47" s="117"/>
+      <c r="B47" s="75"/>
+      <c r="C47" s="75"/>
+      <c r="D47" s="76"/>
+      <c r="E47" s="97"/>
+      <c r="F47" s="97"/>
+      <c r="G47" s="97"/>
       <c r="H47" s="61" t="s">
         <v>227</v>
       </c>
-      <c r="I47" s="105"/>
-      <c r="J47" s="106"/>
+      <c r="I47" s="90"/>
+      <c r="J47" s="91"/>
     </row>
     <row r="48" spans="1:17" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="107" t="s">
+      <c r="A48" s="85" t="s">
         <v>235</v>
       </c>
-      <c r="B48" s="108"/>
-      <c r="C48" s="108"/>
-      <c r="D48" s="109"/>
-      <c r="E48" s="118"/>
-      <c r="F48" s="118"/>
-      <c r="G48" s="118"/>
+      <c r="B48" s="86"/>
+      <c r="C48" s="86"/>
+      <c r="D48" s="87"/>
+      <c r="E48" s="98"/>
+      <c r="F48" s="98"/>
+      <c r="G48" s="98"/>
       <c r="H48" s="62" t="s">
         <v>227</v>
       </c>
-      <c r="I48" s="112"/>
-      <c r="J48" s="113"/>
+      <c r="I48" s="92"/>
+      <c r="J48" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="61">
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:G25"/>
-    <mergeCell ref="A48:D48"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="A47:D47"/>
-    <mergeCell ref="E40:E44"/>
-    <mergeCell ref="E45:E48"/>
-    <mergeCell ref="F40:F44"/>
-    <mergeCell ref="F45:F48"/>
-    <mergeCell ref="G45:G48"/>
-    <mergeCell ref="I45:J45"/>
-    <mergeCell ref="I46:J46"/>
-    <mergeCell ref="I47:J47"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="A43:D43"/>
-    <mergeCell ref="G40:G44"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="A18:B18"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A5:B6"/>
@@ -3632,6 +3603,51 @@
     <mergeCell ref="A25:B26"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="G40:G44"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="A48:D48"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="E40:E44"/>
+    <mergeCell ref="E45:E48"/>
+    <mergeCell ref="F40:F44"/>
+    <mergeCell ref="F45:F48"/>
+    <mergeCell ref="G45:G48"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A39:D39"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E17 G17 I17">
